--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAC299E-6DA0-4F83-81BE-F9CD89C64C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF5671B-07CB-4645-9B2B-AC5D478D783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="822">
   <si>
     <t>家里</t>
   </si>
@@ -5473,6 +5473,42 @@
       <t>）。另外，有的房间立有赫拉特女神雕像，触碰可让主动技能满充能，且回满省地图的角色能量。
 【炸弹房】每个难度都有炸弹房，普通难度可用一级炸炸开，英雄难度可用二级炸炸开，传奇难度可用三级炸炸开，另外正如上面所说，炸弹房就是那个位于boss房前面的第四个可选择盟友的房间。</t>
     </r>
+  </si>
+  <si>
+    <t>待测，待测，400</t>
+  </si>
+  <si>
+    <t>待测，待测，80</t>
+  </si>
+  <si>
+    <t>待测，待测，70</t>
+  </si>
+  <si>
+    <t>待测，待测，180</t>
+  </si>
+  <si>
+    <t>待测，待测，40</t>
+  </si>
+  <si>
+    <t>待测，待测，100</t>
+  </si>
+  <si>
+    <t>待测，待测，0</t>
+  </si>
+  <si>
+    <t>待测，待测，15</t>
+  </si>
+  <si>
+    <t>待测，待测，99</t>
+  </si>
+  <si>
+    <t>待测，待测，14</t>
+  </si>
+  <si>
+    <t>待测，待测，54</t>
+  </si>
+  <si>
+    <t>待测，待测，5</t>
   </si>
 </sst>
 </file>
@@ -5643,7 +5679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -5691,19 +5727,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -5716,45 +5739,6 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -5791,49 +5775,10 @@
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
       <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
@@ -5856,15 +5801,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -5928,9 +5864,18 @@
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -5941,22 +5886,7 @@
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -5965,9 +5895,7 @@
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -5979,6 +5907,60 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
@@ -5986,7 +5968,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -5997,21 +5981,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6040,40 +6039,34 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6082,49 +6075,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6133,31 +6105,61 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6486,17 +6488,17 @@
     <col min="9" max="16384" width="9.06640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="30" t="s">
         <v>732</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -6514,18 +6516,18 @@
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="38" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2">
@@ -6538,13 +6540,13 @@
         <v>600</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="28"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
@@ -6562,18 +6564,18 @@
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="40" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2">
@@ -6584,16 +6586,16 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="28"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2">
@@ -6606,14 +6608,14 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="23" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="28"/>
+      <c r="H6" s="39"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="2">
@@ -6626,14 +6628,14 @@
         <v>6</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="23" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="28"/>
+      <c r="H7" s="39"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="2">
@@ -6646,14 +6648,14 @@
         <v>16</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="23" t="s">
+      <c r="F8" s="19"/>
+      <c r="G8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="2">
@@ -6666,16 +6668,16 @@
         <v>60</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="39"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>656</v>
       </c>
       <c r="B10" s="2">
@@ -6688,16 +6690,16 @@
         <v>40</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="21" t="s">
         <v>657</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="39"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="2">
@@ -6710,14 +6712,14 @@
         <v>6</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="23" t="s">
+      <c r="F11" s="19"/>
+      <c r="G11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="2">
@@ -6730,14 +6732,14 @@
         <v>49</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="23" t="s">
+      <c r="F12" s="19"/>
+      <c r="G12" s="21" t="s">
         <v>690</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="2">
@@ -6750,14 +6752,14 @@
         <v>70</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="23" t="s">
+      <c r="F13" s="19"/>
+      <c r="G13" s="21" t="s">
         <v>691</v>
       </c>
-      <c r="H13" s="28"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="2">
@@ -6768,16 +6770,16 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="21" t="s">
         <v>699</v>
       </c>
-      <c r="H14" s="28"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="2">
@@ -6790,14 +6792,14 @@
         <v>9</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="23" t="s">
+      <c r="F15" s="19"/>
+      <c r="G15" s="21" t="s">
         <v>674</v>
       </c>
-      <c r="H15" s="28"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="2">
@@ -6810,16 +6812,16 @@
         <v>63</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="28"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="2">
@@ -6832,14 +6834,14 @@
         <v>20</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="23" t="s">
+      <c r="F17" s="19"/>
+      <c r="G17" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="28"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="2">
@@ -6852,16 +6854,16 @@
         <v>32</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="21" t="s">
         <v>678</v>
       </c>
-      <c r="H18" s="28"/>
+      <c r="H18" s="39"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="2">
@@ -6874,14 +6876,14 @@
         <v>15</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="23" t="s">
+      <c r="F19" s="19"/>
+      <c r="G19" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H19" s="28"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="2">
@@ -6894,16 +6896,16 @@
         <v>41</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="H20" s="28"/>
+      <c r="H20" s="39"/>
     </row>
     <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B21" s="2">
@@ -6916,14 +6918,14 @@
         <v>10</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="23" t="s">
+      <c r="F21" s="19"/>
+      <c r="G21" s="21" t="s">
         <v>675</v>
       </c>
-      <c r="H21" s="28"/>
+      <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="2">
@@ -6936,16 +6938,16 @@
         <v>651</v>
       </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="21" t="s">
         <v>700</v>
       </c>
-      <c r="H22" s="28"/>
+      <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="2">
@@ -6958,16 +6960,16 @@
         <v>652</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="28"/>
+      <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B24" s="2">
@@ -6980,16 +6982,16 @@
         <v>10</v>
       </c>
       <c r="E24" s="2"/>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="21" t="s">
         <v>673</v>
       </c>
-      <c r="H24" s="28"/>
+      <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B25" s="2">
@@ -7002,16 +7004,16 @@
         <v>50</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="21" t="s">
         <v>677</v>
       </c>
-      <c r="H25" s="28"/>
+      <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B26" s="2">
@@ -7027,13 +7029,13 @@
       <c r="F26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="22" t="s">
         <v>676</v>
       </c>
-      <c r="H26" s="28"/>
+      <c r="H26" s="39"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>57</v>
       </c>
       <c r="B27" s="2">
@@ -7049,13 +7051,13 @@
       <c r="F27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="19" t="s">
         <v>692</v>
       </c>
-      <c r="H27" s="28"/>
+      <c r="H27" s="39"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="2">
@@ -7069,13 +7071,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H28" s="28"/>
+      <c r="H28" s="39"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="2">
@@ -7089,13 +7091,13 @@
       <c r="F29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H29" s="28"/>
+      <c r="H29" s="39"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B30" s="2">
@@ -7111,13 +7113,13 @@
       <c r="F30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="28"/>
+      <c r="H30" s="39"/>
     </row>
     <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B31" s="2">
@@ -7133,13 +7135,13 @@
       <c r="F31" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="28"/>
+      <c r="H31" s="39"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="13" t="s">
         <v>72</v>
       </c>
       <c r="B32" s="2">
@@ -7155,13 +7157,13 @@
       <c r="F32" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H32" s="28"/>
+      <c r="H32" s="39"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -7177,10 +7179,10 @@
       <c r="F33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="H33" s="28"/>
+      <c r="H33" s="39"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
@@ -7201,15 +7203,15 @@
       <c r="F34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="40" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B35" s="2">
@@ -7223,15 +7225,15 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="20" t="s">
+      <c r="G35" s="19" t="s">
         <v>701</v>
       </c>
-      <c r="H35" s="46" t="s">
+      <c r="H35" s="41" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>78</v>
       </c>
       <c r="B36" s="2">
@@ -7245,13 +7247,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="20" t="s">
+      <c r="G36" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="47"/>
+      <c r="H36" s="42"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>80</v>
       </c>
       <c r="B37" s="2">
@@ -7265,13 +7267,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="19" t="s">
         <v>702</v>
       </c>
-      <c r="H37" s="47"/>
+      <c r="H37" s="42"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>81</v>
       </c>
       <c r="B38" s="2">
@@ -7287,13 +7289,13 @@
       <c r="F38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="G38" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="H38" s="47"/>
+      <c r="H38" s="42"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>83</v>
       </c>
       <c r="B39" s="2">
@@ -7307,13 +7309,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="19" t="s">
         <v>704</v>
       </c>
-      <c r="H39" s="47"/>
+      <c r="H39" s="42"/>
     </row>
     <row r="40" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>84</v>
       </c>
       <c r="B40" s="2">
@@ -7329,13 +7331,13 @@
       <c r="F40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="H40" s="47"/>
+      <c r="H40" s="42"/>
     </row>
     <row r="41" spans="1:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>86</v>
       </c>
       <c r="B41" s="2">
@@ -7349,13 +7351,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="H41" s="47"/>
+      <c r="H41" s="42"/>
     </row>
     <row r="42" spans="1:8" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="11" t="s">
         <v>87</v>
       </c>
       <c r="B42" s="2">
@@ -7369,13 +7371,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="H42" s="47"/>
+      <c r="H42" s="42"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="12" t="s">
         <v>88</v>
       </c>
       <c r="B43" s="2">
@@ -7391,13 +7393,13 @@
       <c r="F43" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="19" t="s">
         <v>704</v>
       </c>
-      <c r="H43" s="47"/>
+      <c r="H43" s="42"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="12" t="s">
         <v>634</v>
       </c>
       <c r="B44" s="2">
@@ -7413,13 +7415,13 @@
       <c r="F44" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="20" t="s">
+      <c r="G44" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H44" s="47"/>
+      <c r="H44" s="42"/>
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="12" t="s">
         <v>633</v>
       </c>
       <c r="B45" s="2">
@@ -7435,13 +7437,13 @@
       <c r="F45" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="G45" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H45" s="47"/>
+      <c r="H45" s="42"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="12" t="s">
         <v>632</v>
       </c>
       <c r="B46" s="2">
@@ -7457,13 +7459,13 @@
       <c r="F46" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="G46" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H46" s="47"/>
+      <c r="H46" s="42"/>
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="2">
@@ -7479,13 +7481,13 @@
       <c r="F47" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="G47" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H47" s="47"/>
+      <c r="H47" s="42"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="12" t="s">
         <v>99</v>
       </c>
       <c r="B48" s="2">
@@ -7501,13 +7503,13 @@
       <c r="F48" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G48" s="20" t="s">
+      <c r="G48" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H48" s="47"/>
+      <c r="H48" s="42"/>
     </row>
     <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="13" t="s">
         <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -7523,13 +7525,13 @@
       <c r="F49" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G49" s="20" t="s">
+      <c r="G49" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H49" s="47"/>
+      <c r="H49" s="42"/>
     </row>
     <row r="50" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="13" t="s">
         <v>105</v>
       </c>
       <c r="B50" s="2">
@@ -7545,13 +7547,13 @@
       <c r="F50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G50" s="20" t="s">
+      <c r="G50" s="19" t="s">
         <v>708</v>
       </c>
-      <c r="H50" s="47"/>
+      <c r="H50" s="42"/>
     </row>
     <row r="51" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="13" t="s">
         <v>107</v>
       </c>
       <c r="B51" s="2">
@@ -7567,13 +7569,13 @@
       <c r="F51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="G51" s="19" t="s">
         <v>709</v>
       </c>
-      <c r="H51" s="47"/>
+      <c r="H51" s="42"/>
     </row>
     <row r="52" spans="1:8" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="13" t="s">
         <v>109</v>
       </c>
       <c r="B52" s="2">
@@ -7589,13 +7591,13 @@
       <c r="F52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G52" s="20" t="s">
+      <c r="G52" s="19" t="s">
         <v>710</v>
       </c>
-      <c r="H52" s="47"/>
+      <c r="H52" s="42"/>
     </row>
     <row r="53" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="13" t="s">
         <v>111</v>
       </c>
       <c r="B53" s="2">
@@ -7611,10 +7613,10 @@
       <c r="F53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="G53" s="19" t="s">
         <v>711</v>
       </c>
-      <c r="H53" s="48"/>
+      <c r="H53" s="43"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
@@ -7635,15 +7637,15 @@
       <c r="F54" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="40" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="11" t="s">
         <v>715</v>
       </c>
       <c r="B55" s="2">
@@ -7659,15 +7661,15 @@
       <c r="F55" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="G55" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="H55" s="46" t="s">
+      <c r="H55" s="41" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B56" s="2">
@@ -7683,13 +7685,13 @@
       <c r="F56" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G56" s="20" t="s">
+      <c r="G56" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="H56" s="47"/>
+      <c r="H56" s="42"/>
     </row>
     <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B57" s="2">
@@ -7705,13 +7707,13 @@
       <c r="F57" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="G57" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H57" s="47"/>
+      <c r="H57" s="42"/>
     </row>
     <row r="58" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>120</v>
       </c>
       <c r="B58" s="2">
@@ -7727,13 +7729,13 @@
       <c r="F58" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G58" s="20" t="s">
+      <c r="G58" s="19" t="s">
         <v>696</v>
       </c>
-      <c r="H58" s="47"/>
+      <c r="H58" s="42"/>
     </row>
     <row r="59" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="11" t="s">
         <v>121</v>
       </c>
       <c r="B59" s="2">
@@ -7749,13 +7751,13 @@
       <c r="F59" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G59" s="20" t="s">
+      <c r="G59" s="19" t="s">
         <v>697</v>
       </c>
-      <c r="H59" s="47"/>
+      <c r="H59" s="42"/>
     </row>
     <row r="60" spans="1:8" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="11" t="s">
         <v>123</v>
       </c>
       <c r="B60" s="2">
@@ -7771,13 +7773,13 @@
       <c r="F60" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G60" s="20" t="s">
+      <c r="G60" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="H60" s="47"/>
+      <c r="H60" s="42"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B61" s="2">
@@ -7793,13 +7795,13 @@
       <c r="F61" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="G61" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H61" s="47"/>
+      <c r="H61" s="42"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="12" t="s">
         <v>127</v>
       </c>
       <c r="B62" s="2">
@@ -7815,13 +7817,13 @@
       <c r="F62" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="G62" s="19" t="s">
         <v>698</v>
       </c>
-      <c r="H62" s="47"/>
+      <c r="H62" s="42"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="12" t="s">
         <v>129</v>
       </c>
       <c r="B63" s="2">
@@ -7837,13 +7839,13 @@
       <c r="F63" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="G63" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H63" s="47"/>
+      <c r="H63" s="42"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
       <c r="B64" s="2">
@@ -7861,13 +7863,13 @@
       <c r="F64" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="G64" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H64" s="47"/>
+      <c r="H64" s="42"/>
     </row>
     <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="14" t="s">
         <v>133</v>
       </c>
       <c r="B65" s="2">
@@ -7883,10 +7885,10 @@
       <c r="F65" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="G65" s="20" t="s">
+      <c r="G65" s="19" t="s">
         <v>693</v>
       </c>
-      <c r="H65" s="48"/>
+      <c r="H65" s="43"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
@@ -7907,15 +7909,15 @@
       <c r="F66" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H66" s="25" t="s">
+      <c r="H66" s="44" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="11" t="s">
         <v>135</v>
       </c>
       <c r="B67" s="2">
@@ -7931,15 +7933,15 @@
       <c r="F67" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="G67" s="20" t="s">
+      <c r="G67" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H67" s="49" t="s">
+      <c r="H67" s="45" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="11" t="s">
         <v>138</v>
       </c>
       <c r="B68" s="2">
@@ -7955,13 +7957,13 @@
       <c r="F68" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="G68" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H68" s="47"/>
+      <c r="H68" s="42"/>
     </row>
     <row r="69" spans="1:8" ht="81" x14ac:dyDescent="0.45">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="12" t="s">
         <v>140</v>
       </c>
       <c r="B69" s="2">
@@ -7977,13 +7979,13 @@
       <c r="F69" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G69" s="20" t="s">
+      <c r="G69" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H69" s="47"/>
+      <c r="H69" s="42"/>
     </row>
     <row r="70" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="12" t="s">
         <v>142</v>
       </c>
       <c r="B70" s="2">
@@ -7999,10 +8001,10 @@
       <c r="F70" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="G70" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H70" s="47"/>
+      <c r="H70" s="42"/>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
@@ -8023,15 +8025,15 @@
       <c r="F71" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H71" s="26" t="s">
+      <c r="H71" s="46" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="11" t="s">
         <v>145</v>
       </c>
       <c r="B72" s="2">
@@ -8045,13 +8047,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="20" t="s">
+      <c r="G72" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H72" s="28"/>
+      <c r="H72" s="39"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="11" t="s">
         <v>146</v>
       </c>
       <c r="B73" s="2">
@@ -8065,13 +8067,13 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
-      <c r="G73" s="20" t="s">
+      <c r="G73" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H73" s="28"/>
+      <c r="H73" s="39"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="11" t="s">
         <v>147</v>
       </c>
       <c r="B74" s="2">
@@ -8087,10 +8089,10 @@
       <c r="F74" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G74" s="20" t="s">
+      <c r="G74" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H74" s="28"/>
+      <c r="H74" s="39"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
@@ -8111,15 +8113,15 @@
       <c r="F75" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="40" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A76" s="12" t="s">
+      <c r="A76" s="11" t="s">
         <v>150</v>
       </c>
       <c r="B76" s="2">
@@ -8135,13 +8137,13 @@
       <c r="F76" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G76" s="20" t="s">
+      <c r="G76" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H76" s="28"/>
+      <c r="H76" s="39"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="11" t="s">
         <v>154</v>
       </c>
       <c r="B77" s="2">
@@ -8159,13 +8161,13 @@
       <c r="F77" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G77" s="20" t="s">
+      <c r="G77" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H77" s="28"/>
+      <c r="H77" s="39"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="11" t="s">
         <v>157</v>
       </c>
       <c r="B78" s="2">
@@ -8183,13 +8185,13 @@
       <c r="F78" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G78" s="20" t="s">
+      <c r="G78" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H78" s="28"/>
+      <c r="H78" s="39"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B79" s="2">
@@ -8205,13 +8207,13 @@
       <c r="F79" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G79" s="20" t="s">
+      <c r="G79" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H79" s="28"/>
+      <c r="H79" s="39"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="11" t="s">
         <v>163</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -8227,13 +8229,13 @@
       <c r="F80" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G80" s="20" t="s">
+      <c r="G80" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H80" s="28"/>
+      <c r="H80" s="39"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="11" t="s">
         <v>618</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -8249,13 +8251,13 @@
       <c r="F81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G81" s="20" t="s">
+      <c r="G81" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H81" s="28"/>
+      <c r="H81" s="39"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="11" t="s">
         <v>619</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -8271,13 +8273,13 @@
       <c r="F82" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G82" s="20" t="s">
+      <c r="G82" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H82" s="28"/>
+      <c r="H82" s="39"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="15" t="s">
         <v>172</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -8293,13 +8295,13 @@
       <c r="F83" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G83" s="20" t="s">
+      <c r="G83" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H83" s="28"/>
+      <c r="H83" s="39"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="15" t="s">
         <v>176</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -8315,13 +8317,13 @@
       <c r="F84" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G84" s="20" t="s">
+      <c r="G84" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H84" s="28"/>
+      <c r="H84" s="39"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="15" t="s">
         <v>180</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -8337,13 +8339,13 @@
       <c r="F85" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G85" s="20" t="s">
+      <c r="G85" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H85" s="28"/>
+      <c r="H85" s="39"/>
     </row>
     <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="14" t="s">
         <v>182</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -8359,13 +8361,13 @@
       <c r="F86" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G86" s="20" t="s">
+      <c r="G86" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H86" s="28"/>
+      <c r="H86" s="39"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="14" t="s">
         <v>658</v>
       </c>
       <c r="B87" s="2">
@@ -8381,10 +8383,10 @@
       <c r="F87" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G87" s="20" t="s">
+      <c r="G87" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H87" s="28"/>
+      <c r="H87" s="39"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
@@ -8405,15 +8407,15 @@
       <c r="F88" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G88" s="11" t="s">
+      <c r="G88" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H88" s="25" t="s">
+      <c r="H88" s="44" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="11" t="s">
         <v>188</v>
       </c>
       <c r="B89" s="2">
@@ -8429,13 +8431,13 @@
       <c r="F89" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G89" s="20" t="s">
+      <c r="G89" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="H89" s="28"/>
+      <c r="H89" s="39"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="11" t="s">
         <v>190</v>
       </c>
       <c r="B90" s="2">
@@ -8449,13 +8451,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
-      <c r="G90" s="20" t="s">
+      <c r="G90" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="H90" s="28"/>
+      <c r="H90" s="39"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="11" t="s">
         <v>192</v>
       </c>
       <c r="B91" s="2">
@@ -8469,13 +8471,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="20" t="s">
+      <c r="G91" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H91" s="28"/>
+      <c r="H91" s="39"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="11" t="s">
         <v>194</v>
       </c>
       <c r="B92" s="2">
@@ -8489,13 +8491,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="20" t="s">
+      <c r="G92" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H92" s="28"/>
+      <c r="H92" s="39"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="11" t="s">
         <v>195</v>
       </c>
       <c r="B93" s="2">
@@ -8509,13 +8511,13 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
-      <c r="G93" s="20" t="s">
+      <c r="G93" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H93" s="28"/>
+      <c r="H93" s="39"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="11" t="s">
         <v>196</v>
       </c>
       <c r="B94" s="2">
@@ -8531,13 +8533,13 @@
       <c r="F94" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G94" s="20" t="s">
+      <c r="G94" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="H94" s="28"/>
+      <c r="H94" s="39"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A95" s="12" t="s">
+      <c r="A95" s="11" t="s">
         <v>200</v>
       </c>
       <c r="B95" s="2">
@@ -8551,13 +8553,13 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="20" t="s">
+      <c r="G95" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="H95" s="28"/>
+      <c r="H95" s="39"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A96" s="12" t="s">
+      <c r="A96" s="11" t="s">
         <v>202</v>
       </c>
       <c r="B96" s="2">
@@ -8573,13 +8575,13 @@
       <c r="F96" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G96" s="20" t="s">
+      <c r="G96" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="H96" s="28"/>
+      <c r="H96" s="39"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A97" s="12" t="s">
+      <c r="A97" s="11" t="s">
         <v>206</v>
       </c>
       <c r="B97" s="2">
@@ -8593,13 +8595,13 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
-      <c r="G97" s="20" t="s">
+      <c r="G97" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="H97" s="28"/>
+      <c r="H97" s="39"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="11" t="s">
         <v>663</v>
       </c>
       <c r="B98" s="2">
@@ -8613,13 +8615,13 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
-      <c r="G98" s="20" t="s">
+      <c r="G98" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="H98" s="28"/>
+      <c r="H98" s="39"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="11" t="s">
         <v>664</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -8635,13 +8637,13 @@
       <c r="F99" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G99" s="20" t="s">
+      <c r="G99" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="H99" s="28"/>
-    </row>
-    <row r="100" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A100" s="12" t="s">
+      <c r="H99" s="39"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A100" s="11" t="s">
         <v>212</v>
       </c>
       <c r="B100" s="2">
@@ -8657,13 +8659,13 @@
       <c r="F100" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G100" s="20" t="s">
+      <c r="G100" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="H100" s="28"/>
+      <c r="H100" s="39"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A101" s="12" t="s">
+      <c r="A101" s="11" t="s">
         <v>215</v>
       </c>
       <c r="B101" s="2">
@@ -8679,13 +8681,13 @@
       <c r="F101" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G101" s="20" t="s">
+      <c r="G101" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="H101" s="28"/>
+      <c r="H101" s="39"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="12" t="s">
+      <c r="A102" s="11" t="s">
         <v>218</v>
       </c>
       <c r="B102" s="2">
@@ -8701,13 +8703,13 @@
       <c r="F102" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G102" s="20" t="s">
+      <c r="G102" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="H102" s="28"/>
+      <c r="H102" s="39"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="12" t="s">
         <v>220</v>
       </c>
       <c r="B103" s="2">
@@ -8723,13 +8725,13 @@
       <c r="F103" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="G103" s="20" t="s">
+      <c r="G103" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="H103" s="28"/>
+      <c r="H103" s="39"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="12" t="s">
         <v>223</v>
       </c>
       <c r="B104" s="2">
@@ -8743,13 +8745,13 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
-      <c r="G104" s="20" t="s">
+      <c r="G104" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="H104" s="28"/>
+      <c r="H104" s="39"/>
     </row>
     <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="11" t="s">
         <v>225</v>
       </c>
       <c r="B105" s="2">
@@ -8763,13 +8765,13 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="20" t="s">
+      <c r="G105" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="H105" s="28"/>
+      <c r="H105" s="39"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="11" t="s">
         <v>228</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -8783,13 +8785,13 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
-      <c r="G106" s="20" t="s">
+      <c r="G106" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H106" s="28"/>
+      <c r="H106" s="39"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="11" t="s">
         <v>230</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -8803,13 +8805,13 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
-      <c r="G107" s="20" t="s">
+      <c r="G107" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H107" s="28"/>
+      <c r="H107" s="39"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="11" t="s">
         <v>231</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -8823,13 +8825,13 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
-      <c r="G108" s="20" t="s">
+      <c r="G108" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H108" s="28"/>
+      <c r="H108" s="39"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="12" t="s">
         <v>232</v>
       </c>
       <c r="B109" s="2">
@@ -8843,13 +8845,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="20" t="s">
+      <c r="G109" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="H109" s="28"/>
+      <c r="H109" s="39"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="13" t="s">
         <v>234</v>
       </c>
       <c r="B110" s="2">
@@ -8863,13 +8865,13 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
-      <c r="G110" s="20" t="s">
+      <c r="G110" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="H110" s="28"/>
+      <c r="H110" s="39"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A111" s="15" t="s">
+      <c r="A111" s="14" t="s">
         <v>236</v>
       </c>
       <c r="B111" s="2">
@@ -8883,13 +8885,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
-      <c r="G111" s="20" t="s">
+      <c r="G111" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="H111" s="28"/>
+      <c r="H111" s="39"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="13" t="s">
         <v>238</v>
       </c>
       <c r="B112" s="2">
@@ -8905,13 +8907,13 @@
       <c r="F112" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G112" s="20" t="s">
+      <c r="G112" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H112" s="28"/>
+      <c r="H112" s="39"/>
     </row>
     <row r="113" spans="1:8" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="13" t="s">
         <v>241</v>
       </c>
       <c r="B113" s="2">
@@ -8927,13 +8929,13 @@
       <c r="F113" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="G113" s="20" t="s">
+      <c r="G113" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="H113" s="28"/>
+      <c r="H113" s="39"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="13" t="s">
         <v>243</v>
       </c>
       <c r="B114" s="2">
@@ -8949,13 +8951,13 @@
       <c r="F114" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G114" s="20" t="s">
+      <c r="G114" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="H114" s="28"/>
+      <c r="H114" s="39"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="13" t="s">
         <v>246</v>
       </c>
       <c r="B115" s="2">
@@ -8971,13 +8973,13 @@
       <c r="F115" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="G115" s="20" t="s">
+      <c r="G115" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="H115" s="28"/>
+      <c r="H115" s="39"/>
     </row>
     <row r="116" spans="1:8" ht="121.5" x14ac:dyDescent="0.45">
-      <c r="A116" s="15" t="s">
+      <c r="A116" s="14" t="s">
         <v>603</v>
       </c>
       <c r="B116" s="2">
@@ -8993,10 +8995,10 @@
       <c r="F116" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="G116" s="20" t="s">
+      <c r="G116" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="H116" s="28"/>
+      <c r="H116" s="39"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
@@ -9017,15 +9019,15 @@
       <c r="F117" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G117" s="11" t="s">
+      <c r="G117" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H117" s="26" t="s">
+      <c r="H117" s="46" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A118" s="12" t="s">
+      <c r="A118" s="11" t="s">
         <v>620</v>
       </c>
       <c r="B118" s="2">
@@ -9041,13 +9043,13 @@
       <c r="F118" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="G118" s="20" t="s">
+      <c r="G118" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H118" s="28"/>
+      <c r="H118" s="39"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A119" s="12" t="s">
+      <c r="A119" s="11" t="s">
         <v>621</v>
       </c>
       <c r="B119" s="2">
@@ -9063,13 +9065,13 @@
       <c r="F119" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="G119" s="20" t="s">
+      <c r="G119" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H119" s="28"/>
+      <c r="H119" s="39"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A120" s="12" t="s">
+      <c r="A120" s="11" t="s">
         <v>622</v>
       </c>
       <c r="B120" s="2">
@@ -9085,13 +9087,13 @@
       <c r="F120" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G120" s="20" t="s">
+      <c r="G120" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H120" s="28"/>
+      <c r="H120" s="39"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A121" s="12" t="s">
+      <c r="A121" s="11" t="s">
         <v>257</v>
       </c>
       <c r="B121" s="2">
@@ -9107,13 +9109,13 @@
       <c r="F121" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="G121" s="20" t="s">
+      <c r="G121" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H121" s="28"/>
+      <c r="H121" s="39"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="11" t="s">
         <v>259</v>
       </c>
       <c r="B122" s="2">
@@ -9129,13 +9131,13 @@
       <c r="F122" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="G122" s="20" t="s">
+      <c r="G122" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H122" s="28"/>
+      <c r="H122" s="39"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A123" s="12" t="s">
+      <c r="A123" s="11" t="s">
         <v>623</v>
       </c>
       <c r="B123" s="2">
@@ -9151,13 +9153,13 @@
       <c r="F123" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="G123" s="20" t="s">
+      <c r="G123" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H123" s="28"/>
+      <c r="H123" s="39"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="11" t="s">
         <v>624</v>
       </c>
       <c r="B124" s="2">
@@ -9173,13 +9175,13 @@
       <c r="F124" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="G124" s="20" t="s">
+      <c r="G124" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H124" s="28"/>
+      <c r="H124" s="39"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="12" t="s">
         <v>610</v>
       </c>
       <c r="B125" s="2">
@@ -9195,13 +9197,13 @@
       <c r="F125" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="G125" s="20" t="s">
+      <c r="G125" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H125" s="28"/>
+      <c r="H125" s="39"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="12" t="s">
         <v>614</v>
       </c>
       <c r="B126" s="2">
@@ -9217,13 +9219,13 @@
       <c r="F126" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="G126" s="20" t="s">
+      <c r="G126" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H126" s="28"/>
+      <c r="H126" s="39"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A127" s="14" t="s">
+      <c r="A127" s="13" t="s">
         <v>616</v>
       </c>
       <c r="B127" s="2">
@@ -9239,13 +9241,13 @@
       <c r="F127" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="G127" s="20" t="s">
+      <c r="G127" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H127" s="28"/>
+      <c r="H127" s="39"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
-      <c r="A128" s="14" t="s">
+      <c r="A128" s="13" t="s">
         <v>627</v>
       </c>
       <c r="B128" s="2">
@@ -9261,10 +9263,10 @@
       <c r="F128" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="G128" s="20" t="s">
+      <c r="G128" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H128" s="28"/>
+      <c r="H128" s="39"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
@@ -9285,15 +9287,15 @@
       <c r="F129" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G129" s="11" t="s">
+      <c r="G129" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H129" s="25" t="s">
+      <c r="H129" s="44" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A130" s="12" t="s">
+      <c r="A130" s="11" t="s">
         <v>253</v>
       </c>
       <c r="B130" s="2">
@@ -9309,13 +9311,13 @@
       <c r="F130" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G130" s="20" t="s">
+      <c r="G130" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="H130" s="28"/>
+      <c r="H130" s="39"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B131" s="2">
@@ -9329,13 +9331,13 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
-      <c r="G131" s="20" t="s">
+      <c r="G131" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H131" s="28"/>
+      <c r="H131" s="39"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A132" s="12" t="s">
+      <c r="A132" s="11" t="s">
         <v>260</v>
       </c>
       <c r="B132" s="2">
@@ -9349,13 +9351,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
-      <c r="G132" s="20" t="s">
+      <c r="G132" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="H132" s="28"/>
+      <c r="H132" s="39"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A133" s="12" t="s">
+      <c r="A133" s="11" t="s">
         <v>262</v>
       </c>
       <c r="B133" s="2">
@@ -9371,13 +9373,13 @@
       <c r="F133" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="G133" s="20" t="s">
+      <c r="G133" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H133" s="28"/>
+      <c r="H133" s="39"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A134" s="12" t="s">
+      <c r="A134" s="11" t="s">
         <v>265</v>
       </c>
       <c r="B134" s="2">
@@ -9391,13 +9393,13 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="20" t="s">
+      <c r="G134" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H134" s="28"/>
+      <c r="H134" s="39"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A135" s="12" t="s">
+      <c r="A135" s="11" t="s">
         <v>266</v>
       </c>
       <c r="B135" s="2">
@@ -9413,13 +9415,13 @@
       <c r="F135" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G135" s="20" t="s">
+      <c r="G135" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H135" s="28"/>
+      <c r="H135" s="39"/>
     </row>
     <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A136" s="12" t="s">
+      <c r="A136" s="11" t="s">
         <v>268</v>
       </c>
       <c r="B136" s="2">
@@ -9435,13 +9437,13 @@
       <c r="F136" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G136" s="20" t="s">
+      <c r="G136" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="H136" s="28"/>
+      <c r="H136" s="39"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="12" t="s">
         <v>271</v>
       </c>
       <c r="B137" s="2">
@@ -9459,13 +9461,13 @@
       <c r="F137" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G137" s="20" t="s">
+      <c r="G137" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="H137" s="28"/>
+      <c r="H137" s="39"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="13" t="s">
         <v>274</v>
       </c>
       <c r="B138" s="2">
@@ -9481,13 +9483,13 @@
       <c r="F138" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G138" s="20" t="s">
+      <c r="G138" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="H138" s="28"/>
+      <c r="H138" s="39"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A139" s="14" t="s">
+      <c r="A139" s="13" t="s">
         <v>716</v>
       </c>
       <c r="B139" s="2">
@@ -9503,13 +9505,13 @@
       <c r="F139" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="G139" s="20" t="s">
+      <c r="G139" s="19" t="s">
         <v>718</v>
       </c>
-      <c r="H139" s="28"/>
+      <c r="H139" s="39"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="13" t="s">
         <v>277</v>
       </c>
       <c r="B140" s="2">
@@ -9525,13 +9527,13 @@
       <c r="F140" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G140" s="20" t="s">
+      <c r="G140" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="H140" s="28"/>
+      <c r="H140" s="39"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A141" s="14" t="s">
+      <c r="A141" s="13" t="s">
         <v>279</v>
       </c>
       <c r="B141" s="2">
@@ -9547,13 +9549,13 @@
       <c r="F141" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G141" s="20" t="s">
+      <c r="G141" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="H141" s="28"/>
+      <c r="H141" s="39"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="13" t="s">
         <v>282</v>
       </c>
       <c r="B142" s="2">
@@ -9569,13 +9571,13 @@
       <c r="F142" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G142" s="20" t="s">
+      <c r="G142" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="H142" s="28"/>
+      <c r="H142" s="39"/>
     </row>
     <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A143" s="15" t="s">
+      <c r="A143" s="14" t="s">
         <v>285</v>
       </c>
       <c r="B143" s="2">
@@ -9591,10 +9593,10 @@
       <c r="F143" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G143" s="20" t="s">
+      <c r="G143" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="H143" s="28"/>
+      <c r="H143" s="39"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
@@ -9615,44 +9617,44 @@
       <c r="F144" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="11" t="s">
+      <c r="G144" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H144" s="27" t="s">
+      <c r="H144" s="47" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A145" s="12" t="s">
+      <c r="A145" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="B145" s="2">
-        <v>400</v>
-      </c>
-      <c r="C145" s="2">
-        <v>0</v>
-      </c>
-      <c r="D145" s="2">
-        <v>99</v>
+      <c r="B145" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>818</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G145" s="20" t="s">
+      <c r="G145" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H145" s="28"/>
+      <c r="H145" s="39"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A146" s="12" t="s">
+      <c r="A146" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B146" s="2">
-        <v>80</v>
-      </c>
-      <c r="C146" s="2">
-        <v>0</v>
+      <c r="B146" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>816</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>600</v>
@@ -9661,82 +9663,82 @@
       <c r="F146" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G146" s="20" t="s">
+      <c r="G146" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H146" s="28"/>
+      <c r="H146" s="39"/>
     </row>
     <row r="147" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A147" s="12" t="s">
+      <c r="A147" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B147" s="2">
-        <v>70</v>
-      </c>
-      <c r="C147" s="2">
-        <v>0</v>
-      </c>
-      <c r="D147" s="2">
-        <v>14</v>
+      <c r="B147" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>819</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
-      <c r="G147" s="20" t="s">
+      <c r="G147" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H147" s="28"/>
+      <c r="H147" s="39"/>
     </row>
     <row r="148" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A148" s="12" t="s">
+      <c r="A148" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="B148" s="2">
-        <v>180</v>
-      </c>
-      <c r="C148" s="2">
-        <v>15</v>
-      </c>
-      <c r="D148" s="2">
-        <v>54</v>
+      <c r="B148" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
-      <c r="G148" s="20" t="s">
+      <c r="G148" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H148" s="28"/>
+      <c r="H148" s="39"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A149" s="12" t="s">
+      <c r="A149" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B149" s="2">
-        <v>40</v>
-      </c>
-      <c r="C149" s="2">
-        <v>0</v>
-      </c>
-      <c r="D149" s="2">
-        <v>5</v>
+      <c r="B149" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>821</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G149" s="20" t="s">
+      <c r="G149" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H149" s="28"/>
+      <c r="H149" s="39"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A150" s="12" t="s">
+      <c r="A150" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B150" s="2">
-        <v>100</v>
-      </c>
-      <c r="C150" s="2">
-        <v>0</v>
+      <c r="B150" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>816</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>600</v>
@@ -9745,10 +9747,10 @@
       <c r="F150" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G150" s="20" t="s">
+      <c r="G150" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H150" s="28"/>
+      <c r="H150" s="39"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
@@ -9769,15 +9771,15 @@
       <c r="F151" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G151" s="11" t="s">
+      <c r="G151" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H151" s="27" t="s">
+      <c r="H151" s="47" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A152" s="12" t="s">
+      <c r="A152" s="11" t="s">
         <v>301</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -9793,13 +9795,13 @@
       <c r="F152" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="G152" s="20" t="s">
+      <c r="G152" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="H152" s="28"/>
+      <c r="H152" s="39"/>
     </row>
     <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A153" s="12" t="s">
+      <c r="A153" s="11" t="s">
         <v>680</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -9817,13 +9819,13 @@
       <c r="F153" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="G153" s="20" t="s">
+      <c r="G153" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="H153" s="28"/>
+      <c r="H153" s="39"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A154" s="14" t="s">
+      <c r="A154" s="13" t="s">
         <v>305</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -9841,13 +9843,13 @@
       <c r="F154" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G154" s="20" t="s">
+      <c r="G154" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H154" s="28"/>
+      <c r="H154" s="39"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A155" s="14" t="s">
+      <c r="A155" s="13" t="s">
         <v>311</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -9865,13 +9867,13 @@
       <c r="F155" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="G155" s="20" t="s">
+      <c r="G155" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H155" s="28"/>
+      <c r="H155" s="39"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A156" s="14" t="s">
+      <c r="A156" s="13" t="s">
         <v>314</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -9889,13 +9891,13 @@
       <c r="F156" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="G156" s="20" t="s">
+      <c r="G156" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H156" s="28"/>
+      <c r="H156" s="39"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A157" s="14" t="s">
+      <c r="A157" s="13" t="s">
         <v>316</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -9913,13 +9915,13 @@
       <c r="F157" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="G157" s="20" t="s">
+      <c r="G157" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H157" s="28"/>
+      <c r="H157" s="39"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A158" s="14" t="s">
+      <c r="A158" s="13" t="s">
         <v>592</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -9937,13 +9939,13 @@
       <c r="F158" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="G158" s="20" t="s">
+      <c r="G158" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H158" s="28"/>
+      <c r="H158" s="39"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A159" s="14" t="s">
+      <c r="A159" s="13" t="s">
         <v>588</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -9961,13 +9963,13 @@
       <c r="F159" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="G159" s="20" t="s">
+      <c r="G159" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H159" s="28"/>
+      <c r="H159" s="39"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A160" s="14" t="s">
+      <c r="A160" s="13" t="s">
         <v>589</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -9985,13 +9987,13 @@
       <c r="F160" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G160" s="20" t="s">
+      <c r="G160" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H160" s="28"/>
+      <c r="H160" s="39"/>
     </row>
     <row r="161" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A161" s="14" t="s">
+      <c r="A161" s="13" t="s">
         <v>590</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -10009,13 +10011,13 @@
       <c r="F161" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G161" s="20" t="s">
+      <c r="G161" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H161" s="28"/>
+      <c r="H161" s="39"/>
     </row>
     <row r="162" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="13" t="s">
         <v>591</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -10033,13 +10035,13 @@
       <c r="F162" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="G162" s="20" t="s">
+      <c r="G162" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H162" s="28"/>
+      <c r="H162" s="39"/>
     </row>
     <row r="163" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="A163" s="15" t="s">
+      <c r="A163" s="14" t="s">
         <v>329</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -10057,13 +10059,13 @@
       <c r="F163" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="G163" s="20" t="s">
+      <c r="G163" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="H163" s="28"/>
+      <c r="H163" s="39"/>
     </row>
     <row r="164" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A164" s="15" t="s">
+      <c r="A164" s="14" t="s">
         <v>334</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -10081,13 +10083,13 @@
       <c r="F164" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="G164" s="20" t="s">
+      <c r="G164" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H164" s="28"/>
+      <c r="H164" s="39"/>
     </row>
     <row r="165" spans="1:8" ht="202.5" x14ac:dyDescent="0.45">
-      <c r="A165" s="15" t="s">
+      <c r="A165" s="14" t="s">
         <v>593</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -10105,10 +10107,10 @@
       <c r="F165" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="G165" s="20" t="s">
+      <c r="G165" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="H165" s="28"/>
+      <c r="H165" s="39"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
@@ -10129,15 +10131,15 @@
       <c r="F166" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="11" t="s">
+      <c r="G166" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H166" s="27" t="s">
+      <c r="H166" s="47" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A167" s="12" t="s">
+      <c r="A167" s="11" t="s">
         <v>722</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -10153,15 +10155,15 @@
         <v>748</v>
       </c>
       <c r="F167" s="2"/>
-      <c r="G167" s="35" t="s">
+      <c r="G167" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H167" s="49" t="s">
+      <c r="H167" s="45" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A168" s="12" t="s">
+      <c r="A168" s="11" t="s">
         <v>726</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -10179,13 +10181,13 @@
       <c r="F168" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="G168" s="35" t="s">
+      <c r="G168" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H168" s="49"/>
+      <c r="H168" s="45"/>
     </row>
     <row r="169" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
-      <c r="A169" s="12" t="s">
+      <c r="A169" s="11" t="s">
         <v>727</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -10203,13 +10205,13 @@
       <c r="F169" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="G169" s="35" t="s">
+      <c r="G169" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H169" s="49"/>
+      <c r="H169" s="45"/>
     </row>
     <row r="170" spans="1:8" ht="81" x14ac:dyDescent="0.45">
-      <c r="A170" s="12" t="s">
+      <c r="A170" s="11" t="s">
         <v>728</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -10227,13 +10229,13 @@
       <c r="F170" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="G170" s="35" t="s">
+      <c r="G170" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H170" s="49"/>
+      <c r="H170" s="45"/>
     </row>
     <row r="171" spans="1:8" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A171" s="12" t="s">
+      <c r="A171" s="11" t="s">
         <v>729</v>
       </c>
       <c r="B171" s="2" t="s">
@@ -10251,13 +10253,13 @@
       <c r="F171" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G171" s="35" t="s">
+      <c r="G171" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H171" s="49"/>
+      <c r="H171" s="45"/>
     </row>
     <row r="172" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A172" s="12" t="s">
+      <c r="A172" s="11" t="s">
         <v>730</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -10275,13 +10277,13 @@
       <c r="F172" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="G172" s="35" t="s">
+      <c r="G172" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H172" s="49"/>
+      <c r="H172" s="45"/>
     </row>
     <row r="173" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A173" s="14" t="s">
+      <c r="A173" s="13" t="s">
         <v>724</v>
       </c>
       <c r="B173" s="2" t="s">
@@ -10299,13 +10301,13 @@
       <c r="F173" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="G173" s="35" t="s">
+      <c r="G173" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H173" s="49"/>
+      <c r="H173" s="45"/>
     </row>
     <row r="174" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A174" s="14" t="s">
+      <c r="A174" s="13" t="s">
         <v>725</v>
       </c>
       <c r="B174" s="2" t="s">
@@ -10323,10 +10325,10 @@
       <c r="F174" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="G174" s="35" t="s">
+      <c r="G174" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H174" s="49"/>
+      <c r="H174" s="45"/>
     </row>
     <row r="175" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
@@ -10347,13 +10349,13 @@
       <c r="F175" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G175" s="11" t="s">
+      <c r="G175" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H175" s="49"/>
+      <c r="H175" s="45"/>
     </row>
     <row r="176" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A176" s="13" t="s">
+      <c r="A176" s="12" t="s">
         <v>734</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -10371,13 +10373,13 @@
       <c r="F176" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="G176" s="35" t="s">
+      <c r="G176" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H176" s="49"/>
+      <c r="H176" s="45"/>
     </row>
     <row r="177" spans="1:8" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A177" s="13" t="s">
+      <c r="A177" s="12" t="s">
         <v>735</v>
       </c>
       <c r="B177" s="2" t="s">
@@ -10395,13 +10397,13 @@
       <c r="F177" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="G177" s="35" t="s">
+      <c r="G177" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H177" s="49"/>
+      <c r="H177" s="45"/>
     </row>
     <row r="178" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A178" s="13" t="s">
+      <c r="A178" s="12" t="s">
         <v>736</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -10419,13 +10421,13 @@
       <c r="F178" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="G178" s="35" t="s">
+      <c r="G178" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H178" s="49"/>
+      <c r="H178" s="45"/>
     </row>
     <row r="179" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A179" s="13" t="s">
+      <c r="A179" s="12" t="s">
         <v>737</v>
       </c>
       <c r="B179" s="2" t="s">
@@ -10443,13 +10445,13 @@
       <c r="F179" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="G179" s="35" t="s">
+      <c r="G179" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H179" s="49"/>
+      <c r="H179" s="45"/>
     </row>
     <row r="180" spans="1:8" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A180" s="14" t="s">
+      <c r="A180" s="13" t="s">
         <v>738</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -10467,13 +10469,13 @@
       <c r="F180" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="G180" s="35" t="s">
+      <c r="G180" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H180" s="49"/>
+      <c r="H180" s="45"/>
     </row>
     <row r="181" spans="1:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A181" s="14" t="s">
+      <c r="A181" s="13" t="s">
         <v>739</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -10491,13 +10493,13 @@
       <c r="F181" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="G181" s="35" t="s">
+      <c r="G181" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H181" s="49"/>
+      <c r="H181" s="45"/>
     </row>
     <row r="182" spans="1:8" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A182" s="14" t="s">
+      <c r="A182" s="13" t="s">
         <v>740</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -10515,13 +10517,13 @@
       <c r="F182" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="G182" s="35" t="s">
+      <c r="G182" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H182" s="49"/>
+      <c r="H182" s="45"/>
     </row>
     <row r="183" spans="1:8" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A183" s="14" t="s">
+      <c r="A183" s="13" t="s">
         <v>741</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -10539,13 +10541,13 @@
       <c r="F183" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="G183" s="35" t="s">
+      <c r="G183" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H183" s="49"/>
+      <c r="H183" s="45"/>
     </row>
     <row r="184" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A184" s="15" t="s">
+      <c r="A184" s="14" t="s">
         <v>742</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -10563,13 +10565,13 @@
       <c r="F184" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="G184" s="35" t="s">
+      <c r="G184" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H184" s="49"/>
+      <c r="H184" s="45"/>
     </row>
     <row r="185" spans="1:8" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A185" s="15" t="s">
+      <c r="A185" s="14" t="s">
         <v>743</v>
       </c>
       <c r="B185" s="2" t="s">
@@ -10587,13 +10589,13 @@
       <c r="F185" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="G185" s="35" t="s">
+      <c r="G185" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H185" s="49"/>
+      <c r="H185" s="45"/>
     </row>
     <row r="186" spans="1:8" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A186" s="15" t="s">
+      <c r="A186" s="14" t="s">
         <v>744</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -10611,13 +10613,13 @@
       <c r="F186" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="G186" s="35" t="s">
+      <c r="G186" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H186" s="49"/>
+      <c r="H186" s="45"/>
     </row>
     <row r="187" spans="1:8" ht="83.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A187" s="15" t="s">
+      <c r="A187" s="14" t="s">
         <v>745</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -10635,65 +10637,65 @@
       <c r="F187" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="G187" s="35" t="s">
+      <c r="G187" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H187" s="49"/>
-    </row>
-    <row r="188" spans="1:8" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A188" s="30" t="s">
+      <c r="H187" s="45"/>
+    </row>
+    <row r="188" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A188" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="B188" s="31" t="s">
+      <c r="B188" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C188" s="31" t="s">
+      <c r="C188" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="31" t="s">
+      <c r="D188" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E188" s="31" t="s">
+      <c r="E188" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F188" s="31" t="s">
+      <c r="F188" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G188" s="25" t="s">
+      <c r="G188" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H188" s="27" t="s">
+      <c r="H188" s="47" t="s">
         <v>647</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A189" s="32" t="s">
+      <c r="A189" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="B189" s="33">
+      <c r="B189" s="27">
         <v>120</v>
       </c>
-      <c r="C189" s="33">
+      <c r="C189" s="27">
         <v>57</v>
       </c>
-      <c r="D189" s="33">
+      <c r="D189" s="27">
         <v>40</v>
       </c>
-      <c r="E189" s="34" t="s">
+      <c r="E189" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="F189" s="33" t="s">
+      <c r="F189" s="27" t="s">
         <v>635</v>
       </c>
-      <c r="G189" s="36" t="s">
+      <c r="G189" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="H189" s="43" t="s">
+      <c r="H189" s="48" t="s">
         <v>665</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A190" s="12" t="s">
+      <c r="A190" s="11" t="s">
         <v>342</v>
       </c>
       <c r="B190" s="2">
@@ -10709,11 +10711,11 @@
       <c r="F190" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="G190" s="37"/>
-      <c r="H190" s="44"/>
+      <c r="G190" s="35"/>
+      <c r="H190" s="49"/>
     </row>
     <row r="191" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A191" s="12" t="s">
+      <c r="A191" s="11" t="s">
         <v>344</v>
       </c>
       <c r="B191" s="2">
@@ -10729,11 +10731,11 @@
       <c r="F191" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="G191" s="37"/>
-      <c r="H191" s="44"/>
+      <c r="G191" s="35"/>
+      <c r="H191" s="49"/>
     </row>
     <row r="192" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A192" s="12" t="s">
+      <c r="A192" s="11" t="s">
         <v>346</v>
       </c>
       <c r="B192" s="2">
@@ -10749,11 +10751,11 @@
       <c r="F192" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="G192" s="37"/>
-      <c r="H192" s="44"/>
+      <c r="G192" s="35"/>
+      <c r="H192" s="49"/>
     </row>
     <row r="193" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A193" s="12" t="s">
+      <c r="A193" s="11" t="s">
         <v>348</v>
       </c>
       <c r="B193" s="2">
@@ -10769,11 +10771,11 @@
       <c r="F193" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="G193" s="37"/>
-      <c r="H193" s="44"/>
+      <c r="G193" s="35"/>
+      <c r="H193" s="49"/>
     </row>
     <row r="194" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A194" s="12" t="s">
+      <c r="A194" s="11" t="s">
         <v>350</v>
       </c>
       <c r="B194" s="2">
@@ -10789,11 +10791,11 @@
       <c r="F194" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="G194" s="37"/>
-      <c r="H194" s="44"/>
+      <c r="G194" s="35"/>
+      <c r="H194" s="49"/>
     </row>
     <row r="195" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A195" s="12" t="s">
+      <c r="A195" s="11" t="s">
         <v>352</v>
       </c>
       <c r="B195" s="2">
@@ -10809,11 +10811,11 @@
       <c r="F195" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="G195" s="37"/>
-      <c r="H195" s="44"/>
+      <c r="G195" s="35"/>
+      <c r="H195" s="49"/>
     </row>
     <row r="196" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A196" s="12" t="s">
+      <c r="A196" s="11" t="s">
         <v>354</v>
       </c>
       <c r="B196" s="2">
@@ -10829,11 +10831,11 @@
       <c r="F196" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="G196" s="37"/>
-      <c r="H196" s="44"/>
+      <c r="G196" s="35"/>
+      <c r="H196" s="49"/>
     </row>
     <row r="197" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A197" s="12" t="s">
+      <c r="A197" s="11" t="s">
         <v>356</v>
       </c>
       <c r="B197" s="2">
@@ -10849,11 +10851,11 @@
       <c r="F197" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="G197" s="37"/>
-      <c r="H197" s="44"/>
+      <c r="G197" s="35"/>
+      <c r="H197" s="49"/>
     </row>
     <row r="198" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A198" s="12" t="s">
+      <c r="A198" s="11" t="s">
         <v>358</v>
       </c>
       <c r="B198" s="2">
@@ -10869,11 +10871,11 @@
       <c r="F198" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G198" s="37"/>
-      <c r="H198" s="44"/>
+      <c r="G198" s="35"/>
+      <c r="H198" s="49"/>
     </row>
     <row r="199" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A199" s="13" t="s">
+      <c r="A199" s="12" t="s">
         <v>360</v>
       </c>
       <c r="B199" s="2">
@@ -10889,11 +10891,11 @@
       <c r="F199" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="G199" s="37"/>
-      <c r="H199" s="44"/>
+      <c r="G199" s="35"/>
+      <c r="H199" s="49"/>
     </row>
     <row r="200" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A200" s="13" t="s">
+      <c r="A200" s="12" t="s">
         <v>362</v>
       </c>
       <c r="B200" s="2">
@@ -10909,11 +10911,11 @@
       <c r="F200" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="G200" s="37"/>
-      <c r="H200" s="44"/>
+      <c r="G200" s="35"/>
+      <c r="H200" s="49"/>
     </row>
     <row r="201" spans="1:8" ht="54" x14ac:dyDescent="0.45">
-      <c r="A201" s="13" t="s">
+      <c r="A201" s="12" t="s">
         <v>364</v>
       </c>
       <c r="B201" s="2">
@@ -10931,11 +10933,11 @@
       <c r="F201" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="G201" s="37"/>
-      <c r="H201" s="44"/>
+      <c r="G201" s="35"/>
+      <c r="H201" s="49"/>
     </row>
     <row r="202" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
-      <c r="A202" s="13" t="s">
+      <c r="A202" s="12" t="s">
         <v>366</v>
       </c>
       <c r="B202" s="2">
@@ -10953,11 +10955,11 @@
       <c r="F202" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="G202" s="37"/>
-      <c r="H202" s="44"/>
+      <c r="G202" s="35"/>
+      <c r="H202" s="49"/>
     </row>
     <row r="203" spans="1:8" ht="27" x14ac:dyDescent="0.45">
-      <c r="A203" s="13" t="s">
+      <c r="A203" s="12" t="s">
         <v>631</v>
       </c>
       <c r="B203" s="2">
@@ -10973,30 +10975,30 @@
       <c r="F203" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="G203" s="37"/>
-      <c r="H203" s="44"/>
+      <c r="G203" s="35"/>
+      <c r="H203" s="49"/>
     </row>
     <row r="204" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A204" s="17" t="s">
+      <c r="A204" s="16" t="s">
         <v>630</v>
       </c>
-      <c r="B204" s="18">
+      <c r="B204" s="17">
         <v>500</v>
       </c>
-      <c r="C204" s="18">
+      <c r="C204" s="17">
         <v>87</v>
       </c>
-      <c r="D204" s="18">
+      <c r="D204" s="17">
         <v>130</v>
       </c>
-      <c r="E204" s="29" t="s">
+      <c r="E204" s="23" t="s">
         <v>629</v>
       </c>
-      <c r="F204" s="18" t="s">
+      <c r="F204" s="17" t="s">
         <v>649</v>
       </c>
-      <c r="G204" s="38"/>
-      <c r="H204" s="45"/>
+      <c r="G204" s="36"/>
+      <c r="H204" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF5671B-07CB-4645-9B2B-AC5D478D783D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8FD231-E70C-48E5-BE72-865E70A36880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4265,74 +4265,6 @@
   </si>
   <si>
     <r>
-      <t>【人物介绍】他孤身站在白盾骑士团的战旗下。尽管身负致命伤，他仍坚守一小时，击退了异教徒的猛攻，拼尽全力保护朝圣者。
-【技能效果】圣骑士套装赋予他2.24倍的回血效果；可举盾抵挡三次攻击
-【人物装备】圣骑士套装，法尔维斯护盾，双刃大砍刀
-【所需戒指】普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>：10/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>60</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>【人物介绍】他带着寥寥数名信徒，携着赫拉特之光来到异教徒的土地上。部落向他提出，只要他放弃信仰便可饶他一命 —— 伊恩则以祈祷作答。
 【技能效果】提升友军物理伤害10/</t>
     </r>
@@ -4915,142 +4847,6 @@
         <family val="2"/>
       </rPr>
       <t>：30/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>180</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>【人物介绍】当绝望笼罩众人时，她重新集结了营团，带领他们继续前进。敌方首领倒下了，她的族人安然无恙地走了出来。我们守护着她的遗骸，并坚信埃琳娜的烈酒守护着我们。
-【技能效果】皇帝之盾赋予她给友军提供魔法护盾的能力，吸收一定伤害，持续30秒；4件尖刺护甲赋予她给予近战中敌人反甲伤害,在普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>中分别为20/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-【人物装备】尖刺套装（无头盔），皇帝之盾，铁质变种剑
-【所需戒指】普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>奇：30/</t>
     </r>
     <r>
       <rPr>
@@ -5509,6 +5305,210 @@
   </si>
   <si>
     <t>待测，待测，5</t>
+  </si>
+  <si>
+    <r>
+      <t>【人物介绍】他孤身站在白盾骑士团的战旗下。尽管身负致命伤，他仍坚守一小时，击退了异教徒的猛攻，拼尽全力保护朝圣者。
+【技能效果】圣骑士套装赋予他2.24倍的回血效果；可举盾抵挡三次攻击；战吼嘲讽吸引敌人仇恨
+【人物装备】圣骑士套装，法尔维斯护盾，双刃大砍刀
+【所需戒指】普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：10/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>60</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【人物介绍】当绝望笼罩众人时，她重新集结了营团，带领他们继续前进。敌方首领倒下了，她的族人安然无恙地走了出来。我们守护着她的遗骸，并坚信埃琳娜的烈酒守护着我们。
+【技能效果】皇帝之盾赋予她给友军提供魔法护盾的能力，吸收一定伤害，持续30秒；4件尖刺护甲赋予她给予近战中敌人反甲伤害,在普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>中分别为20/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>60；战吼嘲讽吸引敌人仇恨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+【人物装备】尖刺套装（无头盔），皇帝之盾，铁质变种剑
+【所需戒指】普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>奇：30/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>180</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6099,16 +6099,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6120,16 +6129,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6141,25 +6159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6489,16 +6489,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="40" t="s">
         <v>732</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="37"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -6522,7 +6522,7 @@
       <c r="G2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="31" t="s">
         <v>647</v>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       <c r="G3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="39"/>
+      <c r="H3" s="32"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
@@ -6570,7 +6570,7 @@
       <c r="G4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="33" t="s">
         <v>647</v>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       <c r="G5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="39"/>
+      <c r="H5" s="32"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
@@ -6612,7 +6612,7 @@
       <c r="G6" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="39"/>
+      <c r="H6" s="32"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
@@ -6632,7 +6632,7 @@
       <c r="G7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="39"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
@@ -6652,7 +6652,7 @@
       <c r="G8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="39"/>
+      <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
@@ -6674,7 +6674,7 @@
       <c r="G9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="39"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
@@ -6696,7 +6696,7 @@
       <c r="G10" s="21" t="s">
         <v>657</v>
       </c>
-      <c r="H10" s="39"/>
+      <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
@@ -6716,7 +6716,7 @@
       <c r="G11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="39"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
@@ -6736,7 +6736,7 @@
       <c r="G12" s="21" t="s">
         <v>690</v>
       </c>
-      <c r="H12" s="39"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
@@ -6756,7 +6756,7 @@
       <c r="G13" s="21" t="s">
         <v>691</v>
       </c>
-      <c r="H13" s="39"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
@@ -6776,7 +6776,7 @@
       <c r="G14" s="21" t="s">
         <v>699</v>
       </c>
-      <c r="H14" s="39"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
@@ -6796,7 +6796,7 @@
       <c r="G15" s="21" t="s">
         <v>674</v>
       </c>
-      <c r="H15" s="39"/>
+      <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
@@ -6818,7 +6818,7 @@
       <c r="G16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="39"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
@@ -6838,7 +6838,7 @@
       <c r="G17" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="39"/>
+      <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
@@ -6860,7 +6860,7 @@
       <c r="G18" s="21" t="s">
         <v>678</v>
       </c>
-      <c r="H18" s="39"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
@@ -6880,7 +6880,7 @@
       <c r="G19" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H19" s="39"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="11" t="s">
@@ -6902,7 +6902,7 @@
       <c r="G20" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="32"/>
     </row>
     <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A21" s="11" t="s">
@@ -6922,7 +6922,7 @@
       <c r="G21" s="21" t="s">
         <v>675</v>
       </c>
-      <c r="H21" s="39"/>
+      <c r="H21" s="32"/>
     </row>
     <row r="22" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
@@ -6944,7 +6944,7 @@
       <c r="G22" s="21" t="s">
         <v>700</v>
       </c>
-      <c r="H22" s="39"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="12" t="s">
@@ -6966,7 +6966,7 @@
       <c r="G23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="39"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="12" t="s">
@@ -6988,7 +6988,7 @@
       <c r="G24" s="21" t="s">
         <v>673</v>
       </c>
-      <c r="H24" s="39"/>
+      <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A25" s="12" t="s">
@@ -7010,7 +7010,7 @@
       <c r="G25" s="21" t="s">
         <v>677</v>
       </c>
-      <c r="H25" s="39"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A26" s="12" t="s">
@@ -7032,7 +7032,7 @@
       <c r="G26" s="22" t="s">
         <v>676</v>
       </c>
-      <c r="H26" s="39"/>
+      <c r="H26" s="32"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="12" t="s">
@@ -7054,7 +7054,7 @@
       <c r="G27" s="19" t="s">
         <v>692</v>
       </c>
-      <c r="H27" s="39"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="12" t="s">
@@ -7074,7 +7074,7 @@
       <c r="G28" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H28" s="39"/>
+      <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
@@ -7094,7 +7094,7 @@
       <c r="G29" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H29" s="39"/>
+      <c r="H29" s="32"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
@@ -7116,7 +7116,7 @@
       <c r="G30" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="39"/>
+      <c r="H30" s="32"/>
     </row>
     <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
@@ -7138,7 +7138,7 @@
       <c r="G31" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="39"/>
+      <c r="H31" s="32"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
@@ -7160,7 +7160,7 @@
       <c r="G32" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H32" s="39"/>
+      <c r="H32" s="32"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="14" t="s">
@@ -7182,7 +7182,7 @@
       <c r="G33" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="H33" s="39"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
@@ -7206,7 +7206,7 @@
       <c r="G34" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="40" t="s">
+      <c r="H34" s="33" t="s">
         <v>647</v>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       <c r="G35" s="19" t="s">
         <v>701</v>
       </c>
-      <c r="H35" s="41" t="s">
+      <c r="H35" s="47" t="s">
         <v>714</v>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       <c r="G36" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="42"/>
+      <c r="H36" s="48"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="11" t="s">
@@ -7270,7 +7270,7 @@
       <c r="G37" s="19" t="s">
         <v>702</v>
       </c>
-      <c r="H37" s="42"/>
+      <c r="H37" s="48"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="11" t="s">
@@ -7292,7 +7292,7 @@
       <c r="G38" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="H38" s="42"/>
+      <c r="H38" s="48"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
@@ -7312,7 +7312,7 @@
       <c r="G39" s="19" t="s">
         <v>704</v>
       </c>
-      <c r="H39" s="42"/>
+      <c r="H39" s="48"/>
     </row>
     <row r="40" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
@@ -7334,7 +7334,7 @@
       <c r="G40" s="19" t="s">
         <v>705</v>
       </c>
-      <c r="H40" s="42"/>
+      <c r="H40" s="48"/>
     </row>
     <row r="41" spans="1:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="11" t="s">
@@ -7354,7 +7354,7 @@
       <c r="G41" s="19" t="s">
         <v>706</v>
       </c>
-      <c r="H41" s="42"/>
+      <c r="H41" s="48"/>
     </row>
     <row r="42" spans="1:8" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="11" t="s">
@@ -7374,7 +7374,7 @@
       <c r="G42" s="19" t="s">
         <v>703</v>
       </c>
-      <c r="H42" s="42"/>
+      <c r="H42" s="48"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="12" t="s">
@@ -7396,7 +7396,7 @@
       <c r="G43" s="19" t="s">
         <v>704</v>
       </c>
-      <c r="H43" s="42"/>
+      <c r="H43" s="48"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="12" t="s">
@@ -7418,7 +7418,7 @@
       <c r="G44" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H44" s="42"/>
+      <c r="H44" s="48"/>
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
@@ -7440,7 +7440,7 @@
       <c r="G45" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H45" s="42"/>
+      <c r="H45" s="48"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
@@ -7462,7 +7462,7 @@
       <c r="G46" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H46" s="42"/>
+      <c r="H46" s="48"/>
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="12" t="s">
@@ -7484,7 +7484,7 @@
       <c r="G47" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H47" s="42"/>
+      <c r="H47" s="48"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="12" t="s">
@@ -7506,7 +7506,7 @@
       <c r="G48" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H48" s="42"/>
+      <c r="H48" s="48"/>
     </row>
     <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A49" s="13" t="s">
@@ -7528,7 +7528,7 @@
       <c r="G49" s="19" t="s">
         <v>707</v>
       </c>
-      <c r="H49" s="42"/>
+      <c r="H49" s="48"/>
     </row>
     <row r="50" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="13" t="s">
@@ -7550,7 +7550,7 @@
       <c r="G50" s="19" t="s">
         <v>708</v>
       </c>
-      <c r="H50" s="42"/>
+      <c r="H50" s="48"/>
     </row>
     <row r="51" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="13" t="s">
@@ -7572,7 +7572,7 @@
       <c r="G51" s="19" t="s">
         <v>709</v>
       </c>
-      <c r="H51" s="42"/>
+      <c r="H51" s="48"/>
     </row>
     <row r="52" spans="1:8" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="13" t="s">
@@ -7594,7 +7594,7 @@
       <c r="G52" s="19" t="s">
         <v>710</v>
       </c>
-      <c r="H52" s="42"/>
+      <c r="H52" s="48"/>
     </row>
     <row r="53" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="13" t="s">
@@ -7616,7 +7616,7 @@
       <c r="G53" s="19" t="s">
         <v>711</v>
       </c>
-      <c r="H53" s="43"/>
+      <c r="H53" s="49"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
@@ -7640,7 +7640,7 @@
       <c r="G54" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H54" s="40" t="s">
+      <c r="H54" s="33" t="s">
         <v>647</v>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       <c r="G55" s="19" t="s">
         <v>720</v>
       </c>
-      <c r="H55" s="41" t="s">
+      <c r="H55" s="47" t="s">
         <v>712</v>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       <c r="G56" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="H56" s="42"/>
+      <c r="H56" s="48"/>
     </row>
     <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="11" t="s">
@@ -7710,7 +7710,7 @@
       <c r="G57" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H57" s="42"/>
+      <c r="H57" s="48"/>
     </row>
     <row r="58" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="11" t="s">
@@ -7732,7 +7732,7 @@
       <c r="G58" s="19" t="s">
         <v>696</v>
       </c>
-      <c r="H58" s="42"/>
+      <c r="H58" s="48"/>
     </row>
     <row r="59" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="11" t="s">
@@ -7754,7 +7754,7 @@
       <c r="G59" s="19" t="s">
         <v>697</v>
       </c>
-      <c r="H59" s="42"/>
+      <c r="H59" s="48"/>
     </row>
     <row r="60" spans="1:8" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="11" t="s">
@@ -7776,7 +7776,7 @@
       <c r="G60" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="H60" s="42"/>
+      <c r="H60" s="48"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="11" t="s">
@@ -7798,7 +7798,7 @@
       <c r="G61" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H61" s="42"/>
+      <c r="H61" s="48"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="12" t="s">
@@ -7820,7 +7820,7 @@
       <c r="G62" s="19" t="s">
         <v>698</v>
       </c>
-      <c r="H62" s="42"/>
+      <c r="H62" s="48"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="12" t="s">
@@ -7842,7 +7842,7 @@
       <c r="G63" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H63" s="42"/>
+      <c r="H63" s="48"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="12" t="s">
@@ -7866,7 +7866,7 @@
       <c r="G64" s="19" t="s">
         <v>695</v>
       </c>
-      <c r="H64" s="42"/>
+      <c r="H64" s="48"/>
     </row>
     <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
       <c r="A65" s="14" t="s">
@@ -7888,7 +7888,7 @@
       <c r="G65" s="19" t="s">
         <v>693</v>
       </c>
-      <c r="H65" s="43"/>
+      <c r="H65" s="49"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
@@ -7912,7 +7912,7 @@
       <c r="G66" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H66" s="44" t="s">
+      <c r="H66" s="34" t="s">
         <v>647</v>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       <c r="G67" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H67" s="45" t="s">
+      <c r="H67" s="50" t="s">
         <v>648</v>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       <c r="G68" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H68" s="42"/>
+      <c r="H68" s="48"/>
     </row>
     <row r="69" spans="1:8" ht="81" x14ac:dyDescent="0.45">
       <c r="A69" s="12" t="s">
@@ -7982,7 +7982,7 @@
       <c r="G69" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H69" s="42"/>
+      <c r="H69" s="48"/>
     </row>
     <row r="70" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A70" s="12" t="s">
@@ -8004,7 +8004,7 @@
       <c r="G70" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H70" s="42"/>
+      <c r="H70" s="48"/>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
@@ -8028,7 +8028,7 @@
       <c r="G71" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H71" s="46" t="s">
+      <c r="H71" s="35" t="s">
         <v>647</v>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       <c r="G72" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H72" s="39"/>
+      <c r="H72" s="32"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="11" t="s">
@@ -8070,7 +8070,7 @@
       <c r="G73" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H73" s="39"/>
+      <c r="H73" s="32"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="11" t="s">
@@ -8092,7 +8092,7 @@
       <c r="G74" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H74" s="39"/>
+      <c r="H74" s="32"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
@@ -8116,7 +8116,7 @@
       <c r="G75" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H75" s="40" t="s">
+      <c r="H75" s="33" t="s">
         <v>647</v>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
       <c r="G76" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H76" s="39"/>
+      <c r="H76" s="32"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="11" t="s">
@@ -8164,7 +8164,7 @@
       <c r="G77" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H77" s="39"/>
+      <c r="H77" s="32"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="11" t="s">
@@ -8188,7 +8188,7 @@
       <c r="G78" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H78" s="39"/>
+      <c r="H78" s="32"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="11" t="s">
@@ -8210,7 +8210,7 @@
       <c r="G79" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H79" s="39"/>
+      <c r="H79" s="32"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="11" t="s">
@@ -8232,7 +8232,7 @@
       <c r="G80" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H80" s="39"/>
+      <c r="H80" s="32"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
@@ -8254,7 +8254,7 @@
       <c r="G81" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H81" s="39"/>
+      <c r="H81" s="32"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
@@ -8276,7 +8276,7 @@
       <c r="G82" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H82" s="39"/>
+      <c r="H82" s="32"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="15" t="s">
@@ -8298,7 +8298,7 @@
       <c r="G83" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H83" s="39"/>
+      <c r="H83" s="32"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="15" t="s">
@@ -8320,7 +8320,7 @@
       <c r="G84" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H84" s="39"/>
+      <c r="H84" s="32"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="15" t="s">
@@ -8342,7 +8342,7 @@
       <c r="G85" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H85" s="39"/>
+      <c r="H85" s="32"/>
     </row>
     <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A86" s="14" t="s">
@@ -8364,7 +8364,7 @@
       <c r="G86" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H86" s="39"/>
+      <c r="H86" s="32"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="14" t="s">
@@ -8386,7 +8386,7 @@
       <c r="G87" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H87" s="39"/>
+      <c r="H87" s="32"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
@@ -8410,7 +8410,7 @@
       <c r="G88" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H88" s="44" t="s">
+      <c r="H88" s="34" t="s">
         <v>647</v>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       <c r="G89" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="H89" s="39"/>
+      <c r="H89" s="32"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="11" t="s">
@@ -8454,7 +8454,7 @@
       <c r="G90" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="H90" s="39"/>
+      <c r="H90" s="32"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="11" t="s">
@@ -8474,7 +8474,7 @@
       <c r="G91" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H91" s="39"/>
+      <c r="H91" s="32"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="11" t="s">
@@ -8494,7 +8494,7 @@
       <c r="G92" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H92" s="39"/>
+      <c r="H92" s="32"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="11" t="s">
@@ -8514,7 +8514,7 @@
       <c r="G93" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H93" s="39"/>
+      <c r="H93" s="32"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="11" t="s">
@@ -8536,7 +8536,7 @@
       <c r="G94" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="H94" s="39"/>
+      <c r="H94" s="32"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="11" t="s">
@@ -8556,7 +8556,7 @@
       <c r="G95" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="H95" s="39"/>
+      <c r="H95" s="32"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="11" t="s">
@@ -8578,7 +8578,7 @@
       <c r="G96" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="H96" s="39"/>
+      <c r="H96" s="32"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
@@ -8598,7 +8598,7 @@
       <c r="G97" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="H97" s="39"/>
+      <c r="H97" s="32"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
@@ -8618,7 +8618,7 @@
       <c r="G98" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="H98" s="39"/>
+      <c r="H98" s="32"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
@@ -8640,7 +8640,7 @@
       <c r="G99" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="H99" s="39"/>
+      <c r="H99" s="32"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="11" t="s">
@@ -8662,7 +8662,7 @@
       <c r="G100" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="H100" s="39"/>
+      <c r="H100" s="32"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="11" t="s">
@@ -8684,7 +8684,7 @@
       <c r="G101" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="H101" s="39"/>
+      <c r="H101" s="32"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="11" t="s">
@@ -8706,7 +8706,7 @@
       <c r="G102" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="H102" s="39"/>
+      <c r="H102" s="32"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
@@ -8728,7 +8728,7 @@
       <c r="G103" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="H103" s="39"/>
+      <c r="H103" s="32"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="12" t="s">
@@ -8748,7 +8748,7 @@
       <c r="G104" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="H104" s="39"/>
+      <c r="H104" s="32"/>
     </row>
     <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A105" s="11" t="s">
@@ -8768,7 +8768,7 @@
       <c r="G105" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="H105" s="39"/>
+      <c r="H105" s="32"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="11" t="s">
@@ -8788,7 +8788,7 @@
       <c r="G106" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H106" s="39"/>
+      <c r="H106" s="32"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="11" t="s">
@@ -8808,7 +8808,7 @@
       <c r="G107" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H107" s="39"/>
+      <c r="H107" s="32"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="11" t="s">
@@ -8828,7 +8828,7 @@
       <c r="G108" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H108" s="39"/>
+      <c r="H108" s="32"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
@@ -8848,7 +8848,7 @@
       <c r="G109" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="H109" s="39"/>
+      <c r="H109" s="32"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
@@ -8868,7 +8868,7 @@
       <c r="G110" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="H110" s="39"/>
+      <c r="H110" s="32"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
@@ -8888,7 +8888,7 @@
       <c r="G111" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="H111" s="39"/>
+      <c r="H111" s="32"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
@@ -8910,7 +8910,7 @@
       <c r="G112" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H112" s="39"/>
+      <c r="H112" s="32"/>
     </row>
     <row r="113" spans="1:8" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
@@ -8932,7 +8932,7 @@
       <c r="G113" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="H113" s="39"/>
+      <c r="H113" s="32"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
@@ -8954,7 +8954,7 @@
       <c r="G114" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="H114" s="39"/>
+      <c r="H114" s="32"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
@@ -8976,7 +8976,7 @@
       <c r="G115" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="H115" s="39"/>
+      <c r="H115" s="32"/>
     </row>
     <row r="116" spans="1:8" ht="121.5" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
@@ -8998,7 +8998,7 @@
       <c r="G116" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="H116" s="39"/>
+      <c r="H116" s="32"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
@@ -9022,7 +9022,7 @@
       <c r="G117" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H117" s="46" t="s">
+      <c r="H117" s="35" t="s">
         <v>647</v>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       <c r="G118" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H118" s="39"/>
+      <c r="H118" s="32"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="11" t="s">
@@ -9068,7 +9068,7 @@
       <c r="G119" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H119" s="39"/>
+      <c r="H119" s="32"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="11" t="s">
@@ -9090,7 +9090,7 @@
       <c r="G120" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H120" s="39"/>
+      <c r="H120" s="32"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="11" t="s">
@@ -9112,7 +9112,7 @@
       <c r="G121" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H121" s="39"/>
+      <c r="H121" s="32"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="11" t="s">
@@ -9134,7 +9134,7 @@
       <c r="G122" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H122" s="39"/>
+      <c r="H122" s="32"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="11" t="s">
@@ -9156,7 +9156,7 @@
       <c r="G123" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H123" s="39"/>
+      <c r="H123" s="32"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
@@ -9178,7 +9178,7 @@
       <c r="G124" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H124" s="39"/>
+      <c r="H124" s="32"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
@@ -9200,7 +9200,7 @@
       <c r="G125" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H125" s="39"/>
+      <c r="H125" s="32"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
@@ -9222,7 +9222,7 @@
       <c r="G126" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H126" s="39"/>
+      <c r="H126" s="32"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
@@ -9244,7 +9244,7 @@
       <c r="G127" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H127" s="39"/>
+      <c r="H127" s="32"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="13" t="s">
@@ -9266,7 +9266,7 @@
       <c r="G128" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="H128" s="39"/>
+      <c r="H128" s="32"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
@@ -9290,7 +9290,7 @@
       <c r="G129" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H129" s="44" t="s">
+      <c r="H129" s="34" t="s">
         <v>647</v>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       <c r="G130" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="H130" s="39"/>
+      <c r="H130" s="32"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="12" t="s">
@@ -9334,7 +9334,7 @@
       <c r="G131" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H131" s="39"/>
+      <c r="H131" s="32"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
@@ -9354,7 +9354,7 @@
       <c r="G132" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="H132" s="39"/>
+      <c r="H132" s="32"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="11" t="s">
@@ -9376,7 +9376,7 @@
       <c r="G133" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H133" s="39"/>
+      <c r="H133" s="32"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
@@ -9396,7 +9396,7 @@
       <c r="G134" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H134" s="39"/>
+      <c r="H134" s="32"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
@@ -9418,7 +9418,7 @@
       <c r="G135" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="H135" s="39"/>
+      <c r="H135" s="32"/>
     </row>
     <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="11" t="s">
@@ -9440,7 +9440,7 @@
       <c r="G136" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="H136" s="39"/>
+      <c r="H136" s="32"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
@@ -9464,7 +9464,7 @@
       <c r="G137" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="H137" s="39"/>
+      <c r="H137" s="32"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
@@ -9486,7 +9486,7 @@
       <c r="G138" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="H138" s="39"/>
+      <c r="H138" s="32"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
@@ -9508,7 +9508,7 @@
       <c r="G139" s="19" t="s">
         <v>718</v>
       </c>
-      <c r="H139" s="39"/>
+      <c r="H139" s="32"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
@@ -9530,7 +9530,7 @@
       <c r="G140" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="H140" s="39"/>
+      <c r="H140" s="32"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
@@ -9552,7 +9552,7 @@
       <c r="G141" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="H141" s="39"/>
+      <c r="H141" s="32"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
@@ -9574,7 +9574,7 @@
       <c r="G142" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="H142" s="39"/>
+      <c r="H142" s="32"/>
     </row>
     <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A143" s="14" t="s">
@@ -9596,7 +9596,7 @@
       <c r="G143" s="19" t="s">
         <v>281</v>
       </c>
-      <c r="H143" s="39"/>
+      <c r="H143" s="32"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
@@ -9620,7 +9620,7 @@
       <c r="G144" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H144" s="47" t="s">
+      <c r="H144" s="36" t="s">
         <v>647</v>
       </c>
     </row>
@@ -9629,13 +9629,13 @@
         <v>288</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C145" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>816</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>818</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -9644,17 +9644,17 @@
       <c r="G145" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H145" s="39"/>
+      <c r="H145" s="32"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="11" t="s">
         <v>290</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>600</v>
@@ -9666,60 +9666,60 @@
       <c r="G146" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H146" s="39"/>
+      <c r="H146" s="32"/>
     </row>
     <row r="147" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="11" t="s">
         <v>292</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H147" s="39"/>
+      <c r="H147" s="32"/>
     </row>
     <row r="148" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="11" t="s">
         <v>293</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H148" s="39"/>
+      <c r="H148" s="32"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="11" t="s">
         <v>294</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>816</v>
-      </c>
       <c r="D149" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -9728,17 +9728,17 @@
       <c r="G149" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H149" s="39"/>
+      <c r="H149" s="32"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="11" t="s">
         <v>296</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>600</v>
@@ -9750,7 +9750,7 @@
       <c r="G150" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="H150" s="39"/>
+      <c r="H150" s="32"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
@@ -9774,7 +9774,7 @@
       <c r="G151" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H151" s="47" t="s">
+      <c r="H151" s="36" t="s">
         <v>647</v>
       </c>
     </row>
@@ -9798,7 +9798,7 @@
       <c r="G152" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="H152" s="39"/>
+      <c r="H152" s="32"/>
     </row>
     <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
@@ -9822,7 +9822,7 @@
       <c r="G153" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="H153" s="39"/>
+      <c r="H153" s="32"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
@@ -9846,7 +9846,7 @@
       <c r="G154" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H154" s="39"/>
+      <c r="H154" s="32"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
@@ -9870,7 +9870,7 @@
       <c r="G155" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H155" s="39"/>
+      <c r="H155" s="32"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
@@ -9894,7 +9894,7 @@
       <c r="G156" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H156" s="39"/>
+      <c r="H156" s="32"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
@@ -9918,7 +9918,7 @@
       <c r="G157" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H157" s="39"/>
+      <c r="H157" s="32"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
@@ -9942,7 +9942,7 @@
       <c r="G158" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H158" s="39"/>
+      <c r="H158" s="32"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
@@ -9966,7 +9966,7 @@
       <c r="G159" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H159" s="39"/>
+      <c r="H159" s="32"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
@@ -9990,7 +9990,7 @@
       <c r="G160" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H160" s="39"/>
+      <c r="H160" s="32"/>
     </row>
     <row r="161" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
@@ -10014,7 +10014,7 @@
       <c r="G161" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H161" s="39"/>
+      <c r="H161" s="32"/>
     </row>
     <row r="162" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
@@ -10038,7 +10038,7 @@
       <c r="G162" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H162" s="39"/>
+      <c r="H162" s="32"/>
     </row>
     <row r="163" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
@@ -10062,7 +10062,7 @@
       <c r="G163" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="H163" s="39"/>
+      <c r="H163" s="32"/>
     </row>
     <row r="164" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="14" t="s">
@@ -10086,7 +10086,7 @@
       <c r="G164" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H164" s="39"/>
+      <c r="H164" s="32"/>
     </row>
     <row r="165" spans="1:8" ht="202.5" x14ac:dyDescent="0.45">
       <c r="A165" s="14" t="s">
@@ -10110,7 +10110,7 @@
       <c r="G165" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="H165" s="39"/>
+      <c r="H165" s="32"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
@@ -10134,7 +10134,7 @@
       <c r="G166" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H166" s="47" t="s">
+      <c r="H166" s="36" t="s">
         <v>647</v>
       </c>
     </row>
@@ -10158,8 +10158,8 @@
       <c r="G167" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H167" s="45" t="s">
-        <v>809</v>
+      <c r="H167" s="50" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -10184,7 +10184,7 @@
       <c r="G168" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H168" s="45"/>
+      <c r="H168" s="50"/>
     </row>
     <row r="169" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
@@ -10208,7 +10208,7 @@
       <c r="G169" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H169" s="45"/>
+      <c r="H169" s="50"/>
     </row>
     <row r="170" spans="1:8" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
@@ -10232,7 +10232,7 @@
       <c r="G170" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H170" s="45"/>
+      <c r="H170" s="50"/>
     </row>
     <row r="171" spans="1:8" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
@@ -10256,7 +10256,7 @@
       <c r="G171" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H171" s="45"/>
+      <c r="H171" s="50"/>
     </row>
     <row r="172" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
@@ -10280,7 +10280,7 @@
       <c r="G172" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H172" s="45"/>
+      <c r="H172" s="50"/>
     </row>
     <row r="173" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
@@ -10304,7 +10304,7 @@
       <c r="G173" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H173" s="45"/>
+      <c r="H173" s="50"/>
     </row>
     <row r="174" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
@@ -10328,7 +10328,7 @@
       <c r="G174" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H174" s="45"/>
+      <c r="H174" s="50"/>
     </row>
     <row r="175" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
@@ -10352,7 +10352,7 @@
       <c r="G175" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H175" s="45"/>
+      <c r="H175" s="50"/>
     </row>
     <row r="176" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
@@ -10376,7 +10376,7 @@
       <c r="G176" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H176" s="45"/>
+      <c r="H176" s="50"/>
     </row>
     <row r="177" spans="1:8" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
@@ -10400,7 +10400,7 @@
       <c r="G177" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H177" s="45"/>
+      <c r="H177" s="50"/>
     </row>
     <row r="178" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
@@ -10424,7 +10424,7 @@
       <c r="G178" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H178" s="45"/>
+      <c r="H178" s="50"/>
     </row>
     <row r="179" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
@@ -10448,7 +10448,7 @@
       <c r="G179" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H179" s="45"/>
+      <c r="H179" s="50"/>
     </row>
     <row r="180" spans="1:8" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
@@ -10472,7 +10472,7 @@
       <c r="G180" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H180" s="45"/>
+      <c r="H180" s="50"/>
     </row>
     <row r="181" spans="1:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
@@ -10496,7 +10496,7 @@
       <c r="G181" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H181" s="45"/>
+      <c r="H181" s="50"/>
     </row>
     <row r="182" spans="1:8" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
@@ -10515,12 +10515,12 @@
         <v>600</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="G182" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H182" s="45"/>
+      <c r="H182" s="50"/>
     </row>
     <row r="183" spans="1:8" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
@@ -10539,12 +10539,12 @@
         <v>600</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G183" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H183" s="45"/>
+      <c r="H183" s="50"/>
     </row>
     <row r="184" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
@@ -10563,12 +10563,12 @@
         <v>600</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G184" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H184" s="45"/>
+      <c r="H184" s="50"/>
     </row>
     <row r="185" spans="1:8" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
@@ -10587,12 +10587,12 @@
         <v>775</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G185" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H185" s="45"/>
+      <c r="H185" s="50"/>
     </row>
     <row r="186" spans="1:8" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
@@ -10611,12 +10611,12 @@
         <v>600</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="G186" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H186" s="45"/>
+      <c r="H186" s="50"/>
     </row>
     <row r="187" spans="1:8" ht="83.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="14" t="s">
@@ -10635,12 +10635,12 @@
         <v>600</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G187" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="H187" s="45"/>
+      <c r="H187" s="50"/>
     </row>
     <row r="188" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" s="24" t="s">
@@ -10661,10 +10661,10 @@
       <c r="F188" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G188" s="33" t="s">
+      <c r="G188" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H188" s="47" t="s">
+      <c r="H188" s="36" t="s">
         <v>647</v>
       </c>
     </row>
@@ -10687,10 +10687,10 @@
       <c r="F189" s="27" t="s">
         <v>635</v>
       </c>
-      <c r="G189" s="34" t="s">
+      <c r="G189" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="H189" s="48" t="s">
+      <c r="H189" s="44" t="s">
         <v>665</v>
       </c>
     </row>
@@ -10711,8 +10711,8 @@
       <c r="F190" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="G190" s="35"/>
-      <c r="H190" s="49"/>
+      <c r="G190" s="38"/>
+      <c r="H190" s="45"/>
     </row>
     <row r="191" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
@@ -10731,8 +10731,8 @@
       <c r="F191" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="G191" s="35"/>
-      <c r="H191" s="49"/>
+      <c r="G191" s="38"/>
+      <c r="H191" s="45"/>
     </row>
     <row r="192" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="11" t="s">
@@ -10751,8 +10751,8 @@
       <c r="F192" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="G192" s="35"/>
-      <c r="H192" s="49"/>
+      <c r="G192" s="38"/>
+      <c r="H192" s="45"/>
     </row>
     <row r="193" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A193" s="11" t="s">
@@ -10771,8 +10771,8 @@
       <c r="F193" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="G193" s="35"/>
-      <c r="H193" s="49"/>
+      <c r="G193" s="38"/>
+      <c r="H193" s="45"/>
     </row>
     <row r="194" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
@@ -10791,8 +10791,8 @@
       <c r="F194" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="G194" s="35"/>
-      <c r="H194" s="49"/>
+      <c r="G194" s="38"/>
+      <c r="H194" s="45"/>
     </row>
     <row r="195" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A195" s="11" t="s">
@@ -10811,8 +10811,8 @@
       <c r="F195" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="G195" s="35"/>
-      <c r="H195" s="49"/>
+      <c r="G195" s="38"/>
+      <c r="H195" s="45"/>
     </row>
     <row r="196" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
@@ -10831,8 +10831,8 @@
       <c r="F196" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="G196" s="35"/>
-      <c r="H196" s="49"/>
+      <c r="G196" s="38"/>
+      <c r="H196" s="45"/>
     </row>
     <row r="197" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
@@ -10851,8 +10851,8 @@
       <c r="F197" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="G197" s="35"/>
-      <c r="H197" s="49"/>
+      <c r="G197" s="38"/>
+      <c r="H197" s="45"/>
     </row>
     <row r="198" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
@@ -10871,8 +10871,8 @@
       <c r="F198" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G198" s="35"/>
-      <c r="H198" s="49"/>
+      <c r="G198" s="38"/>
+      <c r="H198" s="45"/>
     </row>
     <row r="199" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
@@ -10891,8 +10891,8 @@
       <c r="F199" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="G199" s="35"/>
-      <c r="H199" s="49"/>
+      <c r="G199" s="38"/>
+      <c r="H199" s="45"/>
     </row>
     <row r="200" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A200" s="12" t="s">
@@ -10911,8 +10911,8 @@
       <c r="F200" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="G200" s="35"/>
-      <c r="H200" s="49"/>
+      <c r="G200" s="38"/>
+      <c r="H200" s="45"/>
     </row>
     <row r="201" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A201" s="12" t="s">
@@ -10933,8 +10933,8 @@
       <c r="F201" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="G201" s="35"/>
-      <c r="H201" s="49"/>
+      <c r="G201" s="38"/>
+      <c r="H201" s="45"/>
     </row>
     <row r="202" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A202" s="12" t="s">
@@ -10955,8 +10955,8 @@
       <c r="F202" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="G202" s="35"/>
-      <c r="H202" s="49"/>
+      <c r="G202" s="38"/>
+      <c r="H202" s="45"/>
     </row>
     <row r="203" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
@@ -10975,8 +10975,8 @@
       <c r="F203" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="G203" s="35"/>
-      <c r="H203" s="49"/>
+      <c r="G203" s="38"/>
+      <c r="H203" s="45"/>
     </row>
     <row r="204" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
@@ -10997,8 +10997,8 @@
       <c r="F204" s="17" t="s">
         <v>649</v>
       </c>
-      <c r="G204" s="36"/>
-      <c r="H204" s="50"/>
+      <c r="G204" s="39"/>
+      <c r="H204" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8FD231-E70C-48E5-BE72-865E70A36880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DF4495-EE28-4117-8EB6-EC8487D33F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5437,15 +5437,15 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>60；战吼嘲讽吸引敌人仇恨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>；战吼嘲讽吸引敌人仇恨
 【人物装备】尖刺套装（无头盔），皇帝之盾，铁质变种剑
 【所需戒指】普通/</t>
     </r>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DF4495-EE28-4117-8EB6-EC8487D33F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211B3F4C-5D7F-4C2D-885B-6DDE570C6D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4944,333 +4944,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>【修道院介绍】这座修道院建立于独立的卢比尼亚并入帝国的时期。它成为了许多赫拉特教会圣徒的安葬之地。人们相信，他们的灵魂会保护修道院免遭灾祸与不幸……卢比尼亚逐渐与帝国其他地区隔绝。人们忘记了通往修道院的路，但我们拒绝离开这些城墙。当寒冷与饥饿渗入我们的灵魂，而墙外那恐怖的低语淹没了我们的祈祷时，我们想起赫拉特教会不仅象征仁慈——也象征净化的火焰。我们不再祈求庇护。修士长达米安的长袍早已被烟灰票黑，他宣扬了一套新的教义：将染病之人的肉身投入火焰，令其获得救赎。守护灵如今已对我们的呼唤充耳不闻。
-【副本介绍】暮焰修道院为继三元素副本哈特/哈利德/弗拉格纳之后的第四个元素副本，火元素副本，形式与古墓类似。修道院有普通/英雄/传奇三个难度，一共有12位盟军可供选择，盟军通过赫拉特祈祷戒指在不同品质的棺材中召唤，稀有品质的盟友在普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>难度中都是免费召唤，独特品质的盟友在普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>难度中所需的戒指数量分别为：10/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，传奇品质的盟友在普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>难度中所需的戒指数量分别为：30/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>180</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>。总共有4个房间来选择盟友，其中一个在炸弹房间，每个房间都有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF4A86E8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>稀有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>独特</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>三种不同品质的棺材各一个，共三个，每个房间只能选择召唤一位盟友。第一三四房间的盟友都是随机出现，第二房间固定为牧师盟友（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF4A86E8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>阿尔弗雷德</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>萨宾纳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>圣彼得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）。另外，有的房间立有赫拉特女神雕像，触碰可让主动技能满充能，且回满省地图的角色能量。
-【炸弹房】每个难度都有炸弹房，普通难度可用一级炸炸开，英雄难度可用二级炸炸开，传奇难度可用三级炸炸开，另外正如上面所说，炸弹房就是那个位于boss房前面的第四个可选择盟友的房间。</t>
-    </r>
-  </si>
-  <si>
     <t>待测，待测，400</t>
   </si>
   <si>
@@ -5508,6 +5181,333 @@
         <family val="2"/>
       </rPr>
       <t>180</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【修道院介绍】这座修道院建立于独立的卢比尼亚并入帝国的时期。它成为了许多赫拉特教会圣徒的安葬之地。人们相信，他们的灵魂会保护修道院免遭灾祸与不幸……卢比尼亚逐渐与帝国其他地区隔绝。人们忘记了通往修道院的路，但我们拒绝离开这些城墙。当寒冷与饥饿渗入我们的灵魂，而墙外那恐怖的低语淹没了我们的祈祷时，我们想起赫拉特教会不仅象征仁慈——也象征净化的火焰。我们不再祈求庇护。修士长达米安的长袍早已被烟灰票黑，他宣扬了一套新的教义：将染病之人的肉身投入火焰，令其获得救赎。守护灵如今已对我们的呼唤充耳不闻。
+【副本介绍】暮焰修道院为继三元素副本哈特/哈利德/弗拉格纳之后的第四个元素副本，火元素副本，形式与古墓类似。修道院有普通/英雄/传奇三个难度，一共有12位盟军可供选择，盟军通过赫拉特祈祷戒指在不同品质的棺材中召唤，稀有品质的盟友在普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>难度中都是免费召唤，独特品质的盟友在普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>难度中所需的戒指数量分别为：10/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，传奇品质的盟友在普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>难度中所需的戒指数量分别为：30/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>180</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。总共有4个房间来选择盟友，其中一个在炸弹房间，每个房间都有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4A86E8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>稀有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>独特</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>三种不同品质的棺材各一个，共三个，每个房间只能选择召唤一位盟友。第一三四房间的盟友都是随机出现，第二房间固定为牧师盟友（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4A86E8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>阿尔弗雷德</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>萨宾娜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>圣彼得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）。另外，有的房间立有赫拉特女神雕像，触碰可让主动技能满充能，且回满省地图的角色能量。
+【炸弹房】每个难度都有炸弹房，普通难度可用一级炸炸开，英雄难度可用二级炸炸开，传奇难度可用三级炸炸开，另外正如上面所说，炸弹房就是那个位于boss房前面的第四个可选择盟友的房间。</t>
     </r>
   </si>
 </sst>
@@ -9629,13 +9629,13 @@
         <v>288</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -9651,10 +9651,10 @@
         <v>290</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>600</v>
@@ -9673,13 +9673,13 @@
         <v>292</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -9693,13 +9693,13 @@
         <v>293</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -9713,13 +9713,13 @@
         <v>294</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -9735,10 +9735,10 @@
         <v>296</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>813</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>814</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>600</v>
@@ -10159,7 +10159,7 @@
         <v>721</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -10515,7 +10515,7 @@
         <v>600</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G182" s="29" t="s">
         <v>721</v>
@@ -10611,7 +10611,7 @@
         <v>600</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G186" s="29" t="s">
         <v>721</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211B3F4C-5D7F-4C2D-885B-6DDE570C6D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960433D6-524A-4549-9DCF-5885D9082B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3517,142 +3517,6 @@
   </si>
   <si>
     <r>
-      <t>【人物介绍】出身于商人世家，他将全部财富捐给了有需要的人，余生都在受赫拉特恩典祝福的修道院中度过。
-【技能效果】回复友军血量30/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>70</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>0（普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>）
-【人物装备】骑士团棉衣，车把
-【所需戒指】普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>：免费/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>免费</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>免费</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>【人物介绍】他退入卢比尼亚的荒野，通过禁食和鞭笞来苦修肉身。据说，他身上的伤疤多得如同卷轴上的经文。
 【技能效果】自身会每一秒以1/</t>
     </r>
@@ -5508,6 +5372,142 @@
       </rPr>
       <t>）。另外，有的房间立有赫拉特女神雕像，触碰可让主动技能满充能，且回满省地图的角色能量。
 【炸弹房】每个难度都有炸弹房，普通难度可用一级炸炸开，英雄难度可用二级炸炸开，传奇难度可用三级炸炸开，另外正如上面所说，炸弹房就是那个位于boss房前面的第四个可选择盟友的房间。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【人物介绍】出身于商人世家，他将全部财富捐给了有需要的人，余生都在受赫拉特恩典祝福的修道院中度过。
+【技能效果】回复友军血量30/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>140</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>（普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>）
+【人物装备】骑士团棉衣，车把
+【所需戒指】普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：免费/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>免费</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>免费</t>
     </r>
   </si>
 </sst>
@@ -6170,9 +6170,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF351C75"/>
       <color rgb="FFFBBC04"/>
       <color rgb="FF4A86E8"/>
-      <color rgb="FF351C75"/>
       <color rgb="FF0B5394"/>
       <color rgb="FF00B050"/>
       <color rgb="FFFF6D01"/>
@@ -9629,13 +9629,13 @@
         <v>288</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -9651,10 +9651,10 @@
         <v>290</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>600</v>
@@ -9673,13 +9673,13 @@
         <v>292</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -9693,13 +9693,13 @@
         <v>293</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -9713,13 +9713,13 @@
         <v>294</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -9735,10 +9735,10 @@
         <v>296</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>600</v>
@@ -10159,7 +10159,7 @@
         <v>721</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
@@ -10395,7 +10395,7 @@
         <v>600</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>798</v>
+        <v>821</v>
       </c>
       <c r="G177" s="29" t="s">
         <v>721</v>
@@ -10419,7 +10419,7 @@
         <v>600</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G178" s="29" t="s">
         <v>721</v>
@@ -10443,7 +10443,7 @@
         <v>600</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G179" s="29" t="s">
         <v>721</v>
@@ -10467,7 +10467,7 @@
         <v>600</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G180" s="29" t="s">
         <v>721</v>
@@ -10491,7 +10491,7 @@
         <v>600</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G181" s="29" t="s">
         <v>721</v>
@@ -10515,7 +10515,7 @@
         <v>600</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G182" s="29" t="s">
         <v>721</v>
@@ -10539,7 +10539,7 @@
         <v>600</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G183" s="29" t="s">
         <v>721</v>
@@ -10563,7 +10563,7 @@
         <v>600</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G184" s="29" t="s">
         <v>721</v>
@@ -10587,7 +10587,7 @@
         <v>775</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G185" s="29" t="s">
         <v>721</v>
@@ -10611,7 +10611,7 @@
         <v>600</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G186" s="29" t="s">
         <v>721</v>
@@ -10635,7 +10635,7 @@
         <v>600</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G187" s="29" t="s">
         <v>721</v>
@@ -11012,6 +11012,7 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960433D6-524A-4549-9DCF-5885D9082B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD3B1F8-9B38-4D05-94A7-55DCC324B775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>物理伤害</t>
-  </si>
-  <si>
-    <t>元素伤害</t>
   </si>
   <si>
     <t>敌人介绍</t>
@@ -5509,6 +5506,9 @@
       </rPr>
       <t>免费</t>
     </r>
+  </si>
+  <si>
+    <t>固定元素伤害</t>
   </si>
 </sst>
 </file>
@@ -6490,7 +6490,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="40" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -6514,21 +6514,21 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="G2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>6</v>
-      </c>
       <c r="H2" s="31" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -6537,11 +6537,11 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>0</v>
@@ -6550,7 +6550,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -6562,21 +6562,21 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>6</v>
-      </c>
       <c r="H4" s="33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>25</v>
@@ -6587,16 +6587,16 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>11</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>12</v>
       </c>
       <c r="H5" s="32"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2">
         <v>70</v>
@@ -6610,13 +6610,13 @@
       <c r="E6" s="2"/>
       <c r="F6" s="19"/>
       <c r="G6" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="32"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>50</v>
@@ -6630,13 +6630,13 @@
       <c r="E7" s="2"/>
       <c r="F7" s="19"/>
       <c r="G7" s="21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
         <v>100</v>
@@ -6650,13 +6650,13 @@
       <c r="E8" s="2"/>
       <c r="F8" s="19"/>
       <c r="G8" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2">
         <v>500</v>
@@ -6669,16 +6669,16 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>20</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>21</v>
       </c>
       <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B10" s="2">
         <v>90</v>
@@ -6691,16 +6691,16 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2">
         <v>50</v>
@@ -6714,13 +6714,13 @@
       <c r="E11" s="2"/>
       <c r="F11" s="19"/>
       <c r="G11" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2">
         <v>200</v>
@@ -6734,13 +6734,13 @@
       <c r="E12" s="2"/>
       <c r="F12" s="19"/>
       <c r="G12" s="21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2">
         <v>300</v>
@@ -6754,13 +6754,13 @@
       <c r="E13" s="2"/>
       <c r="F13" s="19"/>
       <c r="G13" s="21" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2">
         <v>100</v>
@@ -6771,16 +6771,16 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2">
         <v>90</v>
@@ -6794,13 +6794,13 @@
       <c r="E15" s="2"/>
       <c r="F15" s="19"/>
       <c r="G15" s="21" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2">
         <v>80</v>
@@ -6813,16 +6813,16 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>32</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>33</v>
       </c>
       <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2">
         <v>125</v>
@@ -6836,13 +6836,13 @@
       <c r="E17" s="2"/>
       <c r="F17" s="19"/>
       <c r="G17" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2">
         <v>95</v>
@@ -6855,16 +6855,16 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2">
         <v>90</v>
@@ -6878,13 +6878,13 @@
       <c r="E19" s="2"/>
       <c r="F19" s="19"/>
       <c r="G19" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2">
         <v>70</v>
@@ -6893,20 +6893,20 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H20" s="32"/>
     </row>
     <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A21" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2">
         <v>300</v>
@@ -6920,57 +6920,57 @@
       <c r="E21" s="2"/>
       <c r="F21" s="19"/>
       <c r="G21" s="21" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H21" s="32"/>
     </row>
     <row r="22" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2">
         <v>100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2">
         <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2">
         <v>90</v>
@@ -6983,16 +6983,16 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A25" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2">
         <v>140</v>
@@ -7005,16 +7005,16 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A26" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2">
         <v>200</v>
@@ -7027,16 +7027,16 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H26" s="32"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2">
         <v>300</v>
@@ -7049,16 +7049,16 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2">
         <v>2800</v>
@@ -7067,18 +7067,18 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2">
         <v>1000</v>
@@ -7089,16 +7089,16 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="19" t="s">
         <v>64</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>65</v>
       </c>
       <c r="H29" s="32"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2">
         <v>900</v>
@@ -7111,16 +7111,16 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>67</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>68</v>
       </c>
       <c r="H30" s="32"/>
     </row>
     <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31" s="2">
         <v>760</v>
@@ -7133,16 +7133,16 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="H31" s="32"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="2">
         <v>2000</v>
@@ -7155,38 +7155,38 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H32" s="32"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="19" t="s">
         <v>75</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>76</v>
       </c>
       <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -7198,21 +7198,21 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H34" s="33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B35" s="2">
         <v>50</v>
@@ -7226,15 +7226,15 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="19" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H35" s="47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B36" s="2">
         <v>55</v>
@@ -7248,13 +7248,13 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H36" s="48"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37" s="2">
         <v>50</v>
@@ -7268,13 +7268,13 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="19" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H37" s="48"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B38" s="2">
         <v>65</v>
@@ -7287,16 +7287,16 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H38" s="48"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" s="2">
         <v>175</v>
@@ -7310,13 +7310,13 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="19" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H39" s="48"/>
     </row>
     <row r="40" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B40" s="2">
         <v>10</v>
@@ -7325,20 +7325,20 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H40" s="48"/>
     </row>
     <row r="41" spans="1:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B41" s="2">
         <v>400</v>
@@ -7352,13 +7352,13 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="19" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H41" s="48"/>
     </row>
     <row r="42" spans="1:8" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B42" s="2">
         <v>100</v>
@@ -7372,13 +7372,13 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="19" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H42" s="48"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B43" s="2">
         <v>400</v>
@@ -7391,16 +7391,16 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H43" s="48"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="12" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -7413,16 +7413,16 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H44" s="48"/>
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -7435,16 +7435,16 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H45" s="48"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -7457,16 +7457,16 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H46" s="48"/>
     </row>
     <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2">
         <v>400</v>
@@ -7479,16 +7479,16 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H47" s="48"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B48" s="2">
         <v>600</v>
@@ -7501,38 +7501,38 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H48" s="48"/>
     </row>
     <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A49" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="D49" s="2">
         <v>150</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H49" s="48"/>
     </row>
     <row r="50" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B50" s="2">
         <v>1750</v>
@@ -7545,16 +7545,16 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H50" s="48"/>
     </row>
     <row r="51" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B51" s="2">
         <v>900</v>
@@ -7567,16 +7567,16 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H51" s="48"/>
     </row>
     <row r="52" spans="1:8" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B52" s="2">
         <v>1750</v>
@@ -7589,16 +7589,16 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H52" s="48"/>
     </row>
     <row r="53" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B53" s="2">
         <v>1600</v>
@@ -7611,16 +7611,16 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H53" s="49"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1</v>
@@ -7632,21 +7632,21 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H54" s="33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -7659,18 +7659,18 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H55" s="47" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2">
         <v>90</v>
@@ -7683,16 +7683,16 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H56" s="48"/>
     </row>
     <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2">
         <v>200</v>
@@ -7705,16 +7705,16 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H57" s="48"/>
     </row>
     <row r="58" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B58" s="2">
         <v>180</v>
@@ -7727,16 +7727,16 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H58" s="48"/>
     </row>
     <row r="59" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B59" s="2">
         <v>250</v>
@@ -7749,16 +7749,16 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H59" s="48"/>
     </row>
     <row r="60" spans="1:8" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B60" s="2">
         <v>350</v>
@@ -7771,16 +7771,16 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H60" s="48"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B61" s="2">
         <v>350</v>
@@ -7793,16 +7793,16 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H61" s="48"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B62" s="2">
         <v>300</v>
@@ -7815,16 +7815,16 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H62" s="48"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B63" s="2">
         <v>300</v>
@@ -7837,16 +7837,16 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H63" s="48"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B64" s="2">
         <v>300</v>
@@ -7858,19 +7858,19 @@
         <v>45</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H64" s="48"/>
     </row>
     <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
       <c r="A65" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B65" s="2">
         <v>10000</v>
@@ -7879,20 +7879,20 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H65" s="49"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>1</v>
@@ -7904,21 +7904,21 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H66" s="34" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A67" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B67" s="2">
         <v>335</v>
@@ -7931,18 +7931,18 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A68" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B68" s="2">
         <v>450</v>
@@ -7955,16 +7955,16 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H68" s="48"/>
     </row>
     <row r="69" spans="1:8" ht="81" x14ac:dyDescent="0.45">
       <c r="A69" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B69" s="2">
         <v>550</v>
@@ -7977,16 +7977,16 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H69" s="48"/>
     </row>
     <row r="70" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A70" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B70" s="2">
         <v>1000</v>
@@ -7999,16 +7999,16 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H70" s="48"/>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>1</v>
@@ -8020,21 +8020,21 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G71" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H71" s="35" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B72" s="2">
         <v>60</v>
@@ -8048,13 +8048,13 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H72" s="32"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" s="2">
         <v>70</v>
@@ -8068,13 +8068,13 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H73" s="32"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2">
         <v>30</v>
@@ -8087,16 +8087,16 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H74" s="32"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>1</v>
@@ -8108,21 +8108,21 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="G75" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G75" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H75" s="33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B76" s="2">
         <v>800</v>
@@ -8131,20 +8131,20 @@
         <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G76" s="19" t="s">
         <v>152</v>
-      </c>
-      <c r="G76" s="19" t="s">
-        <v>153</v>
       </c>
       <c r="H76" s="32"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" s="2">
         <v>700</v>
@@ -8156,19 +8156,19 @@
         <v>30</v>
       </c>
       <c r="E77" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="G77" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H77" s="32"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B78" s="2">
         <v>800</v>
@@ -8177,22 +8177,22 @@
         <v>23</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E78" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="F78" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="G78" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H78" s="32"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B79" s="2">
         <v>800</v>
@@ -8205,19 +8205,19 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H79" s="32"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -8227,19 +8227,19 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H80" s="32"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -8249,19 +8249,19 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H81" s="32"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" s="2">
         <v>24</v>
@@ -8271,63 +8271,63 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H82" s="32"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="C83" s="2">
         <v>55</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H83" s="32"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="C84" s="2">
         <v>38</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H84" s="32"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C85" s="2">
         <v>38</v>
@@ -8337,19 +8337,19 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H85" s="32"/>
     </row>
     <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A86" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="C86" s="2">
         <v>60</v>
@@ -8359,16 +8359,16 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H86" s="32"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="14" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -8377,20 +8377,20 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H87" s="32"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>1</v>
@@ -8402,21 +8402,21 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="G88" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G88" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H88" s="34" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B89" s="2">
         <v>25</v>
@@ -8425,20 +8425,20 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H89" s="32"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B90" s="2">
         <v>400</v>
@@ -8452,13 +8452,13 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H90" s="32"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -8472,13 +8472,13 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H91" s="32"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -8492,13 +8492,13 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H92" s="32"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -8512,13 +8512,13 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H93" s="32"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B94" s="2">
         <v>200</v>
@@ -8527,20 +8527,20 @@
         <v>0</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G94" s="19" t="s">
         <v>198</v>
-      </c>
-      <c r="G94" s="19" t="s">
-        <v>199</v>
       </c>
       <c r="H94" s="32"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B95" s="2">
         <v>400</v>
@@ -8554,13 +8554,13 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H95" s="32"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B96" s="2">
         <v>60</v>
@@ -8573,16 +8573,16 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G96" s="19" t="s">
         <v>203</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>204</v>
       </c>
       <c r="H96" s="32"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B97" s="2">
         <v>550</v>
@@ -8596,13 +8596,13 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H97" s="32"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -8611,21 +8611,21 @@
         <v>0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H98" s="32"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -8635,16 +8635,16 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H99" s="32"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B100" s="2">
         <v>150</v>
@@ -8657,16 +8657,16 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G100" s="19" t="s">
         <v>213</v>
-      </c>
-      <c r="G100" s="19" t="s">
-        <v>214</v>
       </c>
       <c r="H100" s="32"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B101" s="2">
         <v>110</v>
@@ -8679,16 +8679,16 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G101" s="19" t="s">
         <v>216</v>
-      </c>
-      <c r="G101" s="19" t="s">
-        <v>217</v>
       </c>
       <c r="H101" s="32"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B102" s="2">
         <v>185</v>
@@ -8701,16 +8701,16 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H102" s="32"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B103" s="2">
         <v>300</v>
@@ -8719,20 +8719,20 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G103" s="19" t="s">
         <v>221</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>222</v>
       </c>
       <c r="H103" s="32"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
@@ -8746,19 +8746,19 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H104" s="32"/>
     </row>
     <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A105" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B105" s="2">
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -8766,16 +8766,16 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H105" s="32"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -8786,19 +8786,19 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H106" s="32"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D107" s="2">
         <v>72</v>
@@ -8806,33 +8806,33 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H107" s="32"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H108" s="32"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B109" s="2">
         <v>300</v>
@@ -8846,13 +8846,13 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H109" s="32"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B110" s="2">
         <v>600</v>
@@ -8866,13 +8866,13 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H110" s="32"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B111" s="2">
         <v>1000</v>
@@ -8886,13 +8886,13 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H111" s="32"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B112" s="2">
         <v>450</v>
@@ -8901,20 +8901,20 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G112" s="19" t="s">
         <v>239</v>
-      </c>
-      <c r="G112" s="19" t="s">
-        <v>240</v>
       </c>
       <c r="H112" s="32"/>
     </row>
     <row r="113" spans="1:8" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B113" s="2">
         <v>2500</v>
@@ -8927,16 +8927,16 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H113" s="32"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B114" s="2">
         <v>9000</v>
@@ -8949,16 +8949,16 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G114" s="19" t="s">
         <v>244</v>
-      </c>
-      <c r="G114" s="19" t="s">
-        <v>245</v>
       </c>
       <c r="H114" s="32"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B115" s="2">
         <v>10500</v>
@@ -8967,20 +8967,20 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G115" s="19" t="s">
         <v>248</v>
-      </c>
-      <c r="G115" s="19" t="s">
-        <v>249</v>
       </c>
       <c r="H115" s="32"/>
     </row>
     <row r="116" spans="1:8" ht="121.5" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -8993,16 +8993,16 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H116" s="32"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -9014,21 +9014,21 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="G117" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G117" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H117" s="35" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -9037,20 +9037,20 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G118" s="19" t="s">
         <v>607</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>608</v>
       </c>
       <c r="H118" s="32"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -9063,16 +9063,16 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H119" s="32"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -9081,20 +9081,20 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H120" s="32"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B121" s="2">
         <v>150</v>
@@ -9107,16 +9107,16 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H121" s="32"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B122" s="2">
         <v>300</v>
@@ -9129,16 +9129,16 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H122" s="32"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -9147,20 +9147,20 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H123" s="32"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -9169,20 +9169,20 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H124" s="32"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -9195,16 +9195,16 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H125" s="32"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -9217,16 +9217,16 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H126" s="32"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -9235,20 +9235,20 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H127" s="32"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="13" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -9261,16 +9261,16 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H128" s="32"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>1</v>
@@ -9282,21 +9282,21 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F129" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F129" s="4" t="s">
+      <c r="G129" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G129" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H129" s="34" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B130" s="2">
         <v>50</v>
@@ -9305,20 +9305,20 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G130" s="19" t="s">
         <v>254</v>
-      </c>
-      <c r="G130" s="19" t="s">
-        <v>255</v>
       </c>
       <c r="H130" s="32"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B131" s="2">
         <v>900</v>
@@ -9332,13 +9332,13 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H131" s="32"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B132" s="2">
         <v>100</v>
@@ -9347,18 +9347,18 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H132" s="32"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B133" s="2">
         <v>45</v>
@@ -9371,36 +9371,36 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G133" s="19" t="s">
         <v>263</v>
-      </c>
-      <c r="G133" s="19" t="s">
-        <v>264</v>
       </c>
       <c r="H133" s="32"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B134" s="2">
         <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H134" s="32"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B135" s="2">
         <v>600</v>
@@ -9409,20 +9409,20 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H135" s="32"/>
     </row>
     <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B136" s="2">
         <v>1500</v>
@@ -9431,20 +9431,20 @@
         <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G136" s="19" t="s">
         <v>269</v>
-      </c>
-      <c r="G136" s="19" t="s">
-        <v>270</v>
       </c>
       <c r="H136" s="32"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
@@ -9456,19 +9456,19 @@
         <v>100</v>
       </c>
       <c r="E137" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="G137" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H137" s="32"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B138" s="2">
         <v>1000</v>
@@ -9481,16 +9481,16 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G138" s="19" t="s">
         <v>275</v>
-      </c>
-      <c r="G138" s="19" t="s">
-        <v>276</v>
       </c>
       <c r="H138" s="32"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B139" s="2">
         <v>120</v>
@@ -9499,20 +9499,20 @@
         <v>13</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="G139" s="19" t="s">
         <v>717</v>
-      </c>
-      <c r="G139" s="19" t="s">
-        <v>718</v>
       </c>
       <c r="H139" s="32"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B140" s="2">
         <v>750</v>
@@ -9525,16 +9525,16 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H140" s="32"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B141" s="2">
         <v>150</v>
@@ -9547,16 +9547,16 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G141" s="19" t="s">
         <v>280</v>
-      </c>
-      <c r="G141" s="19" t="s">
-        <v>281</v>
       </c>
       <c r="H141" s="32"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B142" s="2">
         <v>720</v>
@@ -9569,16 +9569,16 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G142" s="19" t="s">
         <v>283</v>
-      </c>
-      <c r="G142" s="19" t="s">
-        <v>284</v>
       </c>
       <c r="H142" s="32"/>
     </row>
     <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A143" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B143" s="2">
         <v>2000</v>
@@ -9591,16 +9591,16 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H143" s="32"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>1</v>
@@ -9612,149 +9612,149 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F144" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F144" s="4" t="s">
+      <c r="G144" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H144" s="36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H145" s="32"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H146" s="32"/>
     </row>
     <row r="147" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H147" s="32"/>
     </row>
     <row r="148" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H148" s="32"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H149" s="32"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>812</v>
-      </c>
       <c r="D150" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H150" s="32"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -9766,355 +9766,355 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F151" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="G151" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G151" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H151" s="36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="C152" s="2">
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G152" s="19" t="s">
         <v>303</v>
-      </c>
-      <c r="G152" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="H152" s="32"/>
     </row>
     <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="D153" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G153" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H153" s="32"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E154" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F154" s="2" t="s">
-        <v>310</v>
-      </c>
       <c r="G154" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H154" s="32"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D155" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G155" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H155" s="32"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="G156" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H156" s="32"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="19" t="s">
         <v>317</v>
-      </c>
-      <c r="G157" s="19" t="s">
-        <v>318</v>
       </c>
       <c r="H157" s="32"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H158" s="32"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H159" s="32"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H160" s="32"/>
     </row>
     <row r="161" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G161" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H161" s="32"/>
     </row>
     <row r="162" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="D162" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G162" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H162" s="32"/>
     </row>
     <row r="163" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E163" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="F163" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H163" s="32"/>
     </row>
     <row r="164" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="D164" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E164" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>337</v>
-      </c>
       <c r="F164" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H164" s="32"/>
     </row>
     <row r="165" spans="1:8" ht="202.5" x14ac:dyDescent="0.45">
       <c r="A165" s="14" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E165" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="F165" s="2" t="s">
-        <v>684</v>
-      </c>
       <c r="G165" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H165" s="32"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -10126,213 +10126,213 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F166" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F166" s="4" t="s">
+      <c r="G166" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="18" t="s">
-        <v>6</v>
-      </c>
       <c r="H166" s="36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D167" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="E167" s="6" t="s">
         <v>747</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>748</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="E168" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="E168" s="6" t="s">
-        <v>748</v>
-      </c>
       <c r="F168" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G168" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H168" s="50"/>
     </row>
     <row r="169" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G169" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H169" s="50"/>
     </row>
     <row r="170" spans="1:8" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>755</v>
-      </c>
       <c r="D170" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H170" s="50"/>
     </row>
     <row r="171" spans="1:8" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D171" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="E171" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="E171" s="6" t="s">
-        <v>758</v>
-      </c>
       <c r="F171" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H171" s="50"/>
     </row>
     <row r="172" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="E172" s="6" t="s">
         <v>763</v>
       </c>
-      <c r="E172" s="6" t="s">
-        <v>764</v>
-      </c>
       <c r="F172" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H172" s="50"/>
     </row>
     <row r="173" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G173" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H173" s="50"/>
     </row>
     <row r="174" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="E174" s="6" t="s">
         <v>766</v>
       </c>
-      <c r="E174" s="6" t="s">
-        <v>767</v>
-      </c>
       <c r="F174" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G174" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H174" s="50"/>
     </row>
     <row r="175" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -10344,307 +10344,307 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F175" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F175" s="4" t="s">
+      <c r="G175" s="18" t="s">
         <v>5</v>
-      </c>
-      <c r="G175" s="18" t="s">
-        <v>6</v>
       </c>
       <c r="H175" s="50"/>
     </row>
     <row r="176" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H176" s="50"/>
     </row>
     <row r="177" spans="1:8" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G177" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H177" s="50"/>
     </row>
     <row r="178" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G178" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H178" s="50"/>
     </row>
     <row r="179" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G179" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H179" s="50"/>
     </row>
     <row r="180" spans="1:8" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G180" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H180" s="50"/>
     </row>
     <row r="181" spans="1:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C181" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="D181" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="D181" s="2" t="s">
-        <v>782</v>
-      </c>
       <c r="E181" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G181" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H181" s="50"/>
     </row>
     <row r="182" spans="1:8" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G182" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H182" s="50"/>
     </row>
     <row r="183" spans="1:8" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H183" s="50"/>
     </row>
     <row r="184" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G184" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H184" s="50"/>
     </row>
     <row r="185" spans="1:8" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="E185" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="E185" s="7" t="s">
-        <v>775</v>
-      </c>
       <c r="F185" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G185" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H185" s="50"/>
     </row>
     <row r="186" spans="1:8" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G186" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H186" s="50"/>
     </row>
     <row r="187" spans="1:8" ht="83.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="14" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G187" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H187" s="50"/>
     </row>
     <row r="188" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" s="24" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>1</v>
@@ -10655,22 +10655,22 @@
       <c r="D188" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E188" s="25" t="s">
+      <c r="E188" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F188" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F188" s="25" t="s">
+      <c r="G188" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G188" s="30" t="s">
-        <v>6</v>
-      </c>
       <c r="H188" s="36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A189" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B189" s="27">
         <v>120</v>
@@ -10682,21 +10682,21 @@
         <v>40</v>
       </c>
       <c r="E189" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F189" s="27" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G189" s="37" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H189" s="44" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B190" s="2">
         <v>120</v>
@@ -10709,14 +10709,14 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G190" s="38"/>
       <c r="H190" s="45"/>
     </row>
     <row r="191" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B191" s="2">
         <v>200</v>
@@ -10729,14 +10729,14 @@
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G191" s="38"/>
       <c r="H191" s="45"/>
     </row>
     <row r="192" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B192" s="2">
         <v>200</v>
@@ -10749,14 +10749,14 @@
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G192" s="38"/>
       <c r="H192" s="45"/>
     </row>
     <row r="193" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A193" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B193" s="2">
         <v>200</v>
@@ -10769,14 +10769,14 @@
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G193" s="38"/>
       <c r="H193" s="45"/>
     </row>
     <row r="194" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B194" s="2">
         <v>200</v>
@@ -10789,14 +10789,14 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G194" s="38"/>
       <c r="H194" s="45"/>
     </row>
     <row r="195" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A195" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B195" s="2">
         <v>200</v>
@@ -10809,14 +10809,14 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G195" s="38"/>
       <c r="H195" s="45"/>
     </row>
     <row r="196" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B196" s="2">
         <v>200</v>
@@ -10829,14 +10829,14 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G196" s="38"/>
       <c r="H196" s="45"/>
     </row>
     <row r="197" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B197" s="2">
         <v>200</v>
@@ -10849,14 +10849,14 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G197" s="38"/>
       <c r="H197" s="45"/>
     </row>
     <row r="198" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B198" s="2">
         <v>120</v>
@@ -10865,18 +10865,18 @@
         <v>55</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G198" s="38"/>
       <c r="H198" s="45"/>
     </row>
     <row r="199" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B199" s="2">
         <v>200</v>
@@ -10889,14 +10889,14 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G199" s="38"/>
       <c r="H199" s="45"/>
     </row>
     <row r="200" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A200" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B200" s="2">
         <v>250</v>
@@ -10909,14 +10909,14 @@
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G200" s="38"/>
       <c r="H200" s="45"/>
     </row>
     <row r="201" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A201" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B201" s="2">
         <v>200</v>
@@ -10928,17 +10928,17 @@
         <v>64</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G201" s="38"/>
       <c r="H201" s="45"/>
     </row>
     <row r="202" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A202" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B202" s="2">
         <v>250</v>
@@ -10950,17 +10950,17 @@
         <v>60</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G202" s="38"/>
       <c r="H202" s="45"/>
     </row>
     <row r="203" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B203" s="2">
         <v>500</v>
@@ -10969,18 +10969,18 @@
         <v>0</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G203" s="38"/>
       <c r="H203" s="45"/>
     </row>
     <row r="204" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B204" s="17">
         <v>500</v>
@@ -10992,10 +10992,10 @@
         <v>130</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G204" s="39"/>
       <c r="H204" s="46"/>
@@ -11030,3674 +11030,3674 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D62" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D70" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D71" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D72" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D73" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D74" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D75" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D76" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D77" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D79" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D80" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D81" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D82" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D83" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D84" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D92" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D105" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D124" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B142" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D144" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D145" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B163" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B179" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B190" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B192" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B198" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B204" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B206" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D207" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B209" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B211" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="E211" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B213" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D214" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B215" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD3B1F8-9B38-4D05-94A7-55DCC324B775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7855576F-E2C0-4541-9E9B-EA08BE644244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="840">
   <si>
     <t>家里</t>
   </si>
@@ -491,12 +491,6 @@
     <t>鲍勃（NPC）</t>
   </si>
   <si>
-    <t>125-250</t>
-  </si>
-  <si>
-    <t>友方单位，使用狂战士战斧，盟友为你而战</t>
-  </si>
-  <si>
     <t>古人墓穴</t>
   </si>
   <si>
@@ -506,78 +500,33 @@
     <t>20 火</t>
   </si>
   <si>
-    <t>友方单位，使用火弓，盟友为你而战</t>
-  </si>
-  <si>
     <t>坎多（NPC）</t>
   </si>
   <si>
-    <t>60 / 98</t>
-  </si>
-  <si>
     <t>20 冰</t>
   </si>
   <si>
-    <t>友方单位，使用冰剑(60+20冻伤)或风刃(98)，盟友为你而战</t>
-  </si>
-  <si>
     <t>文森特（NPC）</t>
   </si>
   <si>
-    <t>友方单位，使用双手剑，盟友为你而战</t>
-  </si>
-  <si>
     <t>不安的幽灵</t>
   </si>
   <si>
-    <t>300 (传奇)</t>
-  </si>
-  <si>
-    <t>受火属性伤害×2</t>
-  </si>
-  <si>
     <t>骷髅射手</t>
   </si>
   <si>
-    <t>450 (传奇)</t>
-  </si>
-  <si>
     <t>远距离射击</t>
   </si>
   <si>
     <t>骷髅新兵</t>
   </si>
   <si>
-    <t>500 (传奇)</t>
-  </si>
-  <si>
-    <t>武器：骑士剑/轻剑</t>
-  </si>
-  <si>
     <t>骷髅守卫</t>
   </si>
   <si>
-    <t>2500 (传奇)</t>
-  </si>
-  <si>
-    <t>87 / 83 / 52-104</t>
-  </si>
-  <si>
-    <t>武器：幽灵剑87、晕锤83、狂战士斧头52-104，配铁钉盾</t>
-  </si>
-  <si>
     <t>骷髅骑士</t>
   </si>
   <si>
-    <t>3000 (传奇)</t>
-  </si>
-  <si>
-    <t>100 / 128</t>
-  </si>
-  <si>
-    <t>武器：罪恶之刃100、嗜血128</t>
-  </si>
-  <si>
     <t>女妖</t>
   </si>
   <si>
@@ -585,14 +534,6 @@
   </si>
   <si>
     <t>幽灵王冈德伯恩</t>
-  </si>
-  <si>
-    <t>12000 (传奇)</t>
-  </si>
-  <si>
-    <t>普攻250并造成出血4*6；幽灵之刃技能吸血340并造成100伤害；
-召唤骨骼(350HP/21%减伤)3-5只；
-强迫玩家石化(不回血)，自身石化时回复130HP</t>
   </si>
   <si>
     <t>愤怒战士的头</t>
@@ -5509,6 +5450,364 @@
   </si>
   <si>
     <t>固定元素伤害</t>
+  </si>
+  <si>
+    <t>待测，待测，250</t>
+  </si>
+  <si>
+    <t>38，待测，55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100，待测，450 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">120，待测，500 </t>
+  </si>
+  <si>
+    <t>13，待测，24</t>
+  </si>
+  <si>
+    <t>5，待测，50</t>
+  </si>
+  <si>
+    <t>10，待测，125</t>
+  </si>
+  <si>
+    <t>13，待测，38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500，待测，3000 </t>
+  </si>
+  <si>
+    <t>15，待测，100 / 128</t>
+  </si>
+  <si>
+    <t>23，待测，38</t>
+  </si>
+  <si>
+    <t>2，待测，14</t>
+  </si>
+  <si>
+    <t>13，待测，0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120，待测，300 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2500，待测，12000 </t>
+  </si>
+  <si>
+    <t>48，待测，60</t>
+  </si>
+  <si>
+    <t>10，待测，87 / 83 / 52-104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500，待测，2500 </t>
+  </si>
+  <si>
+    <t>普通模式武器：锄头/木棍
+英雄模式武器：
+传奇模式武器：骑士剑/轻剑</t>
+  </si>
+  <si>
+    <t>12/14，待测，64</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">普通模式：普攻15并造成出血5*1；幽灵之刃技能吸血100并造成10伤害；召唤骨骼(50HP/0%减伤)2-3只；强迫玩家石化(不回血)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式：普攻250并造成出血4*6；幽灵之刃技能吸血340并造成100伤害；召唤骨骼(350HP/21%减伤)3-5只；强迫玩家石化(不回血)，自身石化时回复130HP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">普通模式武器：青铜矛
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式武器：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式武器：罪恶之刃，嗜血</t>
+    </r>
+  </si>
+  <si>
+    <t>64，待测，70</t>
+  </si>
+  <si>
+    <t>43，待测，125-250</t>
+  </si>
+  <si>
+    <t>120，待测，800</t>
+  </si>
+  <si>
+    <t>64，64，64</t>
+  </si>
+  <si>
+    <t>120，待测，700</t>
+  </si>
+  <si>
+    <t>30，待测，30</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">友方单位，盟友为你而战
+普通模式武器：猎弓30
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式武器：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式武器：灼热火焰之弓（30+20火焰）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">友方单位，盟友为你而战
+普通模式武器：骑士剑64，黑色铁钉盾
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式武器：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式武器：双刃大砍刀70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">友方单位，盟友为你而战
+普通模式武器：铜战斧43
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式武器：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式武器：狂战士战斧125-250</t>
+    </r>
+  </si>
+  <si>
+    <t>23，23，23</t>
+  </si>
+  <si>
+    <t>19，待测，60 / 98</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">友方单位，盟友为你而战
+普通模式武器：冰霜匕首（19+11冰伤）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式武器：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式武器：冰剑（60+20冰伤）/风刃98</t>
+    </r>
+  </si>
+  <si>
+    <t>78，78，78</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">受火属性伤害×2，衰败伤×1，免疫冰伤
+普通模式：造成2点伤害的同时，自身回血2点
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">普通模式武器：配重锤28，配铁钉盾
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式武器：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式武器：幽灵剑87、晕锤83、狂战士斧头52-104，配铁钉盾</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6490,7 +6789,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="40" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -6514,7 +6813,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>4</v>
@@ -6523,7 +6822,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -6537,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="19" t="s">
@@ -6562,7 +6861,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>4</v>
@@ -6571,7 +6870,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -6678,7 +6977,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>655</v>
+        <v>636</v>
       </c>
       <c r="B10" s="2">
         <v>90</v>
@@ -6694,7 +6993,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>656</v>
+        <v>637</v>
       </c>
       <c r="H10" s="32"/>
     </row>
@@ -6734,7 +7033,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="19"/>
       <c r="G12" s="21" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="H12" s="32"/>
     </row>
@@ -6754,7 +7053,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="19"/>
       <c r="G13" s="21" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="H13" s="32"/>
     </row>
@@ -6774,7 +7073,7 @@
         <v>28</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="H14" s="32"/>
     </row>
@@ -6794,7 +7093,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="19"/>
       <c r="G15" s="21" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="H15" s="32"/>
     </row>
@@ -6858,7 +7157,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
       <c r="H18" s="32"/>
     </row>
@@ -6900,7 +7199,7 @@
         <v>41</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="H20" s="32"/>
     </row>
@@ -6920,7 +7219,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="19"/>
       <c r="G21" s="21" t="s">
-        <v>674</v>
+        <v>655</v>
       </c>
       <c r="H21" s="32"/>
     </row>
@@ -6935,14 +7234,14 @@
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>650</v>
+        <v>631</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="19" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="H22" s="32"/>
     </row>
@@ -6957,7 +7256,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>651</v>
+        <v>632</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="19" t="s">
@@ -6986,7 +7285,7 @@
         <v>51</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="H24" s="32"/>
     </row>
@@ -7008,7 +7307,7 @@
         <v>53</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="H25" s="32"/>
     </row>
@@ -7030,7 +7329,7 @@
         <v>55</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="H26" s="32"/>
     </row>
@@ -7052,7 +7351,7 @@
         <v>57</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="H27" s="32"/>
     </row>
@@ -7067,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>678</v>
+        <v>659</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -7158,7 +7457,7 @@
         <v>72</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>686</v>
+        <v>667</v>
       </c>
       <c r="H32" s="32"/>
     </row>
@@ -7167,10 +7466,10 @@
         <v>73</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -7186,7 +7485,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -7198,7 +7497,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>4</v>
@@ -7207,7 +7506,7 @@
         <v>5</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
@@ -7226,10 +7525,10 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="19" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="H35" s="47" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
@@ -7268,7 +7567,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="19" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
       <c r="H37" s="48"/>
     </row>
@@ -7290,7 +7589,7 @@
         <v>81</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="H38" s="48"/>
     </row>
@@ -7310,7 +7609,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="19" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H39" s="48"/>
     </row>
@@ -7325,14 +7624,14 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="H40" s="48"/>
     </row>
@@ -7352,7 +7651,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="19" t="s">
-        <v>705</v>
+        <v>686</v>
       </c>
       <c r="H41" s="48"/>
     </row>
@@ -7372,7 +7671,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="19" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="H42" s="48"/>
     </row>
@@ -7394,13 +7693,13 @@
         <v>88</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="H43" s="48"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="12" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -7416,13 +7715,13 @@
         <v>90</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="H44" s="48"/>
     </row>
     <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -7438,13 +7737,13 @@
         <v>93</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="H45" s="48"/>
     </row>
     <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -7460,7 +7759,7 @@
         <v>95</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="H46" s="48"/>
     </row>
@@ -7482,7 +7781,7 @@
         <v>97</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="H47" s="48"/>
     </row>
@@ -7523,10 +7822,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="H49" s="48"/>
     </row>
@@ -7548,7 +7847,7 @@
         <v>105</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="H50" s="48"/>
     </row>
@@ -7570,7 +7869,7 @@
         <v>107</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="H51" s="48"/>
     </row>
@@ -7592,7 +7891,7 @@
         <v>109</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="H52" s="48"/>
     </row>
@@ -7614,7 +7913,7 @@
         <v>111</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="H53" s="49"/>
     </row>
@@ -7632,7 +7931,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>4</v>
@@ -7641,12 +7940,12 @@
         <v>5</v>
       </c>
       <c r="H54" s="33" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -7662,10 +7961,10 @@
         <v>114</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="H55" s="47" t="s">
-        <v>711</v>
+        <v>692</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -7686,7 +7985,7 @@
         <v>116</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="H56" s="48"/>
     </row>
@@ -7708,7 +8007,7 @@
         <v>118</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="H57" s="48"/>
     </row>
@@ -7730,7 +8029,7 @@
         <v>114</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="H58" s="48"/>
     </row>
@@ -7752,7 +8051,7 @@
         <v>121</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="H59" s="48"/>
     </row>
@@ -7774,7 +8073,7 @@
         <v>123</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="H60" s="48"/>
     </row>
@@ -7796,7 +8095,7 @@
         <v>125</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="H61" s="48"/>
     </row>
@@ -7818,7 +8117,7 @@
         <v>127</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="H62" s="48"/>
     </row>
@@ -7840,7 +8139,7 @@
         <v>129</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="H63" s="48"/>
     </row>
@@ -7858,13 +8157,13 @@
         <v>45</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="H64" s="48"/>
     </row>
@@ -7879,14 +8178,14 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>649</v>
+        <v>630</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>652</v>
+        <v>633</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>692</v>
+        <v>673</v>
       </c>
       <c r="H65" s="49"/>
     </row>
@@ -7904,7 +8203,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>4</v>
@@ -7913,7 +8212,7 @@
         <v>5</v>
       </c>
       <c r="H66" s="34" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
@@ -7931,13 +8230,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>661</v>
+        <v>642</v>
       </c>
       <c r="G67" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>647</v>
+        <v>628</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
@@ -7955,7 +8254,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>660</v>
+        <v>641</v>
       </c>
       <c r="G68" s="19" t="s">
         <v>136</v>
@@ -7977,7 +8276,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>659</v>
+        <v>640</v>
       </c>
       <c r="G69" s="19" t="s">
         <v>136</v>
@@ -7999,7 +8298,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>658</v>
+        <v>639</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>136</v>
@@ -8020,7 +8319,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>4</v>
@@ -8029,7 +8328,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -8108,7 +8407,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>4</v>
@@ -8117,258 +8416,254 @@
         <v>5</v>
       </c>
       <c r="H75" s="33" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A76" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B76" s="2">
-        <v>800</v>
-      </c>
-      <c r="C76" s="2">
-        <v>64</v>
+      <c r="B76" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>828</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>150</v>
+        <v>826</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="G76" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H76" s="32"/>
+    </row>
+    <row r="77" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A77" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G76" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H76" s="32"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A77" s="11" t="s">
+      <c r="B77" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H77" s="32"/>
+    </row>
+    <row r="78" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A78" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B77" s="2">
-        <v>700</v>
-      </c>
-      <c r="C77" s="2">
-        <v>23</v>
-      </c>
-      <c r="D77" s="2">
-        <v>30</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="B78" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="G78" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="H78" s="32"/>
+    </row>
+    <row r="79" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="A79" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="G77" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H77" s="32"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A78" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B78" s="2">
-        <v>800</v>
-      </c>
-      <c r="C78" s="2">
-        <v>23</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G78" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H78" s="32"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A79" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B79" s="2">
-        <v>800</v>
-      </c>
-      <c r="C79" s="2">
-        <v>78</v>
-      </c>
-      <c r="D79" s="2">
-        <v>70</v>
+      <c r="B79" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>825</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>161</v>
+        <v>832</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H79" s="32"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A80" s="11" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C80" s="2">
-        <v>0</v>
-      </c>
-      <c r="D80" s="2">
-        <v>14</v>
+        <v>816</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>814</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>164</v>
+        <v>838</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H80" s="32"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C81" s="2">
-        <v>0</v>
-      </c>
-      <c r="D81" s="2">
-        <v>50</v>
+        <v>805</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>808</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H81" s="32"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C82" s="2">
-        <v>24</v>
-      </c>
-      <c r="D82" s="2">
-        <v>64</v>
+        <v>806</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>822</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>170</v>
+        <v>821</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H82" s="32"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A83" s="15" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="2">
-        <v>55</v>
+        <v>820</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>804</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>173</v>
+        <v>819</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>174</v>
+        <v>839</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H83" s="32"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A84" s="15" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C84" s="2">
-        <v>38</v>
+        <v>811</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>813</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>177</v>
+        <v>812</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>178</v>
+        <v>824</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H84" s="32"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="15" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C85" s="2">
-        <v>38</v>
-      </c>
-      <c r="D85" s="2">
-        <v>125</v>
+        <v>811</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H85" s="32"/>
     </row>
-    <row r="86" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A86" s="14" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C86" s="2">
-        <v>60</v>
-      </c>
-      <c r="D86" s="2">
-        <v>250</v>
+        <v>817</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>803</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>183</v>
+        <v>823</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H86" s="32"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="14" t="s">
-        <v>657</v>
+        <v>638</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -8377,20 +8672,20 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H87" s="32"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>1</v>
@@ -8402,7 +8697,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>4</v>
@@ -8411,12 +8706,12 @@
         <v>5</v>
       </c>
       <c r="H88" s="34" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="11" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B89" s="2">
         <v>25</v>
@@ -8425,20 +8720,20 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="H89" s="32"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="11" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="B90" s="2">
         <v>400</v>
@@ -8452,13 +8747,13 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="19" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="H90" s="32"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="11" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="B91" s="2">
         <v>400</v>
@@ -8472,13 +8767,13 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="19" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="H91" s="32"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="11" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="B92" s="2">
         <v>400</v>
@@ -8492,13 +8787,13 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="19" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="H92" s="32"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="11" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B93" s="2">
         <v>400</v>
@@ -8512,13 +8807,13 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="19" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="H93" s="32"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="11" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="B94" s="2">
         <v>200</v>
@@ -8527,20 +8822,20 @@
         <v>0</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="H94" s="32"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="11" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="B95" s="2">
         <v>400</v>
@@ -8554,13 +8849,13 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="19" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="H95" s="32"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="11" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="B96" s="2">
         <v>60</v>
@@ -8573,16 +8868,16 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" s="2" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="H96" s="32"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="B97" s="2">
         <v>550</v>
@@ -8596,13 +8891,13 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="19" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="H97" s="32"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
-        <v>662</v>
+        <v>643</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -8611,21 +8906,21 @@
         <v>0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="19" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H98" s="32"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -8635,16 +8930,16 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H99" s="32"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="11" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B100" s="2">
         <v>150</v>
@@ -8657,16 +8952,16 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="H100" s="32"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="11" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="B101" s="2">
         <v>110</v>
@@ -8679,16 +8974,16 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="H101" s="32"/>
     </row>
     <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="11" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B102" s="2">
         <v>185</v>
@@ -8701,16 +8996,16 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="H102" s="32"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="B103" s="2">
         <v>300</v>
@@ -8719,20 +9014,20 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="H103" s="32"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="12" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
@@ -8746,19 +9041,19 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="19" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="H104" s="32"/>
     </row>
     <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A105" s="11" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B105" s="2">
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -8766,16 +9061,16 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="H105" s="32"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="11" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -8786,19 +9081,19 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="H106" s="32"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="11" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="D107" s="2">
         <v>72</v>
@@ -8806,33 +9101,33 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="19" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="H107" s="32"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="11" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="19" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="H108" s="32"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="B109" s="2">
         <v>300</v>
@@ -8846,13 +9141,13 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="19" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="H109" s="32"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="B110" s="2">
         <v>600</v>
@@ -8866,13 +9161,13 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="19" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="H110" s="32"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="B111" s="2">
         <v>1000</v>
@@ -8886,13 +9181,13 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="19" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="H111" s="32"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="B112" s="2">
         <v>450</v>
@@ -8901,20 +9196,20 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="H112" s="32"/>
     </row>
     <row r="113" spans="1:8" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="B113" s="2">
         <v>2500</v>
@@ -8927,16 +9222,16 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>688</v>
+        <v>669</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="H113" s="32"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B114" s="2">
         <v>9000</v>
@@ -8949,16 +9244,16 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="H114" s="32"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B115" s="2">
         <v>10500</v>
@@ -8967,20 +9262,20 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="H115" s="32"/>
     </row>
     <row r="116" spans="1:8" ht="121.5" x14ac:dyDescent="0.45">
       <c r="A116" s="14" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -8993,16 +9288,16 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="H116" s="32"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -9014,7 +9309,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>4</v>
@@ -9023,12 +9318,12 @@
         <v>5</v>
       </c>
       <c r="H117" s="35" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="11" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -9037,20 +9332,20 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H118" s="32"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="11" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -9063,16 +9358,16 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>608</v>
+        <v>589</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H119" s="32"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="11" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -9081,20 +9376,20 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H120" s="32"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="11" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="B121" s="2">
         <v>150</v>
@@ -9107,16 +9402,16 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>611</v>
+        <v>592</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H121" s="32"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="11" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="B122" s="2">
         <v>300</v>
@@ -9129,16 +9424,16 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>611</v>
+        <v>592</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H122" s="32"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="11" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -9147,20 +9442,20 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H123" s="32"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
-        <v>623</v>
+        <v>604</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -9169,20 +9464,20 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H124" s="32"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -9195,16 +9490,16 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>610</v>
+        <v>591</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H125" s="32"/>
     </row>
     <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -9217,16 +9512,16 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H126" s="32"/>
     </row>
     <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -9235,20 +9530,20 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H127" s="32"/>
     </row>
     <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A128" s="13" t="s">
-        <v>626</v>
+        <v>607</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -9261,16 +9556,16 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>653</v>
+        <v>634</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="H128" s="32"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>1</v>
@@ -9282,7 +9577,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>4</v>
@@ -9291,12 +9586,12 @@
         <v>5</v>
       </c>
       <c r="H129" s="34" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="11" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B130" s="2">
         <v>50</v>
@@ -9305,14 +9600,14 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="H130" s="32"/>
     </row>
@@ -9338,7 +9633,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B132" s="2">
         <v>100</v>
@@ -9347,18 +9642,18 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="19" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="H132" s="32"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="11" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="B133" s="2">
         <v>45</v>
@@ -9371,36 +9666,36 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="H133" s="32"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="B134" s="2">
         <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="19" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="H134" s="32"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="B135" s="2">
         <v>600</v>
@@ -9409,20 +9704,20 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="H135" s="32"/>
     </row>
     <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="11" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="B136" s="2">
         <v>1500</v>
@@ -9431,20 +9726,20 @@
         <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="H136" s="32"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
@@ -9456,19 +9751,19 @@
         <v>100</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="G137" s="19" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="H137" s="32"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="B138" s="2">
         <v>1000</v>
@@ -9481,16 +9776,16 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="H138" s="32"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="B139" s="2">
         <v>120</v>
@@ -9499,20 +9794,20 @@
         <v>13</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="H139" s="32"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="B140" s="2">
         <v>750</v>
@@ -9528,13 +9823,13 @@
         <v>69</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="H140" s="32"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="B141" s="2">
         <v>150</v>
@@ -9547,16 +9842,16 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="H141" s="32"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B142" s="2">
         <v>720</v>
@@ -9569,16 +9864,16 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="G142" s="19" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="H142" s="32"/>
     </row>
     <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A143" s="14" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="B143" s="2">
         <v>2000</v>
@@ -9591,16 +9886,16 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="H143" s="32"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>1</v>
@@ -9612,7 +9907,7 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>4</v>
@@ -9621,140 +9916,140 @@
         <v>5</v>
       </c>
       <c r="H144" s="36" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="11" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H145" s="32"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="11" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H146" s="32"/>
     </row>
     <row r="147" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="11" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="19" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H147" s="32"/>
     </row>
     <row r="148" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="11" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="19" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H148" s="32"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="11" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H149" s="32"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="11" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H150" s="32"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -9766,7 +10061,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>4</v>
@@ -9775,346 +10070,346 @@
         <v>5</v>
       </c>
       <c r="H151" s="36" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="11" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C152" s="2">
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="G152" s="19" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="H152" s="32"/>
     </row>
     <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
-        <v>679</v>
+        <v>660</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="G153" s="19" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H153" s="32"/>
     </row>
     <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="G154" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H154" s="32"/>
     </row>
     <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="G155" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H155" s="32"/>
     </row>
     <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="G156" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H156" s="32"/>
     </row>
     <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="G157" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H157" s="32"/>
     </row>
     <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H158" s="32"/>
     </row>
     <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H159" s="32"/>
     </row>
     <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H160" s="32"/>
     </row>
     <row r="161" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C161" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F161" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="G161" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H161" s="32"/>
     </row>
     <row r="162" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E162" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F162" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="G162" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H162" s="32"/>
     </row>
     <row r="163" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="H163" s="32"/>
     </row>
     <row r="164" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="14" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>685</v>
+        <v>666</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H164" s="32"/>
     </row>
     <row r="165" spans="1:8" ht="202.5" x14ac:dyDescent="0.45">
       <c r="A165" s="14" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>665</v>
+        <v>646</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>670</v>
+        <v>651</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="G165" s="19" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H165" s="32"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -10126,7 +10421,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>4</v>
@@ -10135,204 +10430,204 @@
         <v>5</v>
       </c>
       <c r="H166" s="36" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
-        <v>725</v>
+        <v>706</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="G168" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H168" s="50"/>
     </row>
     <row r="169" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="G169" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H169" s="50"/>
     </row>
     <row r="170" spans="1:8" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>792</v>
+        <v>773</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H170" s="50"/>
     </row>
     <row r="171" spans="1:8" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H171" s="50"/>
     </row>
     <row r="172" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H172" s="50"/>
     </row>
     <row r="173" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>770</v>
+        <v>751</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="G173" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H173" s="50"/>
     </row>
     <row r="174" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>765</v>
+        <v>746</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>766</v>
+        <v>747</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="G174" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H174" s="50"/>
     </row>
     <row r="175" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -10344,7 +10639,7 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>4</v>
@@ -10356,295 +10651,295 @@
     </row>
     <row r="176" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H176" s="50"/>
     </row>
     <row r="177" spans="1:8" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="G177" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H177" s="50"/>
     </row>
     <row r="178" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="G178" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H178" s="50"/>
     </row>
     <row r="179" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="G179" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H179" s="50"/>
     </row>
     <row r="180" spans="1:8" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="G180" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H180" s="50"/>
     </row>
     <row r="181" spans="1:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="D181" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F181" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="E181" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>800</v>
-      </c>
       <c r="G181" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H181" s="50"/>
     </row>
     <row r="182" spans="1:8" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="G182" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H182" s="50"/>
     </row>
     <row r="183" spans="1:8" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H183" s="50"/>
     </row>
     <row r="184" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="G184" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H184" s="50"/>
     </row>
     <row r="185" spans="1:8" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="G185" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H185" s="50"/>
     </row>
     <row r="186" spans="1:8" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="G186" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H186" s="50"/>
     </row>
     <row r="187" spans="1:8" ht="83.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A187" s="14" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="G187" s="29" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="H187" s="50"/>
     </row>
     <row r="188" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" s="24" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>1</v>
@@ -10656,7 +10951,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>4</v>
@@ -10665,12 +10960,12 @@
         <v>5</v>
       </c>
       <c r="H188" s="36" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A189" s="26" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B189" s="27">
         <v>120</v>
@@ -10682,21 +10977,21 @@
         <v>40</v>
       </c>
       <c r="E189" s="28" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F189" s="27" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="G189" s="37" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="H189" s="44" t="s">
-        <v>664</v>
+        <v>645</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="11" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="B190" s="2">
         <v>120</v>
@@ -10709,14 +11004,14 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2" t="s">
-        <v>635</v>
+        <v>616</v>
       </c>
       <c r="G190" s="38"/>
       <c r="H190" s="45"/>
     </row>
     <row r="191" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B191" s="2">
         <v>200</v>
@@ -10729,14 +11024,14 @@
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2" t="s">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="G191" s="38"/>
       <c r="H191" s="45"/>
     </row>
     <row r="192" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="11" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B192" s="2">
         <v>200</v>
@@ -10749,14 +11044,14 @@
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="G192" s="38"/>
       <c r="H192" s="45"/>
     </row>
     <row r="193" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A193" s="11" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B193" s="2">
         <v>200</v>
@@ -10769,14 +11064,14 @@
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="G193" s="38"/>
       <c r="H193" s="45"/>
     </row>
     <row r="194" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="B194" s="2">
         <v>200</v>
@@ -10789,14 +11084,14 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="G194" s="38"/>
       <c r="H194" s="45"/>
     </row>
     <row r="195" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A195" s="11" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="B195" s="2">
         <v>200</v>
@@ -10809,14 +11104,14 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2" t="s">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="G195" s="38"/>
       <c r="H195" s="45"/>
     </row>
     <row r="196" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="B196" s="2">
         <v>200</v>
@@ -10829,14 +11124,14 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="G196" s="38"/>
       <c r="H196" s="45"/>
     </row>
     <row r="197" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B197" s="2">
         <v>200</v>
@@ -10849,14 +11144,14 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="G197" s="38"/>
       <c r="H197" s="45"/>
     </row>
-    <row r="198" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B198" s="2">
         <v>120</v>
@@ -10865,18 +11160,18 @@
         <v>55</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="2" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="G198" s="38"/>
       <c r="H198" s="45"/>
     </row>
     <row r="199" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="B199" s="2">
         <v>200</v>
@@ -10889,14 +11184,14 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="2" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="G199" s="38"/>
       <c r="H199" s="45"/>
     </row>
     <row r="200" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A200" s="12" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="B200" s="2">
         <v>250</v>
@@ -10909,14 +11204,14 @@
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2" t="s">
-        <v>643</v>
+        <v>624</v>
       </c>
       <c r="G200" s="38"/>
       <c r="H200" s="45"/>
     </row>
     <row r="201" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A201" s="12" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="B201" s="2">
         <v>200</v>
@@ -10928,17 +11223,17 @@
         <v>64</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>644</v>
+        <v>625</v>
       </c>
       <c r="G201" s="38"/>
       <c r="H201" s="45"/>
     </row>
     <row r="202" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A202" s="12" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="B202" s="2">
         <v>250</v>
@@ -10950,17 +11245,17 @@
         <v>60</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>645</v>
+        <v>626</v>
       </c>
       <c r="G202" s="38"/>
       <c r="H202" s="45"/>
     </row>
     <row r="203" spans="1:8" ht="27" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="B203" s="2">
         <v>500</v>
@@ -10969,18 +11264,18 @@
         <v>0</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" s="2" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="G203" s="38"/>
       <c r="H203" s="45"/>
     </row>
     <row r="204" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="B204" s="17">
         <v>500</v>
@@ -10992,10 +11287,10 @@
         <v>130</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>648</v>
+        <v>629</v>
       </c>
       <c r="G204" s="39"/>
       <c r="H204" s="46"/>
@@ -11030,24 +11325,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -11056,15 +11351,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -11073,32 +11368,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>21</v>
@@ -11107,7 +11402,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
@@ -11115,7 +11410,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>25</v>
@@ -11124,15 +11419,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -11141,15 +11436,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -11158,7 +11453,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
@@ -11166,7 +11461,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -11175,15 +11470,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
@@ -11192,7 +11487,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>41</v>
@@ -11200,7 +11495,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
@@ -11209,7 +11504,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
@@ -11217,7 +11512,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>50</v>
@@ -11226,15 +11521,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
@@ -11243,15 +11538,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>52</v>
@@ -11260,7 +11555,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>53</v>
@@ -11268,7 +11563,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>54</v>
@@ -11277,15 +11572,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>56</v>
@@ -11294,15 +11589,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>56</v>
@@ -11311,7 +11606,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>57</v>
@@ -11319,7 +11614,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>60</v>
@@ -11328,15 +11623,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>65</v>
@@ -11345,15 +11640,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>65</v>
@@ -11362,7 +11657,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>66</v>
@@ -11370,7 +11665,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>68</v>
@@ -11379,15 +11674,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>68</v>
@@ -11396,7 +11691,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>69</v>
@@ -11404,7 +11699,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>71</v>
@@ -11413,15 +11708,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>71</v>
@@ -11438,7 +11733,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>76</v>
@@ -11447,15 +11742,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>79</v>
@@ -11464,15 +11759,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>82</v>
@@ -11481,15 +11776,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>85</v>
@@ -11498,15 +11793,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>87</v>
@@ -11515,15 +11810,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>89</v>
@@ -11532,15 +11827,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>89</v>
@@ -11557,7 +11852,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>89</v>
@@ -11566,7 +11861,7 @@
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>91</v>
@@ -11574,7 +11869,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
@@ -11583,15 +11878,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>92</v>
@@ -11600,7 +11895,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>93</v>
@@ -11608,7 +11903,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>94</v>
@@ -11617,15 +11912,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>94</v>
@@ -11634,7 +11929,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>95</v>
@@ -11642,7 +11937,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>96</v>
@@ -11651,15 +11946,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>96</v>
@@ -11668,7 +11963,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>97</v>
@@ -11676,7 +11971,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -11685,15 +11980,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>100</v>
@@ -11702,7 +11997,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>102</v>
@@ -11710,7 +12005,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>100</v>
@@ -11719,7 +12014,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>103</v>
@@ -11727,7 +12022,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>104</v>
@@ -11736,15 +12031,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>104</v>
@@ -11753,7 +12048,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>105</v>
@@ -11761,7 +12056,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -11770,15 +12065,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>106</v>
@@ -11787,15 +12082,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>108</v>
@@ -11804,15 +12099,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>108</v>
@@ -11821,15 +12116,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>110</v>
@@ -11838,15 +12133,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>110</v>
@@ -11855,15 +12150,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>110</v>
@@ -11872,7 +12167,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>111</v>
@@ -11880,7 +12175,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>113</v>
@@ -11889,15 +12184,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>115</v>
@@ -11906,7 +12201,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>116</v>
@@ -11914,7 +12209,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>117</v>
@@ -11931,7 +12226,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>120</v>
@@ -11940,7 +12235,7 @@
         <v>4</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>121</v>
@@ -11948,7 +12243,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>122</v>
@@ -11957,15 +12252,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>124</v>
@@ -11974,15 +12269,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>126</v>
@@ -11991,15 +12286,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>128</v>
@@ -12008,15 +12303,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>128</v>
@@ -12025,7 +12320,7 @@
         <v>4</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>129</v>
@@ -12033,7 +12328,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>130</v>
@@ -12042,15 +12337,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>130</v>
@@ -12059,7 +12354,7 @@
         <v>4</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>131</v>
@@ -12067,24 +12362,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>134</v>
@@ -12093,15 +12388,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>134</v>
@@ -12110,7 +12405,7 @@
         <v>4</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>135</v>
@@ -12118,7 +12413,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>137</v>
@@ -12127,7 +12422,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>138</v>
@@ -12135,7 +12430,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>139</v>
@@ -12144,15 +12439,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>139</v>
@@ -12161,7 +12456,7 @@
         <v>4</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>140</v>
@@ -12169,7 +12464,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>141</v>
@@ -12178,15 +12473,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>141</v>
@@ -12195,7 +12490,7 @@
         <v>4</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>142</v>
@@ -12203,874 +12498,874 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>60</v>
@@ -13079,245 +13374,245 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>69</v>
@@ -13325,1379 +13620,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>540</v>
+        <v>521</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>541</v>
+        <v>522</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>556</v>
+        <v>537</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>558</v>
+        <v>539</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>564</v>
+        <v>545</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7855576F-E2C0-4541-9E9B-EA08BE644244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA310C-C8CD-4CF1-8A81-D87B9744F811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5452,9 +5452,6 @@
     <t>固定元素伤害</t>
   </si>
   <si>
-    <t>待测，待测，250</t>
-  </si>
-  <si>
     <t>38，待测，55</t>
   </si>
   <si>
@@ -5808,6 +5805,9 @@
       </rPr>
       <t>传奇模式武器：幽灵剑87、晕锤83、狂战士斧头52-104，配铁钉盾</t>
     </r>
+  </si>
+  <si>
+    <t>15，待测，250</t>
   </si>
 </sst>
 </file>
@@ -8424,17 +8424,17 @@
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>828</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
@@ -8446,17 +8446,17 @@
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>830</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
@@ -8468,17 +8468,17 @@
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
@@ -8490,17 +8490,17 @@
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
@@ -8512,17 +8512,17 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
@@ -8534,13 +8534,13 @@
         <v>598</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>742</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
@@ -8556,17 +8556,17 @@
         <v>599</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>807</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
@@ -8578,17 +8578,17 @@
         <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
@@ -8600,17 +8600,17 @@
         <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>812</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
@@ -8622,13 +8622,13 @@
         <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -8644,17 +8644,17 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>818</v>
-      </c>
       <c r="D86" s="2" t="s">
-        <v>803</v>
+        <v>839</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA310C-C8CD-4CF1-8A81-D87B9744F811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00BC5CF-5919-44D0-93D9-330EE0B6A84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5503,22 +5503,49 @@
     <t xml:space="preserve">500，待测，2500 </t>
   </si>
   <si>
-    <t>普通模式武器：锄头/木棍
-英雄模式武器：
-传奇模式武器：骑士剑/轻剑</t>
-  </si>
-  <si>
     <t>12/14，待测，64</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">普通模式：普攻15并造成出血5*1；幽灵之刃技能吸血100并造成10伤害；召唤骨骼(50HP/0%减伤)2-3只；强迫玩家石化(不回血)
+    <t>64，待测，70</t>
+  </si>
+  <si>
+    <t>43，待测，125-250</t>
+  </si>
+  <si>
+    <t>120，待测，800</t>
+  </si>
+  <si>
+    <t>64，64，64</t>
+  </si>
+  <si>
+    <t>120，待测，700</t>
+  </si>
+  <si>
+    <t>30，待测，30</t>
+  </si>
+  <si>
+    <t>23，23，23</t>
+  </si>
+  <si>
+    <t>19，待测，60 / 98</t>
+  </si>
+  <si>
+    <t>78，78，78</t>
+  </si>
+  <si>
+    <t>15，待测，250</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【特性】友方单位，盟友为你而战
+【武器介绍】
+普通模式：铜战斧43
 </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFBBC04"/>
+        <color rgb="FFFFC000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -5540,12 +5567,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式：普攻250并造成出血4*6；幽灵之刃技能吸血340并造成100伤害；召唤骨骼(350HP/21%减伤)3-5只；强迫玩家石化(不回血)，自身石化时回复130HP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">普通模式武器：青铜矛
+      <t>传奇模式：狂战士战斧125-250</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【特性】友方单位，盟友为你而战
+【武器介绍】
+普通模式：猎弓30
 </t>
     </r>
     <r>
@@ -5555,7 +5584,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>英雄模式武器：</t>
+      <t>英雄模式：</t>
     </r>
     <r>
       <rPr>
@@ -5573,41 +5602,24 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式武器：罪恶之刃，嗜血</t>
-    </r>
-  </si>
-  <si>
-    <t>64，待测，70</t>
-  </si>
-  <si>
-    <t>43，待测，125-250</t>
-  </si>
-  <si>
-    <t>120，待测，800</t>
-  </si>
-  <si>
-    <t>64，64，64</t>
-  </si>
-  <si>
-    <t>120，待测，700</t>
-  </si>
-  <si>
-    <t>30，待测，30</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">友方单位，盟友为你而战
-普通模式武器：猎弓30
+      <t>传奇模式：灼热火焰之弓（30+20火焰）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【特性】友方单位，盟友为你而战
+【武器介绍】
+普通模式：冰霜匕首（19+11冰伤）
 </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFBBC04"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄模式武器：</t>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式;</t>
     </r>
     <r>
       <rPr>
@@ -5625,13 +5637,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式武器：灼热火焰之弓（30+20火焰）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">友方单位，盟友为你而战
-普通模式武器：骑士剑64，黑色铁钉盾
+      <t>传奇模式；冰剑（60+20冰伤）/风刃98</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【特性】友方单位，盟友为你而战
+【武器介绍】
+普通模式：骑士剑64，黑色铁钉盾
 </t>
     </r>
     <r>
@@ -5641,7 +5654,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>英雄模式武器：</t>
+      <t>英雄模式：</t>
     </r>
     <r>
       <rPr>
@@ -5659,13 +5672,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式武器：双刃大砍刀70</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">友方单位，盟友为你而战
-普通模式武器：铜战斧43
+      <t>传奇模式：双刃大砍刀70</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【特性】受火属性伤害×2，衰败伤×1，免疫冰伤
+【吸血】
+普通模式：造成2点伤害的同时，自身回血2点
 </t>
     </r>
     <r>
@@ -5675,7 +5689,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>英雄模式武器：</t>
+      <t>英雄模式：</t>
     </r>
     <r>
       <rPr>
@@ -5693,29 +5707,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式武器：狂战士战斧125-250</t>
-    </r>
-  </si>
-  <si>
-    <t>23，23，23</t>
-  </si>
-  <si>
-    <t>19，待测，60 / 98</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">友方单位，盟友为你而战
-普通模式武器：冰霜匕首（19+11冰伤）
+      <t>传奇模式：</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【武器介绍】
+普通模式：锄头/木棍
 </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄模式武器：</t>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
     </r>
     <r>
       <rPr>
@@ -5733,16 +5741,13 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式武器：冰剑（60+20冰伤）/风刃98</t>
-    </r>
-  </si>
-  <si>
-    <t>78，78，78</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">受火属性伤害×2，衰败伤×1，免疫冰伤
-普通模式：造成2点伤害的同时，自身回血2点
+      <t>传奇模式：骑士剑/轻剑</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【武器介绍】
+普通模式：配重锤28，配铁钉盾
 </t>
     </r>
     <r>
@@ -5770,22 +5775,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式：</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">普通模式武器：配重锤28，配铁钉盾
+      <t>传奇模式：幽灵剑87、晕锤83、狂战士斧头52-104，配铁钉盾</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【武器介绍】
+普通模式：青铜矛
 </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄模式武器：</t>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
     </r>
     <r>
       <rPr>
@@ -5803,11 +5809,156 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>传奇模式武器：幽灵剑87、晕锤83、狂战士斧头52-104，配铁钉盾</t>
-    </r>
-  </si>
-  <si>
-    <t>15，待测，250</t>
+      <t>传奇模式：罪恶之刃，嗜血</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">【普通攻击】
+普通模式：普攻15并造成出血5*1
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式：普攻250并造成出血4*6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+【吸血】
+普通模式：幽灵之刃技能吸血100并造成10伤害
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">传奇模式：幽灵之刃技能吸血340并造成100伤害
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【骷髅召唤】
+普通模式：召唤骨骼(50HP/0%减伤)2-3只
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式：召唤骨骼(350HP/21%减伤)3-5只</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+【禁疗】
+普通模式：强迫玩家石化(不回血)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFBBC04"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄模式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇模式：强迫玩家石化(不回血)，自身石化时回复130HP</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8419,95 +8570,95 @@
         <v>627</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A76" s="11" t="s">
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
     </row>
-    <row r="77" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A77" s="11" t="s">
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
     </row>
-    <row r="78" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A78" s="11" t="s">
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
     </row>
-    <row r="79" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A79" s="11" t="s">
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
     </row>
-    <row r="80" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A80" s="11" t="s">
         <v>156</v>
       </c>
@@ -8522,7 +8673,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
@@ -8551,7 +8702,7 @@
       </c>
       <c r="H81" s="32"/>
     </row>
-    <row r="82" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
         <v>599</v>
       </c>
@@ -8562,18 +8713,18 @@
         <v>806</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
     </row>
-    <row r="83" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A83" s="15" t="s">
         <v>160</v>
       </c>
@@ -8588,14 +8739,14 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
     </row>
-    <row r="84" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" ht="54" x14ac:dyDescent="0.45">
       <c r="A84" s="15" t="s">
         <v>161</v>
       </c>
@@ -8610,7 +8761,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
@@ -8639,7 +8790,7 @@
       </c>
       <c r="H85" s="32"/>
     </row>
-    <row r="86" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:8" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="14" t="s">
         <v>164</v>
       </c>
@@ -8650,11 +8801,11 @@
         <v>817</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00BC5CF-5919-44D0-93D9-330EE0B6A84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB39A1AC-B0F5-4188-90C5-5EC86A4EAD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="843">
   <si>
     <t>家里</t>
   </si>
@@ -5959,6 +5959,15 @@
       </rPr>
       <t>传奇模式：强迫玩家石化(不回血)，自身石化时回复130HP</t>
     </r>
+  </si>
+  <si>
+    <t>多模式图</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>是</t>
   </si>
 </sst>
 </file>
@@ -6924,7 +6933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="5" customWidth="1"/>
@@ -6935,10 +6944,11 @@
     <col min="6" max="6" width="71.59765625" style="5" customWidth="1"/>
     <col min="7" max="7" width="32.06640625" style="5" customWidth="1"/>
     <col min="8" max="8" width="65.1328125" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="5"/>
+    <col min="9" max="9" width="12.33203125" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="9.06640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="40" t="s">
         <v>712</v>
       </c>
@@ -6950,7 +6960,7 @@
       <c r="G1" s="42"/>
       <c r="H1" s="43"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -6975,8 +6985,11 @@
       <c r="H2" s="31" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I2" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
@@ -6997,8 +7010,11 @@
         <v>0</v>
       </c>
       <c r="H3" s="32"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I3" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
@@ -7023,8 +7039,11 @@
       <c r="H4" s="33" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I4" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
@@ -7043,8 +7062,11 @@
         <v>11</v>
       </c>
       <c r="H5" s="32"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I5" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
@@ -7063,8 +7085,11 @@
         <v>13</v>
       </c>
       <c r="H6" s="32"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I6" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -7083,8 +7108,11 @@
         <v>15</v>
       </c>
       <c r="H7" s="32"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I7" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>16</v>
       </c>
@@ -7103,8 +7131,11 @@
         <v>17</v>
       </c>
       <c r="H8" s="32"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I8" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>18</v>
       </c>
@@ -7125,8 +7156,11 @@
         <v>20</v>
       </c>
       <c r="H9" s="32"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I9" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
         <v>636</v>
       </c>
@@ -7147,8 +7181,11 @@
         <v>637</v>
       </c>
       <c r="H10" s="32"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I10" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
@@ -7167,8 +7204,11 @@
         <v>24</v>
       </c>
       <c r="H11" s="32"/>
-    </row>
-    <row r="12" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I11" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -7187,8 +7227,11 @@
         <v>670</v>
       </c>
       <c r="H12" s="32"/>
-    </row>
-    <row r="13" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I12" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -7207,8 +7250,11 @@
         <v>671</v>
       </c>
       <c r="H13" s="32"/>
-    </row>
-    <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I13" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -7227,8 +7273,11 @@
         <v>679</v>
       </c>
       <c r="H14" s="32"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I14" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -7247,8 +7296,11 @@
         <v>654</v>
       </c>
       <c r="H15" s="32"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I15" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>30</v>
       </c>
@@ -7269,8 +7321,11 @@
         <v>32</v>
       </c>
       <c r="H16" s="32"/>
-    </row>
-    <row r="17" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I16" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
         <v>33</v>
       </c>
@@ -7289,8 +7344,11 @@
         <v>34</v>
       </c>
       <c r="H17" s="32"/>
-    </row>
-    <row r="18" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I17" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
         <v>35</v>
       </c>
@@ -7311,8 +7369,11 @@
         <v>658</v>
       </c>
       <c r="H18" s="32"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I18" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
         <v>37</v>
       </c>
@@ -7331,8 +7392,11 @@
         <v>38</v>
       </c>
       <c r="H19" s="32"/>
-    </row>
-    <row r="20" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I19" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A20" s="11" t="s">
         <v>39</v>
       </c>
@@ -7353,8 +7417,11 @@
         <v>584</v>
       </c>
       <c r="H20" s="32"/>
-    </row>
-    <row r="21" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I20" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A21" s="11" t="s">
         <v>42</v>
       </c>
@@ -7373,8 +7440,11 @@
         <v>655</v>
       </c>
       <c r="H21" s="32"/>
-    </row>
-    <row r="22" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I21" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
         <v>44</v>
       </c>
@@ -7395,8 +7465,11 @@
         <v>680</v>
       </c>
       <c r="H22" s="32"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I22" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="12" t="s">
         <v>47</v>
       </c>
@@ -7417,8 +7490,11 @@
         <v>8</v>
       </c>
       <c r="H23" s="32"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I23" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="12" t="s">
         <v>50</v>
       </c>
@@ -7439,8 +7515,11 @@
         <v>653</v>
       </c>
       <c r="H24" s="32"/>
-    </row>
-    <row r="25" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I24" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A25" s="12" t="s">
         <v>52</v>
       </c>
@@ -7461,8 +7540,11 @@
         <v>657</v>
       </c>
       <c r="H25" s="32"/>
-    </row>
-    <row r="26" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I25" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A26" s="12" t="s">
         <v>54</v>
       </c>
@@ -7483,8 +7565,11 @@
         <v>656</v>
       </c>
       <c r="H26" s="32"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I26" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="12" t="s">
         <v>56</v>
       </c>
@@ -7505,8 +7590,11 @@
         <v>672</v>
       </c>
       <c r="H27" s="32"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I27" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="12" t="s">
         <v>58</v>
       </c>
@@ -7525,8 +7613,11 @@
         <v>59</v>
       </c>
       <c r="H28" s="32"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I28" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
         <v>62</v>
       </c>
@@ -7545,8 +7636,11 @@
         <v>64</v>
       </c>
       <c r="H29" s="32"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I29" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
         <v>65</v>
       </c>
@@ -7567,8 +7661,11 @@
         <v>67</v>
       </c>
       <c r="H30" s="32"/>
-    </row>
-    <row r="31" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I30" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
         <v>68</v>
       </c>
@@ -7589,8 +7686,11 @@
         <v>70</v>
       </c>
       <c r="H31" s="32"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I31" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
         <v>71</v>
       </c>
@@ -7611,8 +7711,11 @@
         <v>667</v>
       </c>
       <c r="H32" s="32"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I32" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="14" t="s">
         <v>73</v>
       </c>
@@ -7633,8 +7736,11 @@
         <v>75</v>
       </c>
       <c r="H33" s="32"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I33" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
         <v>693</v>
       </c>
@@ -7659,8 +7765,11 @@
       <c r="H34" s="33" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I34" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35" s="11" t="s">
         <v>76</v>
       </c>
@@ -7681,8 +7790,11 @@
       <c r="H35" s="47" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I35" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="11" t="s">
         <v>77</v>
       </c>
@@ -7701,8 +7813,11 @@
         <v>78</v>
       </c>
       <c r="H36" s="48"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I36" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37" s="11" t="s">
         <v>79</v>
       </c>
@@ -7721,8 +7836,11 @@
         <v>682</v>
       </c>
       <c r="H37" s="48"/>
-    </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I37" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="11" t="s">
         <v>80</v>
       </c>
@@ -7743,8 +7861,11 @@
         <v>683</v>
       </c>
       <c r="H38" s="48"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I38" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
         <v>82</v>
       </c>
@@ -7763,8 +7884,11 @@
         <v>684</v>
       </c>
       <c r="H39" s="48"/>
-    </row>
-    <row r="40" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I39" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
         <v>83</v>
       </c>
@@ -7785,8 +7909,11 @@
         <v>685</v>
       </c>
       <c r="H40" s="48"/>
-    </row>
-    <row r="41" spans="1:8" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I40" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="11" t="s">
         <v>85</v>
       </c>
@@ -7805,8 +7932,11 @@
         <v>686</v>
       </c>
       <c r="H41" s="48"/>
-    </row>
-    <row r="42" spans="1:8" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I41" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="11" t="s">
         <v>86</v>
       </c>
@@ -7825,8 +7955,11 @@
         <v>683</v>
       </c>
       <c r="H42" s="48"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I42" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="12" t="s">
         <v>87</v>
       </c>
@@ -7847,8 +7980,11 @@
         <v>684</v>
       </c>
       <c r="H43" s="48"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I43" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="12" t="s">
         <v>614</v>
       </c>
@@ -7869,8 +8005,11 @@
         <v>687</v>
       </c>
       <c r="H44" s="48"/>
-    </row>
-    <row r="45" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I44" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
         <v>613</v>
       </c>
@@ -7891,8 +8030,11 @@
         <v>687</v>
       </c>
       <c r="H45" s="48"/>
-    </row>
-    <row r="46" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I45" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
         <v>612</v>
       </c>
@@ -7913,8 +8055,11 @@
         <v>687</v>
       </c>
       <c r="H46" s="48"/>
-    </row>
-    <row r="47" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I46" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A47" s="12" t="s">
         <v>96</v>
       </c>
@@ -7935,8 +8080,11 @@
         <v>687</v>
       </c>
       <c r="H47" s="48"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I47" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" s="12" t="s">
         <v>98</v>
       </c>
@@ -7957,8 +8105,11 @@
         <v>78</v>
       </c>
       <c r="H48" s="48"/>
-    </row>
-    <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I48" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A49" s="13" t="s">
         <v>100</v>
       </c>
@@ -7979,8 +8130,11 @@
         <v>687</v>
       </c>
       <c r="H49" s="48"/>
-    </row>
-    <row r="50" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I49" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="13" t="s">
         <v>104</v>
       </c>
@@ -8001,8 +8155,11 @@
         <v>688</v>
       </c>
       <c r="H50" s="48"/>
-    </row>
-    <row r="51" spans="1:8" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I50" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="13" t="s">
         <v>106</v>
       </c>
@@ -8023,8 +8180,11 @@
         <v>689</v>
       </c>
       <c r="H51" s="48"/>
-    </row>
-    <row r="52" spans="1:8" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I51" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="13" t="s">
         <v>108</v>
       </c>
@@ -8045,8 +8205,11 @@
         <v>690</v>
       </c>
       <c r="H52" s="48"/>
-    </row>
-    <row r="53" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I52" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" s="13" t="s">
         <v>110</v>
       </c>
@@ -8067,8 +8230,11 @@
         <v>691</v>
       </c>
       <c r="H53" s="49"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I53" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
         <v>112</v>
       </c>
@@ -8093,8 +8259,11 @@
       <c r="H54" s="33" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I54" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
         <v>695</v>
       </c>
@@ -8117,8 +8286,11 @@
       <c r="H55" s="47" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I55" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="11" t="s">
         <v>115</v>
       </c>
@@ -8139,8 +8311,11 @@
         <v>674</v>
       </c>
       <c r="H56" s="48"/>
-    </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I56" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="11" t="s">
         <v>117</v>
       </c>
@@ -8161,8 +8336,11 @@
         <v>675</v>
       </c>
       <c r="H57" s="48"/>
-    </row>
-    <row r="58" spans="1:8" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I57" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="11" t="s">
         <v>119</v>
       </c>
@@ -8183,8 +8361,11 @@
         <v>676</v>
       </c>
       <c r="H58" s="48"/>
-    </row>
-    <row r="59" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I58" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="11" t="s">
         <v>120</v>
       </c>
@@ -8205,8 +8386,11 @@
         <v>677</v>
       </c>
       <c r="H59" s="48"/>
-    </row>
-    <row r="60" spans="1:8" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I59" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="11" t="s">
         <v>122</v>
       </c>
@@ -8227,8 +8411,11 @@
         <v>674</v>
       </c>
       <c r="H60" s="48"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I60" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" s="11" t="s">
         <v>124</v>
       </c>
@@ -8249,8 +8436,11 @@
         <v>675</v>
       </c>
       <c r="H61" s="48"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I61" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" s="12" t="s">
         <v>126</v>
       </c>
@@ -8271,8 +8461,11 @@
         <v>678</v>
       </c>
       <c r="H62" s="48"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I62" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" s="12" t="s">
         <v>128</v>
       </c>
@@ -8293,8 +8486,11 @@
         <v>675</v>
       </c>
       <c r="H63" s="48"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I63" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" s="12" t="s">
         <v>130</v>
       </c>
@@ -8317,8 +8513,11 @@
         <v>675</v>
       </c>
       <c r="H64" s="48"/>
-    </row>
-    <row r="65" spans="1:8" ht="162" x14ac:dyDescent="0.45">
+      <c r="I64" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="162.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A65" s="14" t="s">
         <v>132</v>
       </c>
@@ -8339,8 +8538,11 @@
         <v>673</v>
       </c>
       <c r="H65" s="49"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I65" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
         <v>133</v>
       </c>
@@ -8365,8 +8567,11 @@
       <c r="H66" s="34" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I66" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A67" s="11" t="s">
         <v>134</v>
       </c>
@@ -8389,8 +8594,11 @@
       <c r="H67" s="50" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I67" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A68" s="11" t="s">
         <v>137</v>
       </c>
@@ -8411,8 +8619,11 @@
         <v>136</v>
       </c>
       <c r="H68" s="48"/>
-    </row>
-    <row r="69" spans="1:8" ht="81" x14ac:dyDescent="0.45">
+      <c r="I68" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.45">
       <c r="A69" s="12" t="s">
         <v>139</v>
       </c>
@@ -8433,8 +8644,11 @@
         <v>136</v>
       </c>
       <c r="H69" s="48"/>
-    </row>
-    <row r="70" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
+      <c r="I69" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" s="12" t="s">
         <v>141</v>
       </c>
@@ -8455,8 +8669,11 @@
         <v>136</v>
       </c>
       <c r="H70" s="48"/>
-    </row>
-    <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I70" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
         <v>143</v>
       </c>
@@ -8481,8 +8698,11 @@
       <c r="H71" s="35" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I71" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72" s="11" t="s">
         <v>144</v>
       </c>
@@ -8501,8 +8721,11 @@
         <v>143</v>
       </c>
       <c r="H72" s="32"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I72" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73" s="11" t="s">
         <v>145</v>
       </c>
@@ -8521,8 +8744,11 @@
         <v>143</v>
       </c>
       <c r="H73" s="32"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I73" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" s="11" t="s">
         <v>146</v>
       </c>
@@ -8543,8 +8769,11 @@
         <v>143</v>
       </c>
       <c r="H74" s="32"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I74" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
         <v>148</v>
       </c>
@@ -8569,8 +8798,11 @@
       <c r="H75" s="33" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I75" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A76" s="11" t="s">
         <v>149</v>
       </c>
@@ -8591,8 +8823,11 @@
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
-    </row>
-    <row r="77" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I76" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A77" s="11" t="s">
         <v>151</v>
       </c>
@@ -8613,8 +8848,11 @@
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
-    </row>
-    <row r="78" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I77" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A78" s="11" t="s">
         <v>153</v>
       </c>
@@ -8635,8 +8873,11 @@
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
-    </row>
-    <row r="79" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I78" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A79" s="11" t="s">
         <v>155</v>
       </c>
@@ -8657,8 +8898,11 @@
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
-    </row>
-    <row r="80" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I79" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A80" s="11" t="s">
         <v>156</v>
       </c>
@@ -8679,8 +8923,11 @@
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I80" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
         <v>598</v>
       </c>
@@ -8701,8 +8948,11 @@
         <v>150</v>
       </c>
       <c r="H81" s="32"/>
-    </row>
-    <row r="82" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I81" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
         <v>599</v>
       </c>
@@ -8723,8 +8973,11 @@
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
-    </row>
-    <row r="83" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I82" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A83" s="15" t="s">
         <v>160</v>
       </c>
@@ -8745,8 +8998,11 @@
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
-    </row>
-    <row r="84" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I83" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A84" s="15" t="s">
         <v>161</v>
       </c>
@@ -8767,8 +9023,11 @@
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I84" s="5" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85" s="15" t="s">
         <v>162</v>
       </c>
@@ -8789,8 +9048,11 @@
         <v>150</v>
       </c>
       <c r="H85" s="32"/>
-    </row>
-    <row r="86" spans="1:8" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I85" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="14" t="s">
         <v>164</v>
       </c>
@@ -8811,8 +9073,11 @@
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I86" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A87" s="14" t="s">
         <v>638</v>
       </c>
@@ -8833,8 +9098,11 @@
         <v>150</v>
       </c>
       <c r="H87" s="32"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I87" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
         <v>167</v>
       </c>
@@ -8859,8 +9127,11 @@
       <c r="H88" s="34" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I88" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="11" t="s">
         <v>168</v>
       </c>
@@ -8881,8 +9152,11 @@
         <v>169</v>
       </c>
       <c r="H89" s="32"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I89" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90" s="11" t="s">
         <v>170</v>
       </c>
@@ -8901,8 +9175,11 @@
         <v>171</v>
       </c>
       <c r="H90" s="32"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I90" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91" s="11" t="s">
         <v>172</v>
       </c>
@@ -8921,8 +9198,11 @@
         <v>173</v>
       </c>
       <c r="H91" s="32"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I91" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92" s="11" t="s">
         <v>174</v>
       </c>
@@ -8941,8 +9221,11 @@
         <v>173</v>
       </c>
       <c r="H92" s="32"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I92" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93" s="11" t="s">
         <v>175</v>
       </c>
@@ -8961,8 +9244,11 @@
         <v>173</v>
       </c>
       <c r="H93" s="32"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I93" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94" s="11" t="s">
         <v>176</v>
       </c>
@@ -8983,8 +9269,11 @@
         <v>179</v>
       </c>
       <c r="H94" s="32"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I94" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95" s="11" t="s">
         <v>180</v>
       </c>
@@ -9003,8 +9292,11 @@
         <v>181</v>
       </c>
       <c r="H95" s="32"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I95" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96" s="11" t="s">
         <v>182</v>
       </c>
@@ -9025,8 +9317,11 @@
         <v>184</v>
       </c>
       <c r="H96" s="32"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I96" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
         <v>186</v>
       </c>
@@ -9045,8 +9340,11 @@
         <v>187</v>
       </c>
       <c r="H97" s="32"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I97" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
         <v>643</v>
       </c>
@@ -9065,8 +9363,11 @@
         <v>189</v>
       </c>
       <c r="H98" s="32"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I98" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
         <v>644</v>
       </c>
@@ -9087,8 +9388,11 @@
         <v>189</v>
       </c>
       <c r="H99" s="32"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I99" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100" s="11" t="s">
         <v>192</v>
       </c>
@@ -9109,8 +9413,11 @@
         <v>194</v>
       </c>
       <c r="H100" s="32"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I100" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101" s="11" t="s">
         <v>195</v>
       </c>
@@ -9131,8 +9438,11 @@
         <v>197</v>
       </c>
       <c r="H101" s="32"/>
-    </row>
-    <row r="102" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I101" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="11" t="s">
         <v>198</v>
       </c>
@@ -9153,8 +9463,11 @@
         <v>197</v>
       </c>
       <c r="H102" s="32"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I102" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
         <v>200</v>
       </c>
@@ -9175,8 +9488,11 @@
         <v>202</v>
       </c>
       <c r="H103" s="32"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I103" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104" s="12" t="s">
         <v>203</v>
       </c>
@@ -9195,8 +9511,11 @@
         <v>204</v>
       </c>
       <c r="H104" s="32"/>
-    </row>
-    <row r="105" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I104" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A105" s="11" t="s">
         <v>205</v>
       </c>
@@ -9215,8 +9534,11 @@
         <v>207</v>
       </c>
       <c r="H105" s="32"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I105" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106" s="11" t="s">
         <v>208</v>
       </c>
@@ -9235,8 +9557,11 @@
         <v>209</v>
       </c>
       <c r="H106" s="32"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I106" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107" s="11" t="s">
         <v>210</v>
       </c>
@@ -9255,8 +9580,11 @@
         <v>209</v>
       </c>
       <c r="H107" s="32"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I107" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108" s="11" t="s">
         <v>211</v>
       </c>
@@ -9275,8 +9603,11 @@
         <v>209</v>
       </c>
       <c r="H108" s="32"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I108" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
         <v>212</v>
       </c>
@@ -9295,8 +9626,11 @@
         <v>213</v>
       </c>
       <c r="H109" s="32"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I109" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
         <v>214</v>
       </c>
@@ -9315,8 +9649,11 @@
         <v>215</v>
       </c>
       <c r="H110" s="32"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I110" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
         <v>216</v>
       </c>
@@ -9335,8 +9672,11 @@
         <v>217</v>
       </c>
       <c r="H111" s="32"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I111" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
         <v>218</v>
       </c>
@@ -9357,8 +9697,11 @@
         <v>220</v>
       </c>
       <c r="H112" s="32"/>
-    </row>
-    <row r="113" spans="1:8" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I112" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
         <v>221</v>
       </c>
@@ -9379,8 +9722,11 @@
         <v>194</v>
       </c>
       <c r="H113" s="32"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I113" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
         <v>223</v>
       </c>
@@ -9401,8 +9747,11 @@
         <v>225</v>
       </c>
       <c r="H114" s="32"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I114" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
         <v>226</v>
       </c>
@@ -9423,8 +9772,11 @@
         <v>229</v>
       </c>
       <c r="H115" s="32"/>
-    </row>
-    <row r="116" spans="1:8" ht="121.5" x14ac:dyDescent="0.45">
+      <c r="I115" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="121.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A116" s="14" t="s">
         <v>583</v>
       </c>
@@ -9445,8 +9797,11 @@
         <v>231</v>
       </c>
       <c r="H116" s="32"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I116" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
         <v>585</v>
       </c>
@@ -9471,8 +9826,11 @@
       <c r="H117" s="35" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I117" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" s="11" t="s">
         <v>600</v>
       </c>
@@ -9493,8 +9851,11 @@
         <v>588</v>
       </c>
       <c r="H118" s="32"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I118" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" s="11" t="s">
         <v>601</v>
       </c>
@@ -9515,8 +9876,11 @@
         <v>588</v>
       </c>
       <c r="H119" s="32"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I119" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" s="11" t="s">
         <v>602</v>
       </c>
@@ -9537,8 +9901,11 @@
         <v>588</v>
       </c>
       <c r="H120" s="32"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I120" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" s="11" t="s">
         <v>237</v>
       </c>
@@ -9559,8 +9926,11 @@
         <v>588</v>
       </c>
       <c r="H121" s="32"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I121" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122" s="11" t="s">
         <v>239</v>
       </c>
@@ -9581,8 +9951,11 @@
         <v>588</v>
       </c>
       <c r="H122" s="32"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I122" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123" s="11" t="s">
         <v>603</v>
       </c>
@@ -9603,8 +9976,11 @@
         <v>588</v>
       </c>
       <c r="H123" s="32"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I123" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
         <v>604</v>
       </c>
@@ -9625,8 +10001,11 @@
         <v>588</v>
       </c>
       <c r="H124" s="32"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I124" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
         <v>590</v>
       </c>
@@ -9647,8 +10026,11 @@
         <v>588</v>
       </c>
       <c r="H125" s="32"/>
-    </row>
-    <row r="126" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I125" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
         <v>594</v>
       </c>
@@ -9669,8 +10051,11 @@
         <v>588</v>
       </c>
       <c r="H126" s="32"/>
-    </row>
-    <row r="127" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I126" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
         <v>596</v>
       </c>
@@ -9691,8 +10076,11 @@
         <v>588</v>
       </c>
       <c r="H127" s="32"/>
-    </row>
-    <row r="128" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
+      <c r="I127" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A128" s="13" t="s">
         <v>607</v>
       </c>
@@ -9713,8 +10101,11 @@
         <v>588</v>
       </c>
       <c r="H128" s="32"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I128" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
         <v>232</v>
       </c>
@@ -9739,8 +10130,11 @@
       <c r="H129" s="34" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I129" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130" s="11" t="s">
         <v>233</v>
       </c>
@@ -9761,8 +10155,11 @@
         <v>235</v>
       </c>
       <c r="H130" s="32"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I130" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131" s="12" t="s">
         <v>60</v>
       </c>
@@ -9781,8 +10178,11 @@
         <v>61</v>
       </c>
       <c r="H131" s="32"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I131" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
         <v>240</v>
       </c>
@@ -9801,8 +10201,11 @@
         <v>241</v>
       </c>
       <c r="H132" s="32"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I132" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133" s="11" t="s">
         <v>242</v>
       </c>
@@ -9823,8 +10226,11 @@
         <v>244</v>
       </c>
       <c r="H133" s="32"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I133" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
         <v>245</v>
       </c>
@@ -9843,8 +10249,11 @@
         <v>244</v>
       </c>
       <c r="H134" s="32"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I134" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
         <v>246</v>
       </c>
@@ -9865,8 +10274,11 @@
         <v>244</v>
       </c>
       <c r="H135" s="32"/>
-    </row>
-    <row r="136" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I135" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="11" t="s">
         <v>248</v>
       </c>
@@ -9887,8 +10299,11 @@
         <v>250</v>
       </c>
       <c r="H136" s="32"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I136" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
         <v>251</v>
       </c>
@@ -9911,8 +10326,11 @@
         <v>250</v>
       </c>
       <c r="H137" s="32"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I137" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
         <v>254</v>
       </c>
@@ -9933,8 +10351,11 @@
         <v>256</v>
       </c>
       <c r="H138" s="32"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I138" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
         <v>696</v>
       </c>
@@ -9955,8 +10376,11 @@
         <v>698</v>
       </c>
       <c r="H139" s="32"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I139" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
         <v>257</v>
       </c>
@@ -9977,8 +10401,11 @@
         <v>258</v>
       </c>
       <c r="H140" s="32"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I140" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
         <v>259</v>
       </c>
@@ -9999,8 +10426,11 @@
         <v>261</v>
       </c>
       <c r="H141" s="32"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I141" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
         <v>262</v>
       </c>
@@ -10021,8 +10451,11 @@
         <v>264</v>
       </c>
       <c r="H142" s="32"/>
-    </row>
-    <row r="143" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I142" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A143" s="14" t="s">
         <v>265</v>
       </c>
@@ -10043,8 +10476,11 @@
         <v>261</v>
       </c>
       <c r="H143" s="32"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I143" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
         <v>267</v>
       </c>
@@ -10069,8 +10505,11 @@
       <c r="H144" s="36" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I144" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" s="11" t="s">
         <v>268</v>
       </c>
@@ -10091,8 +10530,11 @@
         <v>267</v>
       </c>
       <c r="H145" s="32"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I145" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" s="11" t="s">
         <v>270</v>
       </c>
@@ -10113,8 +10555,11 @@
         <v>267</v>
       </c>
       <c r="H146" s="32"/>
-    </row>
-    <row r="147" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I146" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="11" t="s">
         <v>272</v>
       </c>
@@ -10133,8 +10578,11 @@
         <v>267</v>
       </c>
       <c r="H147" s="32"/>
-    </row>
-    <row r="148" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I147" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="11" t="s">
         <v>273</v>
       </c>
@@ -10153,8 +10601,11 @@
         <v>267</v>
       </c>
       <c r="H148" s="32"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I148" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" s="11" t="s">
         <v>274</v>
       </c>
@@ -10175,8 +10626,11 @@
         <v>267</v>
       </c>
       <c r="H149" s="32"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I149" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A150" s="11" t="s">
         <v>276</v>
       </c>
@@ -10197,8 +10651,11 @@
         <v>267</v>
       </c>
       <c r="H150" s="32"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I150" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
         <v>713</v>
       </c>
@@ -10223,8 +10680,11 @@
       <c r="H151" s="36" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I151" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" s="11" t="s">
         <v>281</v>
       </c>
@@ -10245,8 +10705,11 @@
         <v>284</v>
       </c>
       <c r="H152" s="32"/>
-    </row>
-    <row r="153" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I152" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
         <v>660</v>
       </c>
@@ -10269,8 +10732,11 @@
         <v>279</v>
       </c>
       <c r="H153" s="32"/>
-    </row>
-    <row r="154" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I153" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
         <v>285</v>
       </c>
@@ -10293,8 +10759,11 @@
         <v>298</v>
       </c>
       <c r="H154" s="32"/>
-    </row>
-    <row r="155" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I154" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
         <v>291</v>
       </c>
@@ -10317,8 +10786,11 @@
         <v>298</v>
       </c>
       <c r="H155" s="32"/>
-    </row>
-    <row r="156" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I155" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
         <v>294</v>
       </c>
@@ -10341,8 +10813,11 @@
         <v>298</v>
       </c>
       <c r="H156" s="32"/>
-    </row>
-    <row r="157" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I156" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
         <v>296</v>
       </c>
@@ -10365,8 +10840,11 @@
         <v>298</v>
       </c>
       <c r="H157" s="32"/>
-    </row>
-    <row r="158" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I157" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
         <v>572</v>
       </c>
@@ -10389,8 +10867,11 @@
         <v>298</v>
       </c>
       <c r="H158" s="32"/>
-    </row>
-    <row r="159" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I158" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
         <v>568</v>
       </c>
@@ -10413,8 +10894,11 @@
         <v>298</v>
       </c>
       <c r="H159" s="32"/>
-    </row>
-    <row r="160" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I159" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
         <v>569</v>
       </c>
@@ -10437,8 +10921,11 @@
         <v>298</v>
       </c>
       <c r="H160" s="32"/>
-    </row>
-    <row r="161" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I160" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
         <v>570</v>
       </c>
@@ -10461,8 +10948,11 @@
         <v>298</v>
       </c>
       <c r="H161" s="32"/>
-    </row>
-    <row r="162" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I161" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
         <v>571</v>
       </c>
@@ -10485,8 +10975,11 @@
         <v>298</v>
       </c>
       <c r="H162" s="32"/>
-    </row>
-    <row r="163" spans="1:8" ht="67.5" x14ac:dyDescent="0.45">
+      <c r="I162" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
         <v>309</v>
       </c>
@@ -10509,8 +11002,11 @@
         <v>284</v>
       </c>
       <c r="H163" s="32"/>
-    </row>
-    <row r="164" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I163" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="14" t="s">
         <v>314</v>
       </c>
@@ -10533,8 +11029,11 @@
         <v>298</v>
       </c>
       <c r="H164" s="32"/>
-    </row>
-    <row r="165" spans="1:8" ht="202.5" x14ac:dyDescent="0.45">
+      <c r="I164" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="202.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A165" s="14" t="s">
         <v>573</v>
       </c>
@@ -10557,8 +11056,11 @@
         <v>279</v>
       </c>
       <c r="H165" s="32"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I165" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
         <v>701</v>
       </c>
@@ -10583,8 +11085,11 @@
       <c r="H166" s="36" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I166" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
         <v>702</v>
       </c>
@@ -10607,8 +11112,11 @@
       <c r="H167" s="50" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I167" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
         <v>706</v>
       </c>
@@ -10631,8 +11139,11 @@
         <v>701</v>
       </c>
       <c r="H168" s="50"/>
-    </row>
-    <row r="169" spans="1:8" ht="94.5" x14ac:dyDescent="0.45">
+      <c r="I168" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
         <v>707</v>
       </c>
@@ -10655,8 +11166,11 @@
         <v>701</v>
       </c>
       <c r="H169" s="50"/>
-    </row>
-    <row r="170" spans="1:8" ht="81" x14ac:dyDescent="0.45">
+      <c r="I169" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
         <v>708</v>
       </c>
@@ -10679,8 +11193,11 @@
         <v>701</v>
       </c>
       <c r="H170" s="50"/>
-    </row>
-    <row r="171" spans="1:8" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I170" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
         <v>709</v>
       </c>
@@ -10703,8 +11220,11 @@
         <v>701</v>
       </c>
       <c r="H171" s="50"/>
-    </row>
-    <row r="172" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I171" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
         <v>710</v>
       </c>
@@ -10727,8 +11247,11 @@
         <v>701</v>
       </c>
       <c r="H172" s="50"/>
-    </row>
-    <row r="173" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I172" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
         <v>704</v>
       </c>
@@ -10751,8 +11274,11 @@
         <v>701</v>
       </c>
       <c r="H173" s="50"/>
-    </row>
-    <row r="174" spans="1:8" ht="207" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I173" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
         <v>705</v>
       </c>
@@ -10775,8 +11301,11 @@
         <v>701</v>
       </c>
       <c r="H174" s="50"/>
-    </row>
-    <row r="175" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I174" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
         <v>726</v>
       </c>
@@ -10799,8 +11328,11 @@
         <v>5</v>
       </c>
       <c r="H175" s="50"/>
-    </row>
-    <row r="176" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I175" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
         <v>714</v>
       </c>
@@ -10823,8 +11355,11 @@
         <v>701</v>
       </c>
       <c r="H176" s="50"/>
-    </row>
-    <row r="177" spans="1:8" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I176" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
         <v>715</v>
       </c>
@@ -10847,8 +11382,11 @@
         <v>701</v>
       </c>
       <c r="H177" s="50"/>
-    </row>
-    <row r="178" spans="1:8" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I177" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
         <v>716</v>
       </c>
@@ -10871,8 +11409,11 @@
         <v>701</v>
       </c>
       <c r="H178" s="50"/>
-    </row>
-    <row r="179" spans="1:8" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I178" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
         <v>717</v>
       </c>
@@ -10895,8 +11436,11 @@
         <v>701</v>
       </c>
       <c r="H179" s="50"/>
-    </row>
-    <row r="180" spans="1:8" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I179" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
         <v>718</v>
       </c>
@@ -10919,8 +11463,11 @@
         <v>701</v>
       </c>
       <c r="H180" s="50"/>
-    </row>
-    <row r="181" spans="1:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I180" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
         <v>719</v>
       </c>
@@ -10943,8 +11490,11 @@
         <v>701</v>
       </c>
       <c r="H181" s="50"/>
-    </row>
-    <row r="182" spans="1:8" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I181" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
         <v>720</v>
       </c>
@@ -10967,8 +11517,11 @@
         <v>701</v>
       </c>
       <c r="H182" s="50"/>
-    </row>
-    <row r="183" spans="1:8" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I182" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
         <v>721</v>
       </c>
@@ -10991,8 +11544,11 @@
         <v>701</v>
       </c>
       <c r="H183" s="50"/>
-    </row>
-    <row r="184" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I183" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
         <v>722</v>
       </c>
@@ -11015,8 +11571,11 @@
         <v>701</v>
       </c>
       <c r="H184" s="50"/>
-    </row>
-    <row r="185" spans="1:8" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I184" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
         <v>723</v>
       </c>
@@ -11039,8 +11598,11 @@
         <v>701</v>
       </c>
       <c r="H185" s="50"/>
-    </row>
-    <row r="186" spans="1:8" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I185" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
         <v>724</v>
       </c>
@@ -11063,8 +11625,11 @@
         <v>701</v>
       </c>
       <c r="H186" s="50"/>
-    </row>
-    <row r="187" spans="1:8" ht="83.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I186" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A187" s="14" t="s">
         <v>725</v>
       </c>
@@ -11087,8 +11652,11 @@
         <v>701</v>
       </c>
       <c r="H187" s="50"/>
-    </row>
-    <row r="188" spans="1:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="I187" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" s="24" t="s">
         <v>319</v>
       </c>
@@ -11113,8 +11681,11 @@
       <c r="H188" s="36" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I188" s="31" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A189" s="26" t="s">
         <v>320</v>
       </c>
@@ -11139,8 +11710,11 @@
       <c r="H189" s="44" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I189" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="11" t="s">
         <v>322</v>
       </c>
@@ -11159,8 +11733,11 @@
       </c>
       <c r="G190" s="38"/>
       <c r="H190" s="45"/>
-    </row>
-    <row r="191" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I190" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
         <v>324</v>
       </c>
@@ -11179,8 +11756,11 @@
       </c>
       <c r="G191" s="38"/>
       <c r="H191" s="45"/>
-    </row>
-    <row r="192" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I191" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="11" t="s">
         <v>326</v>
       </c>
@@ -11199,8 +11779,11 @@
       </c>
       <c r="G192" s="38"/>
       <c r="H192" s="45"/>
-    </row>
-    <row r="193" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I192" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A193" s="11" t="s">
         <v>328</v>
       </c>
@@ -11219,8 +11802,11 @@
       </c>
       <c r="G193" s="38"/>
       <c r="H193" s="45"/>
-    </row>
-    <row r="194" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I193" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
         <v>330</v>
       </c>
@@ -11239,8 +11825,11 @@
       </c>
       <c r="G194" s="38"/>
       <c r="H194" s="45"/>
-    </row>
-    <row r="195" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I194" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A195" s="11" t="s">
         <v>332</v>
       </c>
@@ -11259,8 +11848,11 @@
       </c>
       <c r="G195" s="38"/>
       <c r="H195" s="45"/>
-    </row>
-    <row r="196" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I195" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
         <v>334</v>
       </c>
@@ -11279,8 +11871,11 @@
       </c>
       <c r="G196" s="38"/>
       <c r="H196" s="45"/>
-    </row>
-    <row r="197" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I196" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
         <v>336</v>
       </c>
@@ -11299,8 +11894,11 @@
       </c>
       <c r="G197" s="38"/>
       <c r="H197" s="45"/>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I197" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
         <v>338</v>
       </c>
@@ -11319,8 +11917,11 @@
       </c>
       <c r="G198" s="38"/>
       <c r="H198" s="45"/>
-    </row>
-    <row r="199" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I198" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
         <v>340</v>
       </c>
@@ -11339,8 +11940,11 @@
       </c>
       <c r="G199" s="38"/>
       <c r="H199" s="45"/>
-    </row>
-    <row r="200" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I199" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A200" s="12" t="s">
         <v>342</v>
       </c>
@@ -11359,8 +11963,11 @@
       </c>
       <c r="G200" s="38"/>
       <c r="H200" s="45"/>
-    </row>
-    <row r="201" spans="1:8" ht="54" x14ac:dyDescent="0.45">
+      <c r="I200" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A201" s="12" t="s">
         <v>344</v>
       </c>
@@ -11381,8 +11988,11 @@
       </c>
       <c r="G201" s="38"/>
       <c r="H201" s="45"/>
-    </row>
-    <row r="202" spans="1:8" ht="40.5" x14ac:dyDescent="0.45">
+      <c r="I201" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A202" s="12" t="s">
         <v>346</v>
       </c>
@@ -11403,8 +12013,11 @@
       </c>
       <c r="G202" s="38"/>
       <c r="H202" s="45"/>
-    </row>
-    <row r="203" spans="1:8" ht="27" x14ac:dyDescent="0.45">
+      <c r="I202" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
         <v>611</v>
       </c>
@@ -11423,8 +12036,11 @@
       </c>
       <c r="G203" s="38"/>
       <c r="H203" s="45"/>
-    </row>
-    <row r="204" spans="1:8" ht="54.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="I203" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
         <v>610</v>
       </c>
@@ -11445,6 +12061,9 @@
       </c>
       <c r="G204" s="39"/>
       <c r="H204" s="46"/>
+      <c r="I204" s="5" t="s">
+        <v>841</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB39A1AC-B0F5-4188-90C5-5EC86A4EAD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7208CD8-F2A2-4F29-8AF8-49AAAC8D32C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4678,74 +4678,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>【人物介绍】他以如此狂烈的怒火粉碎伪神，每一锤落下，石块都被击飞百步之外。据说，锤上镶着他摧毁的第一个偶像的一块碎片。
-【技能效果】给近战中的对手施加禁疗效果
-【人物装备】圣殿骑士套装，碎颅者
-【所需戒指】普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>：30/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>180</t>
-    </r>
-  </si>
-  <si>
     <t>待测，待测，400</t>
   </si>
   <si>
@@ -4851,142 +4783,6 @@
   </si>
   <si>
     <r>
-      <t>【人物介绍】当绝望笼罩众人时，她重新集结了营团，带领他们继续前进。敌方首领倒下了，她的族人安然无恙地走了出来。我们守护着她的遗骸，并坚信埃琳娜的烈酒守护着我们。
-【技能效果】皇帝之盾赋予她给友军提供魔法护盾的能力，吸收一定伤害，持续30秒；4件尖刺护甲赋予她给予近战中敌人反甲伤害,在普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传奇</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>中分别为20/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>；战吼嘲讽吸引敌人仇恨
-【人物装备】尖刺套装（无头盔），皇帝之盾，铁质变种剑
-【所需戒指】普通/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>英雄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>传</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>奇：30/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF351C75"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>180</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>【修道院介绍】这座修道院建立于独立的卢比尼亚并入帝国的时期。它成为了许多赫拉特教会圣徒的安葬之地。人们相信，他们的灵魂会保护修道院免遭灾祸与不幸……卢比尼亚逐渐与帝国其他地区隔绝。人们忘记了通往修道院的路，但我们拒绝离开这些城墙。当寒冷与饥饿渗入我们的灵魂，而墙外那恐怖的低语淹没了我们的祈祷时，我们想起赫拉特教会不仅象征仁慈——也象征净化的火焰。我们不再祈求庇护。修士长达米安的长袍早已被烟灰票黑，他宣扬了一套新的教义：将染病之人的肉身投入火焰，令其获得救赎。守护灵如今已对我们的呼唤充耳不闻。
 【副本介绍】暮焰修道院为继三元素副本哈特/哈利德/弗拉格纳之后的第四个元素副本，火元素副本，形式与古墓类似。修道院有普通/英雄/传奇三个难度，一共有12位盟军可供选择，盟军通过赫拉特祈祷戒指在不同品质的棺材中召唤，稀有品质的盟友在普通/</t>
     </r>
@@ -5968,6 +5764,210 @@
   </si>
   <si>
     <t>是</t>
+  </si>
+  <si>
+    <r>
+      <t>【人物介绍】当绝望笼罩众人时，她重新集结了营团，带领他们继续前进。敌方首领倒下了，她的族人安然无恙地走了出来。我们守护着她的遗骸，并坚信埃琳娜的烈酒守护着我们。
+【技能效果】皇帝之盾赋予她给友军提供魔法护盾的能力，吸收一定伤害，持续30秒；4件尖刺护甲赋予她给予近战中敌人反甲伤害,在普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>中分别为20/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>；战吼嘲讽吸引敌人仇恨；免疫眩晕
+【人物装备】尖刺套装（无头盔），皇帝之盾，铁质变种剑
+【所需戒指】普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>奇：30/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>180</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【人物介绍】他以如此狂烈的怒火粉碎伪神，每一锤落下，石块都被击飞百步之外。据说，锤上镶着他摧毁的第一个偶像的一块碎片。
+【技能效果】给近战中的对手施加禁疗效果；免疫眩晕
+【人物装备】圣殿骑士套装，碎颅者
+【所需戒指】普通/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>英雄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>传奇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：30/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF351C75"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>180</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -6974,7 +6974,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>4</v>
@@ -6986,7 +6986,7 @@
         <v>627</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -7028,7 +7028,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>4</v>
@@ -7040,7 +7040,7 @@
         <v>627</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="H32" s="32"/>
       <c r="I32" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -7754,7 +7754,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>4</v>
@@ -7766,7 +7766,7 @@
         <v>627</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -7791,7 +7791,7 @@
         <v>694</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="H36" s="48"/>
       <c r="I36" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="H37" s="48"/>
       <c r="I37" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="H38" s="48"/>
       <c r="I38" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="H39" s="48"/>
       <c r="I39" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="H40" s="48"/>
       <c r="I40" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H41" s="48"/>
       <c r="I41" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="H42" s="48"/>
       <c r="I42" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="H43" s="48"/>
       <c r="I43" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="H44" s="48"/>
       <c r="I44" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="H45" s="48"/>
       <c r="I45" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H46" s="48"/>
       <c r="I46" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="H47" s="48"/>
       <c r="I47" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="H48" s="48"/>
       <c r="I48" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="H49" s="48"/>
       <c r="I49" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="H50" s="48"/>
       <c r="I50" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="H51" s="48"/>
       <c r="I51" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H52" s="48"/>
       <c r="I52" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H53" s="49"/>
       <c r="I53" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -8248,7 +8248,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>4</v>
@@ -8260,7 +8260,7 @@
         <v>627</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8287,7 +8287,7 @@
         <v>692</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="H56" s="48"/>
       <c r="I56" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="H57" s="48"/>
       <c r="I57" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="H58" s="48"/>
       <c r="I58" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="H59" s="48"/>
       <c r="I59" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="H60" s="48"/>
       <c r="I60" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="H61" s="48"/>
       <c r="I61" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="H62" s="48"/>
       <c r="I62" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H63" s="48"/>
       <c r="I63" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H64" s="48"/>
       <c r="I64" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="162.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="H65" s="49"/>
       <c r="I65" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -8556,7 +8556,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>4</v>
@@ -8568,7 +8568,7 @@
         <v>627</v>
       </c>
       <c r="I66" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -8595,7 +8595,7 @@
         <v>628</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="H68" s="48"/>
       <c r="I68" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.45">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H69" s="48"/>
       <c r="I69" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H70" s="48"/>
       <c r="I70" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -8687,7 +8687,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>4</v>
@@ -8699,7 +8699,7 @@
         <v>627</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="H72" s="32"/>
       <c r="I72" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -8787,7 +8787,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>4</v>
@@ -8799,7 +8799,7 @@
         <v>627</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8807,24 +8807,24 @@
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8832,24 +8832,24 @@
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>827</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
       <c r="I77" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8857,24 +8857,24 @@
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
       <c r="I78" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8882,24 +8882,24 @@
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
       <c r="I79" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8907,24 +8907,24 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
       <c r="I80" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
@@ -8932,13 +8932,13 @@
         <v>598</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>742</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="H81" s="32"/>
       <c r="I81" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8957,24 +8957,24 @@
         <v>599</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
       <c r="I82" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8982,24 +8982,24 @@
         <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
       <c r="I83" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9007,24 +9007,24 @@
         <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>812</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -9032,13 +9032,13 @@
         <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="H85" s="32"/>
       <c r="I85" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -9057,24 +9057,24 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="H87" s="32"/>
       <c r="I87" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -9116,7 +9116,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>4</v>
@@ -9128,7 +9128,7 @@
         <v>627</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="H90" s="32"/>
       <c r="I90" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H91" s="32"/>
       <c r="I91" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H92" s="32"/>
       <c r="I92" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="H93" s="32"/>
       <c r="I93" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="H94" s="32"/>
       <c r="I94" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="H95" s="32"/>
       <c r="I95" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.45">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="H101" s="32"/>
       <c r="I101" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="H102" s="32"/>
       <c r="I102" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H103" s="32"/>
       <c r="I103" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="121.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
@@ -9815,7 +9815,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>4</v>
@@ -9827,7 +9827,7 @@
         <v>627</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="H121" s="32"/>
       <c r="I121" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.45">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.45">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="H123" s="32"/>
       <c r="I123" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.45">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="H124" s="32"/>
       <c r="I124" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.45">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="H125" s="32"/>
       <c r="I125" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="H126" s="32"/>
       <c r="I126" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="H127" s="32"/>
       <c r="I127" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="H128" s="32"/>
       <c r="I128" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.45">
@@ -10119,7 +10119,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>4</v>
@@ -10131,7 +10131,7 @@
         <v>627</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.45">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="H130" s="32"/>
       <c r="I130" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.45">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="H131" s="32"/>
       <c r="I131" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.45">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="H132" s="32"/>
       <c r="I132" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.45">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="H133" s="32"/>
       <c r="I133" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.45">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H134" s="32"/>
       <c r="I134" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.45">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="H135" s="32"/>
       <c r="I135" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="H136" s="32"/>
       <c r="I136" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.45">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="H137" s="32"/>
       <c r="I137" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.45">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="H138" s="32"/>
       <c r="I138" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.45">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.45">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="H140" s="32"/>
       <c r="I140" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.45">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="H141" s="32"/>
       <c r="I141" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.45">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="H142" s="32"/>
       <c r="I142" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="H143" s="32"/>
       <c r="I143" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.45">
@@ -10494,7 +10494,7 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>4</v>
@@ -10506,7 +10506,7 @@
         <v>627</v>
       </c>
       <c r="I144" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.45">
@@ -10514,13 +10514,13 @@
         <v>268</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="H145" s="32"/>
       <c r="I145" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.45">
@@ -10539,10 +10539,10 @@
         <v>270</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>580</v>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="H146" s="32"/>
       <c r="I146" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -10564,13 +10564,13 @@
         <v>272</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="H147" s="32"/>
       <c r="I147" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -10587,13 +10587,13 @@
         <v>273</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="H148" s="32"/>
       <c r="I148" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.45">
@@ -10610,13 +10610,13 @@
         <v>274</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="H149" s="32"/>
       <c r="I149" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10635,10 +10635,10 @@
         <v>276</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>580</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="H150" s="32"/>
       <c r="I150" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.45">
@@ -10669,7 +10669,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>4</v>
@@ -10681,7 +10681,7 @@
         <v>627</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.45">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="H152" s="32"/>
       <c r="I152" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="H153" s="32"/>
       <c r="I153" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="H154" s="32"/>
       <c r="I154" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="H155" s="32"/>
       <c r="I155" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="H156" s="32"/>
       <c r="I156" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="H157" s="32"/>
       <c r="I157" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="H158" s="32"/>
       <c r="I158" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="H159" s="32"/>
       <c r="I159" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="H161" s="32"/>
       <c r="I161" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="H162" s="32"/>
       <c r="I162" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="H163" s="32"/>
       <c r="I163" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="H164" s="32"/>
       <c r="I164" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="202.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H165" s="32"/>
       <c r="I165" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.45">
@@ -11074,7 +11074,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>4</v>
@@ -11086,7 +11086,7 @@
         <v>627</v>
       </c>
       <c r="I166" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11110,10 +11110,10 @@
         <v>701</v>
       </c>
       <c r="H167" s="50" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="H168" s="50"/>
       <c r="I168" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="94.5" x14ac:dyDescent="0.45">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H169" s="50"/>
       <c r="I169" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="81" x14ac:dyDescent="0.45">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="H170" s="50"/>
       <c r="I170" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="H171" s="50"/>
       <c r="I171" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="H172" s="50"/>
       <c r="I172" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.45">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="H173" s="50"/>
       <c r="I173" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.45">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="H174" s="50"/>
       <c r="I174" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -11319,7 +11319,7 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>4</v>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="H175" s="50"/>
       <c r="I175" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="H176" s="50"/>
       <c r="I176" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11376,14 +11376,14 @@
         <v>580</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G177" s="29" t="s">
         <v>701</v>
       </c>
       <c r="H177" s="50"/>
       <c r="I177" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="H178" s="50"/>
       <c r="I178" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="H179" s="50"/>
       <c r="I179" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="H180" s="50"/>
       <c r="I180" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="H181" s="50"/>
       <c r="I181" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11511,14 +11511,14 @@
         <v>580</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G182" s="29" t="s">
         <v>701</v>
       </c>
       <c r="H182" s="50"/>
       <c r="I182" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="H183" s="50"/>
       <c r="I183" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="H184" s="50"/>
       <c r="I184" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H185" s="50"/>
       <c r="I185" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -11619,14 +11619,14 @@
         <v>580</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>799</v>
+        <v>841</v>
       </c>
       <c r="G186" s="29" t="s">
         <v>701</v>
       </c>
       <c r="H186" s="50"/>
       <c r="I186" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11646,14 +11646,14 @@
         <v>580</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>785</v>
+        <v>842</v>
       </c>
       <c r="G187" s="29" t="s">
         <v>701</v>
       </c>
       <c r="H187" s="50"/>
       <c r="I187" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11670,7 +11670,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>4</v>
@@ -11682,7 +11682,7 @@
         <v>627</v>
       </c>
       <c r="I188" s="31" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11711,7 +11711,7 @@
         <v>645</v>
       </c>
       <c r="I189" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11734,7 +11734,7 @@
       <c r="G190" s="38"/>
       <c r="H190" s="45"/>
       <c r="I190" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11757,7 +11757,7 @@
       <c r="G191" s="38"/>
       <c r="H191" s="45"/>
       <c r="I191" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11780,7 +11780,7 @@
       <c r="G192" s="38"/>
       <c r="H192" s="45"/>
       <c r="I192" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11803,7 +11803,7 @@
       <c r="G193" s="38"/>
       <c r="H193" s="45"/>
       <c r="I193" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11826,7 +11826,7 @@
       <c r="G194" s="38"/>
       <c r="H194" s="45"/>
       <c r="I194" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11849,7 +11849,7 @@
       <c r="G195" s="38"/>
       <c r="H195" s="45"/>
       <c r="I195" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11872,7 +11872,7 @@
       <c r="G196" s="38"/>
       <c r="H196" s="45"/>
       <c r="I196" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11895,7 +11895,7 @@
       <c r="G197" s="38"/>
       <c r="H197" s="45"/>
       <c r="I197" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.45">
@@ -11918,7 +11918,7 @@
       <c r="G198" s="38"/>
       <c r="H198" s="45"/>
       <c r="I198" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -11941,7 +11941,7 @@
       <c r="G199" s="38"/>
       <c r="H199" s="45"/>
       <c r="I199" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -11964,7 +11964,7 @@
       <c r="G200" s="38"/>
       <c r="H200" s="45"/>
       <c r="I200" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -11989,7 +11989,7 @@
       <c r="G201" s="38"/>
       <c r="H201" s="45"/>
       <c r="I201" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -12014,7 +12014,7 @@
       <c r="G202" s="38"/>
       <c r="H202" s="45"/>
       <c r="I202" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -12037,7 +12037,7 @@
       <c r="G203" s="38"/>
       <c r="H203" s="45"/>
       <c r="I203" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -12062,7 +12062,7 @@
       <c r="G204" s="39"/>
       <c r="H204" s="46"/>
       <c r="I204" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7208CD8-F2A2-4F29-8AF8-49AAAC8D32C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6A337B-CE4E-4953-8691-0CC8AC8EA61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5904,7 +5904,7 @@
   <si>
     <r>
       <t>【人物介绍】他以如此狂烈的怒火粉碎伪神，每一锤落下，石块都被击飞百步之外。据说，锤上镶着他摧毁的第一个偶像的一块碎片。
-【技能效果】给近战中的对手施加禁疗效果；免疫眩晕
+【技能效果】给近战中的对手施加禁疗效果；概率眩晕敌人，且自身免疫眩晕
 【人物装备】圣殿骑士套装，碎颅者
 【所需戒指】普通/</t>
     </r>
@@ -6469,7 +6469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6620,6 +6620,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6959,6 +6962,7 @@
       <c r="F1" s="41"/>
       <c r="G1" s="42"/>
       <c r="H1" s="43"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -7010,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="32"/>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7062,7 +7066,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32"/>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7085,7 +7089,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="32"/>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7108,7 +7112,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="32"/>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7131,7 +7135,7 @@
         <v>17</v>
       </c>
       <c r="H8" s="32"/>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7156,7 +7160,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="32"/>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7181,7 +7185,7 @@
         <v>637</v>
       </c>
       <c r="H10" s="32"/>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7204,7 +7208,7 @@
         <v>24</v>
       </c>
       <c r="H11" s="32"/>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7227,7 +7231,7 @@
         <v>670</v>
       </c>
       <c r="H12" s="32"/>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7250,7 +7254,7 @@
         <v>671</v>
       </c>
       <c r="H13" s="32"/>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7273,7 +7277,7 @@
         <v>679</v>
       </c>
       <c r="H14" s="32"/>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7296,7 +7300,7 @@
         <v>654</v>
       </c>
       <c r="H15" s="32"/>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7321,7 +7325,7 @@
         <v>32</v>
       </c>
       <c r="H16" s="32"/>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7344,7 +7348,7 @@
         <v>34</v>
       </c>
       <c r="H17" s="32"/>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7369,7 +7373,7 @@
         <v>658</v>
       </c>
       <c r="H18" s="32"/>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7392,7 +7396,7 @@
         <v>38</v>
       </c>
       <c r="H19" s="32"/>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7417,7 +7421,7 @@
         <v>584</v>
       </c>
       <c r="H20" s="32"/>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7440,7 +7444,7 @@
         <v>655</v>
       </c>
       <c r="H21" s="32"/>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7465,7 +7469,7 @@
         <v>680</v>
       </c>
       <c r="H22" s="32"/>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7490,7 +7494,7 @@
         <v>8</v>
       </c>
       <c r="H23" s="32"/>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7515,7 +7519,7 @@
         <v>653</v>
       </c>
       <c r="H24" s="32"/>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7540,7 +7544,7 @@
         <v>657</v>
       </c>
       <c r="H25" s="32"/>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7565,7 +7569,7 @@
         <v>656</v>
       </c>
       <c r="H26" s="32"/>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7590,7 +7594,7 @@
         <v>672</v>
       </c>
       <c r="H27" s="32"/>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7613,7 +7617,7 @@
         <v>59</v>
       </c>
       <c r="H28" s="32"/>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7636,7 +7640,7 @@
         <v>64</v>
       </c>
       <c r="H29" s="32"/>
-      <c r="I29" s="5" t="s">
+      <c r="I29" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7661,7 +7665,7 @@
         <v>67</v>
       </c>
       <c r="H30" s="32"/>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7686,7 +7690,7 @@
         <v>70</v>
       </c>
       <c r="H31" s="32"/>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7711,7 +7715,7 @@
         <v>667</v>
       </c>
       <c r="H32" s="32"/>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7736,7 +7740,7 @@
         <v>75</v>
       </c>
       <c r="H33" s="32"/>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7790,7 +7794,7 @@
       <c r="H35" s="47" t="s">
         <v>694</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7813,7 +7817,7 @@
         <v>78</v>
       </c>
       <c r="H36" s="48"/>
-      <c r="I36" s="5" t="s">
+      <c r="I36" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7836,7 +7840,7 @@
         <v>682</v>
       </c>
       <c r="H37" s="48"/>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7861,7 +7865,7 @@
         <v>683</v>
       </c>
       <c r="H38" s="48"/>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7884,7 +7888,7 @@
         <v>684</v>
       </c>
       <c r="H39" s="48"/>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7909,7 +7913,7 @@
         <v>685</v>
       </c>
       <c r="H40" s="48"/>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7932,7 +7936,7 @@
         <v>686</v>
       </c>
       <c r="H41" s="48"/>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7955,7 +7959,7 @@
         <v>683</v>
       </c>
       <c r="H42" s="48"/>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7980,7 +7984,7 @@
         <v>684</v>
       </c>
       <c r="H43" s="48"/>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8005,7 +8009,7 @@
         <v>687</v>
       </c>
       <c r="H44" s="48"/>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8030,7 +8034,7 @@
         <v>687</v>
       </c>
       <c r="H45" s="48"/>
-      <c r="I45" s="5" t="s">
+      <c r="I45" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8055,7 +8059,7 @@
         <v>687</v>
       </c>
       <c r="H46" s="48"/>
-      <c r="I46" s="5" t="s">
+      <c r="I46" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8080,7 +8084,7 @@
         <v>687</v>
       </c>
       <c r="H47" s="48"/>
-      <c r="I47" s="5" t="s">
+      <c r="I47" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8105,7 +8109,7 @@
         <v>78</v>
       </c>
       <c r="H48" s="48"/>
-      <c r="I48" s="5" t="s">
+      <c r="I48" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8130,7 +8134,7 @@
         <v>687</v>
       </c>
       <c r="H49" s="48"/>
-      <c r="I49" s="5" t="s">
+      <c r="I49" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8155,7 +8159,7 @@
         <v>688</v>
       </c>
       <c r="H50" s="48"/>
-      <c r="I50" s="5" t="s">
+      <c r="I50" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8180,7 +8184,7 @@
         <v>689</v>
       </c>
       <c r="H51" s="48"/>
-      <c r="I51" s="5" t="s">
+      <c r="I51" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8205,7 +8209,7 @@
         <v>690</v>
       </c>
       <c r="H52" s="48"/>
-      <c r="I52" s="5" t="s">
+      <c r="I52" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8230,7 +8234,7 @@
         <v>691</v>
       </c>
       <c r="H53" s="49"/>
-      <c r="I53" s="5" t="s">
+      <c r="I53" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8286,7 +8290,7 @@
       <c r="H55" s="47" t="s">
         <v>692</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="I55" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8311,7 +8315,7 @@
         <v>674</v>
       </c>
       <c r="H56" s="48"/>
-      <c r="I56" s="5" t="s">
+      <c r="I56" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8336,7 +8340,7 @@
         <v>675</v>
       </c>
       <c r="H57" s="48"/>
-      <c r="I57" s="5" t="s">
+      <c r="I57" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8361,7 +8365,7 @@
         <v>676</v>
       </c>
       <c r="H58" s="48"/>
-      <c r="I58" s="5" t="s">
+      <c r="I58" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8386,7 +8390,7 @@
         <v>677</v>
       </c>
       <c r="H59" s="48"/>
-      <c r="I59" s="5" t="s">
+      <c r="I59" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8411,7 +8415,7 @@
         <v>674</v>
       </c>
       <c r="H60" s="48"/>
-      <c r="I60" s="5" t="s">
+      <c r="I60" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8436,7 +8440,7 @@
         <v>675</v>
       </c>
       <c r="H61" s="48"/>
-      <c r="I61" s="5" t="s">
+      <c r="I61" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8461,7 +8465,7 @@
         <v>678</v>
       </c>
       <c r="H62" s="48"/>
-      <c r="I62" s="5" t="s">
+      <c r="I62" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8486,7 +8490,7 @@
         <v>675</v>
       </c>
       <c r="H63" s="48"/>
-      <c r="I63" s="5" t="s">
+      <c r="I63" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8513,7 +8517,7 @@
         <v>675</v>
       </c>
       <c r="H64" s="48"/>
-      <c r="I64" s="5" t="s">
+      <c r="I64" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8538,7 +8542,7 @@
         <v>673</v>
       </c>
       <c r="H65" s="49"/>
-      <c r="I65" s="5" t="s">
+      <c r="I65" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8594,7 +8598,7 @@
       <c r="H67" s="50" t="s">
         <v>628</v>
       </c>
-      <c r="I67" s="5" t="s">
+      <c r="I67" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8619,7 +8623,7 @@
         <v>136</v>
       </c>
       <c r="H68" s="48"/>
-      <c r="I68" s="5" t="s">
+      <c r="I68" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8644,7 +8648,7 @@
         <v>136</v>
       </c>
       <c r="H69" s="48"/>
-      <c r="I69" s="5" t="s">
+      <c r="I69" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8669,7 +8673,7 @@
         <v>136</v>
       </c>
       <c r="H70" s="48"/>
-      <c r="I70" s="5" t="s">
+      <c r="I70" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8721,7 +8725,7 @@
         <v>143</v>
       </c>
       <c r="H72" s="32"/>
-      <c r="I72" s="5" t="s">
+      <c r="I72" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8744,7 +8748,7 @@
         <v>143</v>
       </c>
       <c r="H73" s="32"/>
-      <c r="I73" s="5" t="s">
+      <c r="I73" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8769,7 +8773,7 @@
         <v>143</v>
       </c>
       <c r="H74" s="32"/>
-      <c r="I74" s="5" t="s">
+      <c r="I74" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8823,7 +8827,7 @@
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
-      <c r="I76" s="5" t="s">
+      <c r="I76" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8848,7 +8852,7 @@
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
-      <c r="I77" s="5" t="s">
+      <c r="I77" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8873,7 +8877,7 @@
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
-      <c r="I78" s="5" t="s">
+      <c r="I78" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8898,7 +8902,7 @@
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
-      <c r="I79" s="5" t="s">
+      <c r="I79" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8923,7 +8927,7 @@
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
-      <c r="I80" s="5" t="s">
+      <c r="I80" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8948,7 +8952,7 @@
         <v>150</v>
       </c>
       <c r="H81" s="32"/>
-      <c r="I81" s="5" t="s">
+      <c r="I81" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8973,7 +8977,7 @@
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
-      <c r="I82" s="5" t="s">
+      <c r="I82" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8998,7 +9002,7 @@
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
-      <c r="I83" s="5" t="s">
+      <c r="I83" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -9023,7 +9027,7 @@
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
-      <c r="I84" s="5" t="s">
+      <c r="I84" s="51" t="s">
         <v>840</v>
       </c>
     </row>
@@ -9048,7 +9052,7 @@
         <v>150</v>
       </c>
       <c r="H85" s="32"/>
-      <c r="I85" s="5" t="s">
+      <c r="I85" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9073,7 +9077,7 @@
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
-      <c r="I86" s="5" t="s">
+      <c r="I86" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9098,7 +9102,7 @@
         <v>150</v>
       </c>
       <c r="H87" s="32"/>
-      <c r="I87" s="5" t="s">
+      <c r="I87" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9152,7 +9156,7 @@
         <v>169</v>
       </c>
       <c r="H89" s="32"/>
-      <c r="I89" s="5" t="s">
+      <c r="I89" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9175,7 +9179,7 @@
         <v>171</v>
       </c>
       <c r="H90" s="32"/>
-      <c r="I90" s="5" t="s">
+      <c r="I90" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9198,7 +9202,7 @@
         <v>173</v>
       </c>
       <c r="H91" s="32"/>
-      <c r="I91" s="5" t="s">
+      <c r="I91" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9221,7 +9225,7 @@
         <v>173</v>
       </c>
       <c r="H92" s="32"/>
-      <c r="I92" s="5" t="s">
+      <c r="I92" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9244,7 +9248,7 @@
         <v>173</v>
       </c>
       <c r="H93" s="32"/>
-      <c r="I93" s="5" t="s">
+      <c r="I93" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9269,7 +9273,7 @@
         <v>179</v>
       </c>
       <c r="H94" s="32"/>
-      <c r="I94" s="5" t="s">
+      <c r="I94" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9292,7 +9296,7 @@
         <v>181</v>
       </c>
       <c r="H95" s="32"/>
-      <c r="I95" s="5" t="s">
+      <c r="I95" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9317,7 +9321,7 @@
         <v>184</v>
       </c>
       <c r="H96" s="32"/>
-      <c r="I96" s="5" t="s">
+      <c r="I96" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9340,7 +9344,7 @@
         <v>187</v>
       </c>
       <c r="H97" s="32"/>
-      <c r="I97" s="5" t="s">
+      <c r="I97" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9363,7 +9367,7 @@
         <v>189</v>
       </c>
       <c r="H98" s="32"/>
-      <c r="I98" s="5" t="s">
+      <c r="I98" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9388,11 +9392,11 @@
         <v>189</v>
       </c>
       <c r="H99" s="32"/>
-      <c r="I99" s="5" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I99" s="51" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="11" t="s">
         <v>192</v>
       </c>
@@ -9413,7 +9417,7 @@
         <v>194</v>
       </c>
       <c r="H100" s="32"/>
-      <c r="I100" s="5" t="s">
+      <c r="I100" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9438,7 +9442,7 @@
         <v>197</v>
       </c>
       <c r="H101" s="32"/>
-      <c r="I101" s="5" t="s">
+      <c r="I101" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9463,7 +9467,7 @@
         <v>197</v>
       </c>
       <c r="H102" s="32"/>
-      <c r="I102" s="5" t="s">
+      <c r="I102" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9488,7 +9492,7 @@
         <v>202</v>
       </c>
       <c r="H103" s="32"/>
-      <c r="I103" s="5" t="s">
+      <c r="I103" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9511,7 +9515,7 @@
         <v>204</v>
       </c>
       <c r="H104" s="32"/>
-      <c r="I104" s="5" t="s">
+      <c r="I104" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9534,7 +9538,7 @@
         <v>207</v>
       </c>
       <c r="H105" s="32"/>
-      <c r="I105" s="5" t="s">
+      <c r="I105" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9557,7 +9561,7 @@
         <v>209</v>
       </c>
       <c r="H106" s="32"/>
-      <c r="I106" s="5" t="s">
+      <c r="I106" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9580,7 +9584,7 @@
         <v>209</v>
       </c>
       <c r="H107" s="32"/>
-      <c r="I107" s="5" t="s">
+      <c r="I107" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9603,7 +9607,7 @@
         <v>209</v>
       </c>
       <c r="H108" s="32"/>
-      <c r="I108" s="5" t="s">
+      <c r="I108" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9626,7 +9630,7 @@
         <v>213</v>
       </c>
       <c r="H109" s="32"/>
-      <c r="I109" s="5" t="s">
+      <c r="I109" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9649,7 +9653,7 @@
         <v>215</v>
       </c>
       <c r="H110" s="32"/>
-      <c r="I110" s="5" t="s">
+      <c r="I110" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9672,7 +9676,7 @@
         <v>217</v>
       </c>
       <c r="H111" s="32"/>
-      <c r="I111" s="5" t="s">
+      <c r="I111" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9697,7 +9701,7 @@
         <v>220</v>
       </c>
       <c r="H112" s="32"/>
-      <c r="I112" s="5" t="s">
+      <c r="I112" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9722,7 +9726,7 @@
         <v>194</v>
       </c>
       <c r="H113" s="32"/>
-      <c r="I113" s="5" t="s">
+      <c r="I113" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9747,7 +9751,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="32"/>
-      <c r="I114" s="5" t="s">
+      <c r="I114" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9772,7 +9776,7 @@
         <v>229</v>
       </c>
       <c r="H115" s="32"/>
-      <c r="I115" s="5" t="s">
+      <c r="I115" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9797,7 +9801,7 @@
         <v>231</v>
       </c>
       <c r="H116" s="32"/>
-      <c r="I116" s="5" t="s">
+      <c r="I116" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9851,7 +9855,7 @@
         <v>588</v>
       </c>
       <c r="H118" s="32"/>
-      <c r="I118" s="5" t="s">
+      <c r="I118" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9876,7 +9880,7 @@
         <v>588</v>
       </c>
       <c r="H119" s="32"/>
-      <c r="I119" s="5" t="s">
+      <c r="I119" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9901,7 +9905,7 @@
         <v>588</v>
       </c>
       <c r="H120" s="32"/>
-      <c r="I120" s="5" t="s">
+      <c r="I120" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9926,7 +9930,7 @@
         <v>588</v>
       </c>
       <c r="H121" s="32"/>
-      <c r="I121" s="5" t="s">
+      <c r="I121" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9951,7 +9955,7 @@
         <v>588</v>
       </c>
       <c r="H122" s="32"/>
-      <c r="I122" s="5" t="s">
+      <c r="I122" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9976,7 +9980,7 @@
         <v>588</v>
       </c>
       <c r="H123" s="32"/>
-      <c r="I123" s="5" t="s">
+      <c r="I123" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10001,7 +10005,7 @@
         <v>588</v>
       </c>
       <c r="H124" s="32"/>
-      <c r="I124" s="5" t="s">
+      <c r="I124" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10026,7 +10030,7 @@
         <v>588</v>
       </c>
       <c r="H125" s="32"/>
-      <c r="I125" s="5" t="s">
+      <c r="I125" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10051,7 +10055,7 @@
         <v>588</v>
       </c>
       <c r="H126" s="32"/>
-      <c r="I126" s="5" t="s">
+      <c r="I126" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10076,7 +10080,7 @@
         <v>588</v>
       </c>
       <c r="H127" s="32"/>
-      <c r="I127" s="5" t="s">
+      <c r="I127" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10101,7 +10105,7 @@
         <v>588</v>
       </c>
       <c r="H128" s="32"/>
-      <c r="I128" s="5" t="s">
+      <c r="I128" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10155,7 +10159,7 @@
         <v>235</v>
       </c>
       <c r="H130" s="32"/>
-      <c r="I130" s="5" t="s">
+      <c r="I130" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10178,7 +10182,7 @@
         <v>61</v>
       </c>
       <c r="H131" s="32"/>
-      <c r="I131" s="5" t="s">
+      <c r="I131" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10201,7 +10205,7 @@
         <v>241</v>
       </c>
       <c r="H132" s="32"/>
-      <c r="I132" s="5" t="s">
+      <c r="I132" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10226,7 +10230,7 @@
         <v>244</v>
       </c>
       <c r="H133" s="32"/>
-      <c r="I133" s="5" t="s">
+      <c r="I133" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10249,7 +10253,7 @@
         <v>244</v>
       </c>
       <c r="H134" s="32"/>
-      <c r="I134" s="5" t="s">
+      <c r="I134" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10274,7 +10278,7 @@
         <v>244</v>
       </c>
       <c r="H135" s="32"/>
-      <c r="I135" s="5" t="s">
+      <c r="I135" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10299,7 +10303,7 @@
         <v>250</v>
       </c>
       <c r="H136" s="32"/>
-      <c r="I136" s="5" t="s">
+      <c r="I136" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10326,7 +10330,7 @@
         <v>250</v>
       </c>
       <c r="H137" s="32"/>
-      <c r="I137" s="5" t="s">
+      <c r="I137" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10351,7 +10355,7 @@
         <v>256</v>
       </c>
       <c r="H138" s="32"/>
-      <c r="I138" s="5" t="s">
+      <c r="I138" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10376,7 +10380,7 @@
         <v>698</v>
       </c>
       <c r="H139" s="32"/>
-      <c r="I139" s="5" t="s">
+      <c r="I139" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10401,7 +10405,7 @@
         <v>258</v>
       </c>
       <c r="H140" s="32"/>
-      <c r="I140" s="5" t="s">
+      <c r="I140" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10426,7 +10430,7 @@
         <v>261</v>
       </c>
       <c r="H141" s="32"/>
-      <c r="I141" s="5" t="s">
+      <c r="I141" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10451,7 +10455,7 @@
         <v>264</v>
       </c>
       <c r="H142" s="32"/>
-      <c r="I142" s="5" t="s">
+      <c r="I142" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10476,7 +10480,7 @@
         <v>261</v>
       </c>
       <c r="H143" s="32"/>
-      <c r="I143" s="5" t="s">
+      <c r="I143" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10530,7 +10534,7 @@
         <v>267</v>
       </c>
       <c r="H145" s="32"/>
-      <c r="I145" s="5" t="s">
+      <c r="I145" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10555,7 +10559,7 @@
         <v>267</v>
       </c>
       <c r="H146" s="32"/>
-      <c r="I146" s="5" t="s">
+      <c r="I146" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10578,7 +10582,7 @@
         <v>267</v>
       </c>
       <c r="H147" s="32"/>
-      <c r="I147" s="5" t="s">
+      <c r="I147" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10601,7 +10605,7 @@
         <v>267</v>
       </c>
       <c r="H148" s="32"/>
-      <c r="I148" s="5" t="s">
+      <c r="I148" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10626,7 +10630,7 @@
         <v>267</v>
       </c>
       <c r="H149" s="32"/>
-      <c r="I149" s="5" t="s">
+      <c r="I149" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10651,7 +10655,7 @@
         <v>267</v>
       </c>
       <c r="H150" s="32"/>
-      <c r="I150" s="5" t="s">
+      <c r="I150" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10705,7 +10709,7 @@
         <v>284</v>
       </c>
       <c r="H152" s="32"/>
-      <c r="I152" s="5" t="s">
+      <c r="I152" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10732,7 +10736,7 @@
         <v>279</v>
       </c>
       <c r="H153" s="32"/>
-      <c r="I153" s="5" t="s">
+      <c r="I153" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10759,7 +10763,7 @@
         <v>298</v>
       </c>
       <c r="H154" s="32"/>
-      <c r="I154" s="5" t="s">
+      <c r="I154" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10786,7 +10790,7 @@
         <v>298</v>
       </c>
       <c r="H155" s="32"/>
-      <c r="I155" s="5" t="s">
+      <c r="I155" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10813,7 +10817,7 @@
         <v>298</v>
       </c>
       <c r="H156" s="32"/>
-      <c r="I156" s="5" t="s">
+      <c r="I156" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10840,7 +10844,7 @@
         <v>298</v>
       </c>
       <c r="H157" s="32"/>
-      <c r="I157" s="5" t="s">
+      <c r="I157" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10867,7 +10871,7 @@
         <v>298</v>
       </c>
       <c r="H158" s="32"/>
-      <c r="I158" s="5" t="s">
+      <c r="I158" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10894,7 +10898,7 @@
         <v>298</v>
       </c>
       <c r="H159" s="32"/>
-      <c r="I159" s="5" t="s">
+      <c r="I159" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10921,7 +10925,7 @@
         <v>298</v>
       </c>
       <c r="H160" s="32"/>
-      <c r="I160" s="5" t="s">
+      <c r="I160" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10948,7 +10952,7 @@
         <v>298</v>
       </c>
       <c r="H161" s="32"/>
-      <c r="I161" s="5" t="s">
+      <c r="I161" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10975,7 +10979,7 @@
         <v>298</v>
       </c>
       <c r="H162" s="32"/>
-      <c r="I162" s="5" t="s">
+      <c r="I162" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11002,7 +11006,7 @@
         <v>284</v>
       </c>
       <c r="H163" s="32"/>
-      <c r="I163" s="5" t="s">
+      <c r="I163" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11029,7 +11033,7 @@
         <v>298</v>
       </c>
       <c r="H164" s="32"/>
-      <c r="I164" s="5" t="s">
+      <c r="I164" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11056,7 +11060,7 @@
         <v>279</v>
       </c>
       <c r="H165" s="32"/>
-      <c r="I165" s="5" t="s">
+      <c r="I165" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11112,7 +11116,7 @@
       <c r="H167" s="50" t="s">
         <v>798</v>
       </c>
-      <c r="I167" s="5" t="s">
+      <c r="I167" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11139,7 +11143,7 @@
         <v>701</v>
       </c>
       <c r="H168" s="50"/>
-      <c r="I168" s="5" t="s">
+      <c r="I168" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11166,7 +11170,7 @@
         <v>701</v>
       </c>
       <c r="H169" s="50"/>
-      <c r="I169" s="5" t="s">
+      <c r="I169" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11193,7 +11197,7 @@
         <v>701</v>
       </c>
       <c r="H170" s="50"/>
-      <c r="I170" s="5" t="s">
+      <c r="I170" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11220,7 +11224,7 @@
         <v>701</v>
       </c>
       <c r="H171" s="50"/>
-      <c r="I171" s="5" t="s">
+      <c r="I171" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11247,7 +11251,7 @@
         <v>701</v>
       </c>
       <c r="H172" s="50"/>
-      <c r="I172" s="5" t="s">
+      <c r="I172" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11274,7 +11278,7 @@
         <v>701</v>
       </c>
       <c r="H173" s="50"/>
-      <c r="I173" s="5" t="s">
+      <c r="I173" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11301,7 +11305,7 @@
         <v>701</v>
       </c>
       <c r="H174" s="50"/>
-      <c r="I174" s="5" t="s">
+      <c r="I174" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11328,7 +11332,7 @@
         <v>5</v>
       </c>
       <c r="H175" s="50"/>
-      <c r="I175" s="5" t="s">
+      <c r="I175" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11355,7 +11359,7 @@
         <v>701</v>
       </c>
       <c r="H176" s="50"/>
-      <c r="I176" s="5" t="s">
+      <c r="I176" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11382,7 +11386,7 @@
         <v>701</v>
       </c>
       <c r="H177" s="50"/>
-      <c r="I177" s="5" t="s">
+      <c r="I177" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11409,7 +11413,7 @@
         <v>701</v>
       </c>
       <c r="H178" s="50"/>
-      <c r="I178" s="5" t="s">
+      <c r="I178" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11436,7 +11440,7 @@
         <v>701</v>
       </c>
       <c r="H179" s="50"/>
-      <c r="I179" s="5" t="s">
+      <c r="I179" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11463,7 +11467,7 @@
         <v>701</v>
       </c>
       <c r="H180" s="50"/>
-      <c r="I180" s="5" t="s">
+      <c r="I180" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11490,7 +11494,7 @@
         <v>701</v>
       </c>
       <c r="H181" s="50"/>
-      <c r="I181" s="5" t="s">
+      <c r="I181" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11517,7 +11521,7 @@
         <v>701</v>
       </c>
       <c r="H182" s="50"/>
-      <c r="I182" s="5" t="s">
+      <c r="I182" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11544,7 +11548,7 @@
         <v>701</v>
       </c>
       <c r="H183" s="50"/>
-      <c r="I183" s="5" t="s">
+      <c r="I183" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11571,7 +11575,7 @@
         <v>701</v>
       </c>
       <c r="H184" s="50"/>
-      <c r="I184" s="5" t="s">
+      <c r="I184" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11598,7 +11602,7 @@
         <v>701</v>
       </c>
       <c r="H185" s="50"/>
-      <c r="I185" s="5" t="s">
+      <c r="I185" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11625,7 +11629,7 @@
         <v>701</v>
       </c>
       <c r="H186" s="50"/>
-      <c r="I186" s="5" t="s">
+      <c r="I186" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11652,7 +11656,7 @@
         <v>701</v>
       </c>
       <c r="H187" s="50"/>
-      <c r="I187" s="5" t="s">
+      <c r="I187" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11710,7 +11714,7 @@
       <c r="H189" s="44" t="s">
         <v>645</v>
       </c>
-      <c r="I189" s="5" t="s">
+      <c r="I189" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11733,7 +11737,7 @@
       </c>
       <c r="G190" s="38"/>
       <c r="H190" s="45"/>
-      <c r="I190" s="5" t="s">
+      <c r="I190" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11756,7 +11760,7 @@
       </c>
       <c r="G191" s="38"/>
       <c r="H191" s="45"/>
-      <c r="I191" s="5" t="s">
+      <c r="I191" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11779,7 +11783,7 @@
       </c>
       <c r="G192" s="38"/>
       <c r="H192" s="45"/>
-      <c r="I192" s="5" t="s">
+      <c r="I192" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11802,7 +11806,7 @@
       </c>
       <c r="G193" s="38"/>
       <c r="H193" s="45"/>
-      <c r="I193" s="5" t="s">
+      <c r="I193" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11825,7 +11829,7 @@
       </c>
       <c r="G194" s="38"/>
       <c r="H194" s="45"/>
-      <c r="I194" s="5" t="s">
+      <c r="I194" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11848,7 +11852,7 @@
       </c>
       <c r="G195" s="38"/>
       <c r="H195" s="45"/>
-      <c r="I195" s="5" t="s">
+      <c r="I195" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11871,7 +11875,7 @@
       </c>
       <c r="G196" s="38"/>
       <c r="H196" s="45"/>
-      <c r="I196" s="5" t="s">
+      <c r="I196" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11894,11 +11898,11 @@
       </c>
       <c r="G197" s="38"/>
       <c r="H197" s="45"/>
-      <c r="I197" s="5" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I197" s="51" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
         <v>338</v>
       </c>
@@ -11917,7 +11921,7 @@
       </c>
       <c r="G198" s="38"/>
       <c r="H198" s="45"/>
-      <c r="I198" s="5" t="s">
+      <c r="I198" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11940,7 +11944,7 @@
       </c>
       <c r="G199" s="38"/>
       <c r="H199" s="45"/>
-      <c r="I199" s="5" t="s">
+      <c r="I199" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11963,7 +11967,7 @@
       </c>
       <c r="G200" s="38"/>
       <c r="H200" s="45"/>
-      <c r="I200" s="5" t="s">
+      <c r="I200" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11988,7 +11992,7 @@
       </c>
       <c r="G201" s="38"/>
       <c r="H201" s="45"/>
-      <c r="I201" s="5" t="s">
+      <c r="I201" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12013,7 +12017,7 @@
       </c>
       <c r="G202" s="38"/>
       <c r="H202" s="45"/>
-      <c r="I202" s="5" t="s">
+      <c r="I202" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12036,7 +12040,7 @@
       </c>
       <c r="G203" s="38"/>
       <c r="H203" s="45"/>
-      <c r="I203" s="5" t="s">
+      <c r="I203" s="51" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12061,7 +12065,7 @@
       </c>
       <c r="G204" s="39"/>
       <c r="H204" s="46"/>
-      <c r="I204" s="5" t="s">
+      <c r="I204" s="51" t="s">
         <v>839</v>
       </c>
     </row>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6A337B-CE4E-4953-8691-0CC8AC8EA61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D029548F-D10A-4763-8D53-ADDA1118DBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="850">
   <si>
     <t>家里</t>
   </si>
@@ -5968,6 +5968,27 @@
       </rPr>
       <t>180</t>
     </r>
+  </si>
+  <si>
+    <t>200，待测，待测</t>
+  </si>
+  <si>
+    <t>250，待测，待测</t>
+  </si>
+  <si>
+    <t>500，待测，待测</t>
+  </si>
+  <si>
+    <t>300，待测，待测</t>
+  </si>
+  <si>
+    <t>400，待测，待测</t>
+  </si>
+  <si>
+    <t>180，待测，待测</t>
+  </si>
+  <si>
+    <t>220，待测，待测</t>
   </si>
 </sst>
 </file>
@@ -6579,6 +6600,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6620,9 +6644,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6952,17 +6973,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>712</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="51"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -7014,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="32"/>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7066,7 +7087,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="32"/>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7089,7 +7110,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="32"/>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7112,7 +7133,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="32"/>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7135,7 +7156,7 @@
         <v>17</v>
       </c>
       <c r="H8" s="32"/>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7160,7 +7181,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="32"/>
-      <c r="I9" s="51" t="s">
+      <c r="I9" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7185,7 +7206,7 @@
         <v>637</v>
       </c>
       <c r="H10" s="32"/>
-      <c r="I10" s="51" t="s">
+      <c r="I10" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7208,7 +7229,7 @@
         <v>24</v>
       </c>
       <c r="H11" s="32"/>
-      <c r="I11" s="51" t="s">
+      <c r="I11" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7231,7 +7252,7 @@
         <v>670</v>
       </c>
       <c r="H12" s="32"/>
-      <c r="I12" s="51" t="s">
+      <c r="I12" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7254,7 +7275,7 @@
         <v>671</v>
       </c>
       <c r="H13" s="32"/>
-      <c r="I13" s="51" t="s">
+      <c r="I13" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7277,7 +7298,7 @@
         <v>679</v>
       </c>
       <c r="H14" s="32"/>
-      <c r="I14" s="51" t="s">
+      <c r="I14" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7300,7 +7321,7 @@
         <v>654</v>
       </c>
       <c r="H15" s="32"/>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7325,7 +7346,7 @@
         <v>32</v>
       </c>
       <c r="H16" s="32"/>
-      <c r="I16" s="51" t="s">
+      <c r="I16" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7348,7 +7369,7 @@
         <v>34</v>
       </c>
       <c r="H17" s="32"/>
-      <c r="I17" s="51" t="s">
+      <c r="I17" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7373,7 +7394,7 @@
         <v>658</v>
       </c>
       <c r="H18" s="32"/>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7396,7 +7417,7 @@
         <v>38</v>
       </c>
       <c r="H19" s="32"/>
-      <c r="I19" s="51" t="s">
+      <c r="I19" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7421,7 +7442,7 @@
         <v>584</v>
       </c>
       <c r="H20" s="32"/>
-      <c r="I20" s="51" t="s">
+      <c r="I20" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7444,7 +7465,7 @@
         <v>655</v>
       </c>
       <c r="H21" s="32"/>
-      <c r="I21" s="51" t="s">
+      <c r="I21" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7469,7 +7490,7 @@
         <v>680</v>
       </c>
       <c r="H22" s="32"/>
-      <c r="I22" s="51" t="s">
+      <c r="I22" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7494,7 +7515,7 @@
         <v>8</v>
       </c>
       <c r="H23" s="32"/>
-      <c r="I23" s="51" t="s">
+      <c r="I23" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7519,7 +7540,7 @@
         <v>653</v>
       </c>
       <c r="H24" s="32"/>
-      <c r="I24" s="51" t="s">
+      <c r="I24" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7544,7 +7565,7 @@
         <v>657</v>
       </c>
       <c r="H25" s="32"/>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7569,7 +7590,7 @@
         <v>656</v>
       </c>
       <c r="H26" s="32"/>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7594,7 +7615,7 @@
         <v>672</v>
       </c>
       <c r="H27" s="32"/>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7617,7 +7638,7 @@
         <v>59</v>
       </c>
       <c r="H28" s="32"/>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7640,7 +7661,7 @@
         <v>64</v>
       </c>
       <c r="H29" s="32"/>
-      <c r="I29" s="51" t="s">
+      <c r="I29" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7665,7 +7686,7 @@
         <v>67</v>
       </c>
       <c r="H30" s="32"/>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7690,7 +7711,7 @@
         <v>70</v>
       </c>
       <c r="H31" s="32"/>
-      <c r="I31" s="51" t="s">
+      <c r="I31" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7715,7 +7736,7 @@
         <v>667</v>
       </c>
       <c r="H32" s="32"/>
-      <c r="I32" s="51" t="s">
+      <c r="I32" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7740,7 +7761,7 @@
         <v>75</v>
       </c>
       <c r="H33" s="32"/>
-      <c r="I33" s="51" t="s">
+      <c r="I33" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7791,10 +7812,10 @@
       <c r="G35" s="19" t="s">
         <v>681</v>
       </c>
-      <c r="H35" s="47" t="s">
+      <c r="H35" s="48" t="s">
         <v>694</v>
       </c>
-      <c r="I35" s="51" t="s">
+      <c r="I35" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7816,8 +7837,8 @@
       <c r="G36" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="48"/>
-      <c r="I36" s="51" t="s">
+      <c r="H36" s="49"/>
+      <c r="I36" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7839,8 +7860,8 @@
       <c r="G37" s="19" t="s">
         <v>682</v>
       </c>
-      <c r="H37" s="48"/>
-      <c r="I37" s="51" t="s">
+      <c r="H37" s="49"/>
+      <c r="I37" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7864,8 +7885,8 @@
       <c r="G38" s="19" t="s">
         <v>683</v>
       </c>
-      <c r="H38" s="48"/>
-      <c r="I38" s="51" t="s">
+      <c r="H38" s="49"/>
+      <c r="I38" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7887,8 +7908,8 @@
       <c r="G39" s="19" t="s">
         <v>684</v>
       </c>
-      <c r="H39" s="48"/>
-      <c r="I39" s="51" t="s">
+      <c r="H39" s="49"/>
+      <c r="I39" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7912,8 +7933,8 @@
       <c r="G40" s="19" t="s">
         <v>685</v>
       </c>
-      <c r="H40" s="48"/>
-      <c r="I40" s="51" t="s">
+      <c r="H40" s="49"/>
+      <c r="I40" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7935,8 +7956,8 @@
       <c r="G41" s="19" t="s">
         <v>686</v>
       </c>
-      <c r="H41" s="48"/>
-      <c r="I41" s="51" t="s">
+      <c r="H41" s="49"/>
+      <c r="I41" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7958,8 +7979,8 @@
       <c r="G42" s="19" t="s">
         <v>683</v>
       </c>
-      <c r="H42" s="48"/>
-      <c r="I42" s="51" t="s">
+      <c r="H42" s="49"/>
+      <c r="I42" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7983,8 +8004,8 @@
       <c r="G43" s="19" t="s">
         <v>684</v>
       </c>
-      <c r="H43" s="48"/>
-      <c r="I43" s="51" t="s">
+      <c r="H43" s="49"/>
+      <c r="I43" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8008,8 +8029,8 @@
       <c r="G44" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H44" s="48"/>
-      <c r="I44" s="51" t="s">
+      <c r="H44" s="49"/>
+      <c r="I44" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8033,8 +8054,8 @@
       <c r="G45" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H45" s="48"/>
-      <c r="I45" s="51" t="s">
+      <c r="H45" s="49"/>
+      <c r="I45" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8058,8 +8079,8 @@
       <c r="G46" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H46" s="48"/>
-      <c r="I46" s="51" t="s">
+      <c r="H46" s="49"/>
+      <c r="I46" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8083,8 +8104,8 @@
       <c r="G47" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H47" s="48"/>
-      <c r="I47" s="51" t="s">
+      <c r="H47" s="49"/>
+      <c r="I47" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8108,8 +8129,8 @@
       <c r="G48" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H48" s="48"/>
-      <c r="I48" s="51" t="s">
+      <c r="H48" s="49"/>
+      <c r="I48" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8133,8 +8154,8 @@
       <c r="G49" s="19" t="s">
         <v>687</v>
       </c>
-      <c r="H49" s="48"/>
-      <c r="I49" s="51" t="s">
+      <c r="H49" s="49"/>
+      <c r="I49" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8158,8 +8179,8 @@
       <c r="G50" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="H50" s="48"/>
-      <c r="I50" s="51" t="s">
+      <c r="H50" s="49"/>
+      <c r="I50" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8183,8 +8204,8 @@
       <c r="G51" s="19" t="s">
         <v>689</v>
       </c>
-      <c r="H51" s="48"/>
-      <c r="I51" s="51" t="s">
+      <c r="H51" s="49"/>
+      <c r="I51" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8208,8 +8229,8 @@
       <c r="G52" s="19" t="s">
         <v>690</v>
       </c>
-      <c r="H52" s="48"/>
-      <c r="I52" s="51" t="s">
+      <c r="H52" s="49"/>
+      <c r="I52" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8233,8 +8254,8 @@
       <c r="G53" s="19" t="s">
         <v>691</v>
       </c>
-      <c r="H53" s="49"/>
-      <c r="I53" s="51" t="s">
+      <c r="H53" s="50"/>
+      <c r="I53" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8287,10 +8308,10 @@
       <c r="G55" s="19" t="s">
         <v>700</v>
       </c>
-      <c r="H55" s="47" t="s">
+      <c r="H55" s="48" t="s">
         <v>692</v>
       </c>
-      <c r="I55" s="51" t="s">
+      <c r="I55" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8314,8 +8335,8 @@
       <c r="G56" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="H56" s="48"/>
-      <c r="I56" s="51" t="s">
+      <c r="H56" s="49"/>
+      <c r="I56" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8339,8 +8360,8 @@
       <c r="G57" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="H57" s="48"/>
-      <c r="I57" s="51" t="s">
+      <c r="H57" s="49"/>
+      <c r="I57" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8364,8 +8385,8 @@
       <c r="G58" s="19" t="s">
         <v>676</v>
       </c>
-      <c r="H58" s="48"/>
-      <c r="I58" s="51" t="s">
+      <c r="H58" s="49"/>
+      <c r="I58" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8389,8 +8410,8 @@
       <c r="G59" s="19" t="s">
         <v>677</v>
       </c>
-      <c r="H59" s="48"/>
-      <c r="I59" s="51" t="s">
+      <c r="H59" s="49"/>
+      <c r="I59" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8414,8 +8435,8 @@
       <c r="G60" s="19" t="s">
         <v>674</v>
       </c>
-      <c r="H60" s="48"/>
-      <c r="I60" s="51" t="s">
+      <c r="H60" s="49"/>
+      <c r="I60" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8439,8 +8460,8 @@
       <c r="G61" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="H61" s="48"/>
-      <c r="I61" s="51" t="s">
+      <c r="H61" s="49"/>
+      <c r="I61" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8464,8 +8485,8 @@
       <c r="G62" s="19" t="s">
         <v>678</v>
       </c>
-      <c r="H62" s="48"/>
-      <c r="I62" s="51" t="s">
+      <c r="H62" s="49"/>
+      <c r="I62" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8489,8 +8510,8 @@
       <c r="G63" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="H63" s="48"/>
-      <c r="I63" s="51" t="s">
+      <c r="H63" s="49"/>
+      <c r="I63" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8516,8 +8537,8 @@
       <c r="G64" s="19" t="s">
         <v>675</v>
       </c>
-      <c r="H64" s="48"/>
-      <c r="I64" s="51" t="s">
+      <c r="H64" s="49"/>
+      <c r="I64" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8541,8 +8562,8 @@
       <c r="G65" s="19" t="s">
         <v>673</v>
       </c>
-      <c r="H65" s="49"/>
-      <c r="I65" s="51" t="s">
+      <c r="H65" s="50"/>
+      <c r="I65" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8595,10 +8616,10 @@
       <c r="G67" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H67" s="50" t="s">
+      <c r="H67" s="51" t="s">
         <v>628</v>
       </c>
-      <c r="I67" s="51" t="s">
+      <c r="I67" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8622,8 +8643,8 @@
       <c r="G68" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H68" s="48"/>
-      <c r="I68" s="51" t="s">
+      <c r="H68" s="49"/>
+      <c r="I68" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8647,8 +8668,8 @@
       <c r="G69" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H69" s="48"/>
-      <c r="I69" s="51" t="s">
+      <c r="H69" s="49"/>
+      <c r="I69" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8672,8 +8693,8 @@
       <c r="G70" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H70" s="48"/>
-      <c r="I70" s="51" t="s">
+      <c r="H70" s="49"/>
+      <c r="I70" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8725,7 +8746,7 @@
         <v>143</v>
       </c>
       <c r="H72" s="32"/>
-      <c r="I72" s="51" t="s">
+      <c r="I72" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8748,7 +8769,7 @@
         <v>143</v>
       </c>
       <c r="H73" s="32"/>
-      <c r="I73" s="51" t="s">
+      <c r="I73" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8773,7 +8794,7 @@
         <v>143</v>
       </c>
       <c r="H74" s="32"/>
-      <c r="I74" s="51" t="s">
+      <c r="I74" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8827,7 +8848,7 @@
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
-      <c r="I76" s="51" t="s">
+      <c r="I76" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8852,7 +8873,7 @@
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
-      <c r="I77" s="51" t="s">
+      <c r="I77" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8877,7 +8898,7 @@
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
-      <c r="I78" s="51" t="s">
+      <c r="I78" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8902,7 +8923,7 @@
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
-      <c r="I79" s="51" t="s">
+      <c r="I79" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -8927,7 +8948,7 @@
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
-      <c r="I80" s="51" t="s">
+      <c r="I80" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8952,7 +8973,7 @@
         <v>150</v>
       </c>
       <c r="H81" s="32"/>
-      <c r="I81" s="51" t="s">
+      <c r="I81" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -8977,7 +8998,7 @@
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
-      <c r="I82" s="51" t="s">
+      <c r="I82" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -9002,7 +9023,7 @@
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
-      <c r="I83" s="51" t="s">
+      <c r="I83" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -9027,7 +9048,7 @@
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
-      <c r="I84" s="51" t="s">
+      <c r="I84" s="37" t="s">
         <v>840</v>
       </c>
     </row>
@@ -9052,7 +9073,7 @@
         <v>150</v>
       </c>
       <c r="H85" s="32"/>
-      <c r="I85" s="51" t="s">
+      <c r="I85" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9077,7 +9098,7 @@
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
-      <c r="I86" s="51" t="s">
+      <c r="I86" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9102,7 +9123,7 @@
         <v>150</v>
       </c>
       <c r="H87" s="32"/>
-      <c r="I87" s="51" t="s">
+      <c r="I87" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9156,7 +9177,7 @@
         <v>169</v>
       </c>
       <c r="H89" s="32"/>
-      <c r="I89" s="51" t="s">
+      <c r="I89" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9179,7 +9200,7 @@
         <v>171</v>
       </c>
       <c r="H90" s="32"/>
-      <c r="I90" s="51" t="s">
+      <c r="I90" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9202,7 +9223,7 @@
         <v>173</v>
       </c>
       <c r="H91" s="32"/>
-      <c r="I91" s="51" t="s">
+      <c r="I91" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9225,7 +9246,7 @@
         <v>173</v>
       </c>
       <c r="H92" s="32"/>
-      <c r="I92" s="51" t="s">
+      <c r="I92" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9248,7 +9269,7 @@
         <v>173</v>
       </c>
       <c r="H93" s="32"/>
-      <c r="I93" s="51" t="s">
+      <c r="I93" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9273,7 +9294,7 @@
         <v>179</v>
       </c>
       <c r="H94" s="32"/>
-      <c r="I94" s="51" t="s">
+      <c r="I94" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9296,7 +9317,7 @@
         <v>181</v>
       </c>
       <c r="H95" s="32"/>
-      <c r="I95" s="51" t="s">
+      <c r="I95" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9321,7 +9342,7 @@
         <v>184</v>
       </c>
       <c r="H96" s="32"/>
-      <c r="I96" s="51" t="s">
+      <c r="I96" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9344,7 +9365,7 @@
         <v>187</v>
       </c>
       <c r="H97" s="32"/>
-      <c r="I97" s="51" t="s">
+      <c r="I97" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9367,7 +9388,7 @@
         <v>189</v>
       </c>
       <c r="H98" s="32"/>
-      <c r="I98" s="51" t="s">
+      <c r="I98" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9392,7 +9413,7 @@
         <v>189</v>
       </c>
       <c r="H99" s="32"/>
-      <c r="I99" s="51" t="s">
+      <c r="I99" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9417,7 +9438,7 @@
         <v>194</v>
       </c>
       <c r="H100" s="32"/>
-      <c r="I100" s="51" t="s">
+      <c r="I100" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9442,7 +9463,7 @@
         <v>197</v>
       </c>
       <c r="H101" s="32"/>
-      <c r="I101" s="51" t="s">
+      <c r="I101" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9467,7 +9488,7 @@
         <v>197</v>
       </c>
       <c r="H102" s="32"/>
-      <c r="I102" s="51" t="s">
+      <c r="I102" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9492,7 +9513,7 @@
         <v>202</v>
       </c>
       <c r="H103" s="32"/>
-      <c r="I103" s="51" t="s">
+      <c r="I103" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9515,7 +9536,7 @@
         <v>204</v>
       </c>
       <c r="H104" s="32"/>
-      <c r="I104" s="51" t="s">
+      <c r="I104" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9538,7 +9559,7 @@
         <v>207</v>
       </c>
       <c r="H105" s="32"/>
-      <c r="I105" s="51" t="s">
+      <c r="I105" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9561,7 +9582,7 @@
         <v>209</v>
       </c>
       <c r="H106" s="32"/>
-      <c r="I106" s="51" t="s">
+      <c r="I106" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9584,7 +9605,7 @@
         <v>209</v>
       </c>
       <c r="H107" s="32"/>
-      <c r="I107" s="51" t="s">
+      <c r="I107" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9607,7 +9628,7 @@
         <v>209</v>
       </c>
       <c r="H108" s="32"/>
-      <c r="I108" s="51" t="s">
+      <c r="I108" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9630,7 +9651,7 @@
         <v>213</v>
       </c>
       <c r="H109" s="32"/>
-      <c r="I109" s="51" t="s">
+      <c r="I109" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9653,7 +9674,7 @@
         <v>215</v>
       </c>
       <c r="H110" s="32"/>
-      <c r="I110" s="51" t="s">
+      <c r="I110" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9676,7 +9697,7 @@
         <v>217</v>
       </c>
       <c r="H111" s="32"/>
-      <c r="I111" s="51" t="s">
+      <c r="I111" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9701,7 +9722,7 @@
         <v>220</v>
       </c>
       <c r="H112" s="32"/>
-      <c r="I112" s="51" t="s">
+      <c r="I112" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9726,7 +9747,7 @@
         <v>194</v>
       </c>
       <c r="H113" s="32"/>
-      <c r="I113" s="51" t="s">
+      <c r="I113" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9751,7 +9772,7 @@
         <v>225</v>
       </c>
       <c r="H114" s="32"/>
-      <c r="I114" s="51" t="s">
+      <c r="I114" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9776,7 +9797,7 @@
         <v>229</v>
       </c>
       <c r="H115" s="32"/>
-      <c r="I115" s="51" t="s">
+      <c r="I115" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9801,7 +9822,7 @@
         <v>231</v>
       </c>
       <c r="H116" s="32"/>
-      <c r="I116" s="51" t="s">
+      <c r="I116" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9855,7 +9876,7 @@
         <v>588</v>
       </c>
       <c r="H118" s="32"/>
-      <c r="I118" s="51" t="s">
+      <c r="I118" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9880,7 +9901,7 @@
         <v>588</v>
       </c>
       <c r="H119" s="32"/>
-      <c r="I119" s="51" t="s">
+      <c r="I119" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9905,7 +9926,7 @@
         <v>588</v>
       </c>
       <c r="H120" s="32"/>
-      <c r="I120" s="51" t="s">
+      <c r="I120" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9930,7 +9951,7 @@
         <v>588</v>
       </c>
       <c r="H121" s="32"/>
-      <c r="I121" s="51" t="s">
+      <c r="I121" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9955,7 +9976,7 @@
         <v>588</v>
       </c>
       <c r="H122" s="32"/>
-      <c r="I122" s="51" t="s">
+      <c r="I122" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -9980,7 +10001,7 @@
         <v>588</v>
       </c>
       <c r="H123" s="32"/>
-      <c r="I123" s="51" t="s">
+      <c r="I123" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10005,7 +10026,7 @@
         <v>588</v>
       </c>
       <c r="H124" s="32"/>
-      <c r="I124" s="51" t="s">
+      <c r="I124" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10030,7 +10051,7 @@
         <v>588</v>
       </c>
       <c r="H125" s="32"/>
-      <c r="I125" s="51" t="s">
+      <c r="I125" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10055,7 +10076,7 @@
         <v>588</v>
       </c>
       <c r="H126" s="32"/>
-      <c r="I126" s="51" t="s">
+      <c r="I126" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10080,7 +10101,7 @@
         <v>588</v>
       </c>
       <c r="H127" s="32"/>
-      <c r="I127" s="51" t="s">
+      <c r="I127" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10105,7 +10126,7 @@
         <v>588</v>
       </c>
       <c r="H128" s="32"/>
-      <c r="I128" s="51" t="s">
+      <c r="I128" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10159,7 +10180,7 @@
         <v>235</v>
       </c>
       <c r="H130" s="32"/>
-      <c r="I130" s="51" t="s">
+      <c r="I130" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10182,7 +10203,7 @@
         <v>61</v>
       </c>
       <c r="H131" s="32"/>
-      <c r="I131" s="51" t="s">
+      <c r="I131" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10205,7 +10226,7 @@
         <v>241</v>
       </c>
       <c r="H132" s="32"/>
-      <c r="I132" s="51" t="s">
+      <c r="I132" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10230,7 +10251,7 @@
         <v>244</v>
       </c>
       <c r="H133" s="32"/>
-      <c r="I133" s="51" t="s">
+      <c r="I133" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10253,7 +10274,7 @@
         <v>244</v>
       </c>
       <c r="H134" s="32"/>
-      <c r="I134" s="51" t="s">
+      <c r="I134" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10278,7 +10299,7 @@
         <v>244</v>
       </c>
       <c r="H135" s="32"/>
-      <c r="I135" s="51" t="s">
+      <c r="I135" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10303,7 +10324,7 @@
         <v>250</v>
       </c>
       <c r="H136" s="32"/>
-      <c r="I136" s="51" t="s">
+      <c r="I136" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10330,7 +10351,7 @@
         <v>250</v>
       </c>
       <c r="H137" s="32"/>
-      <c r="I137" s="51" t="s">
+      <c r="I137" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10355,7 +10376,7 @@
         <v>256</v>
       </c>
       <c r="H138" s="32"/>
-      <c r="I138" s="51" t="s">
+      <c r="I138" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10380,7 +10401,7 @@
         <v>698</v>
       </c>
       <c r="H139" s="32"/>
-      <c r="I139" s="51" t="s">
+      <c r="I139" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10405,7 +10426,7 @@
         <v>258</v>
       </c>
       <c r="H140" s="32"/>
-      <c r="I140" s="51" t="s">
+      <c r="I140" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10430,7 +10451,7 @@
         <v>261</v>
       </c>
       <c r="H141" s="32"/>
-      <c r="I141" s="51" t="s">
+      <c r="I141" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10455,7 +10476,7 @@
         <v>264</v>
       </c>
       <c r="H142" s="32"/>
-      <c r="I142" s="51" t="s">
+      <c r="I142" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10480,7 +10501,7 @@
         <v>261</v>
       </c>
       <c r="H143" s="32"/>
-      <c r="I143" s="51" t="s">
+      <c r="I143" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10534,7 +10555,7 @@
         <v>267</v>
       </c>
       <c r="H145" s="32"/>
-      <c r="I145" s="51" t="s">
+      <c r="I145" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10559,7 +10580,7 @@
         <v>267</v>
       </c>
       <c r="H146" s="32"/>
-      <c r="I146" s="51" t="s">
+      <c r="I146" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10582,7 +10603,7 @@
         <v>267</v>
       </c>
       <c r="H147" s="32"/>
-      <c r="I147" s="51" t="s">
+      <c r="I147" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10605,7 +10626,7 @@
         <v>267</v>
       </c>
       <c r="H148" s="32"/>
-      <c r="I148" s="51" t="s">
+      <c r="I148" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10630,7 +10651,7 @@
         <v>267</v>
       </c>
       <c r="H149" s="32"/>
-      <c r="I149" s="51" t="s">
+      <c r="I149" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10655,7 +10676,7 @@
         <v>267</v>
       </c>
       <c r="H150" s="32"/>
-      <c r="I150" s="51" t="s">
+      <c r="I150" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10709,7 +10730,7 @@
         <v>284</v>
       </c>
       <c r="H152" s="32"/>
-      <c r="I152" s="51" t="s">
+      <c r="I152" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10736,7 +10757,7 @@
         <v>279</v>
       </c>
       <c r="H153" s="32"/>
-      <c r="I153" s="51" t="s">
+      <c r="I153" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10763,7 +10784,7 @@
         <v>298</v>
       </c>
       <c r="H154" s="32"/>
-      <c r="I154" s="51" t="s">
+      <c r="I154" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10790,7 +10811,7 @@
         <v>298</v>
       </c>
       <c r="H155" s="32"/>
-      <c r="I155" s="51" t="s">
+      <c r="I155" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10817,7 +10838,7 @@
         <v>298</v>
       </c>
       <c r="H156" s="32"/>
-      <c r="I156" s="51" t="s">
+      <c r="I156" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10844,7 +10865,7 @@
         <v>298</v>
       </c>
       <c r="H157" s="32"/>
-      <c r="I157" s="51" t="s">
+      <c r="I157" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10871,7 +10892,7 @@
         <v>298</v>
       </c>
       <c r="H158" s="32"/>
-      <c r="I158" s="51" t="s">
+      <c r="I158" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10898,7 +10919,7 @@
         <v>298</v>
       </c>
       <c r="H159" s="32"/>
-      <c r="I159" s="51" t="s">
+      <c r="I159" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10925,7 +10946,7 @@
         <v>298</v>
       </c>
       <c r="H160" s="32"/>
-      <c r="I160" s="51" t="s">
+      <c r="I160" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10952,7 +10973,7 @@
         <v>298</v>
       </c>
       <c r="H161" s="32"/>
-      <c r="I161" s="51" t="s">
+      <c r="I161" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -10979,7 +11000,7 @@
         <v>298</v>
       </c>
       <c r="H162" s="32"/>
-      <c r="I162" s="51" t="s">
+      <c r="I162" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11006,7 +11027,7 @@
         <v>284</v>
       </c>
       <c r="H163" s="32"/>
-      <c r="I163" s="51" t="s">
+      <c r="I163" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11033,7 +11054,7 @@
         <v>298</v>
       </c>
       <c r="H164" s="32"/>
-      <c r="I164" s="51" t="s">
+      <c r="I164" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11060,7 +11081,7 @@
         <v>279</v>
       </c>
       <c r="H165" s="32"/>
-      <c r="I165" s="51" t="s">
+      <c r="I165" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11113,10 +11134,10 @@
       <c r="G167" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H167" s="50" t="s">
+      <c r="H167" s="51" t="s">
         <v>798</v>
       </c>
-      <c r="I167" s="51" t="s">
+      <c r="I167" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11142,8 +11163,8 @@
       <c r="G168" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H168" s="50"/>
-      <c r="I168" s="51" t="s">
+      <c r="H168" s="51"/>
+      <c r="I168" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11169,8 +11190,8 @@
       <c r="G169" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H169" s="50"/>
-      <c r="I169" s="51" t="s">
+      <c r="H169" s="51"/>
+      <c r="I169" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11196,8 +11217,8 @@
       <c r="G170" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H170" s="50"/>
-      <c r="I170" s="51" t="s">
+      <c r="H170" s="51"/>
+      <c r="I170" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11223,8 +11244,8 @@
       <c r="G171" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H171" s="50"/>
-      <c r="I171" s="51" t="s">
+      <c r="H171" s="51"/>
+      <c r="I171" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11250,8 +11271,8 @@
       <c r="G172" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H172" s="50"/>
-      <c r="I172" s="51" t="s">
+      <c r="H172" s="51"/>
+      <c r="I172" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11277,8 +11298,8 @@
       <c r="G173" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H173" s="50"/>
-      <c r="I173" s="51" t="s">
+      <c r="H173" s="51"/>
+      <c r="I173" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11304,8 +11325,8 @@
       <c r="G174" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H174" s="50"/>
-      <c r="I174" s="51" t="s">
+      <c r="H174" s="51"/>
+      <c r="I174" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11331,8 +11352,8 @@
       <c r="G175" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H175" s="50"/>
-      <c r="I175" s="51" t="s">
+      <c r="H175" s="51"/>
+      <c r="I175" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11341,7 +11362,7 @@
         <v>714</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>574</v>
+        <v>843</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>770</v>
@@ -11358,8 +11379,8 @@
       <c r="G176" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H176" s="50"/>
-      <c r="I176" s="51" t="s">
+      <c r="H176" s="51"/>
+      <c r="I176" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11368,7 +11389,7 @@
         <v>715</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>574</v>
+        <v>848</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>770</v>
@@ -11385,8 +11406,8 @@
       <c r="G177" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H177" s="50"/>
-      <c r="I177" s="51" t="s">
+      <c r="H177" s="51"/>
+      <c r="I177" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11395,7 +11416,7 @@
         <v>716</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>574</v>
+        <v>846</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>768</v>
@@ -11412,8 +11433,8 @@
       <c r="G178" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H178" s="50"/>
-      <c r="I178" s="51" t="s">
+      <c r="H178" s="51"/>
+      <c r="I178" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11422,7 +11443,7 @@
         <v>717</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>574</v>
+        <v>843</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>766</v>
@@ -11439,8 +11460,8 @@
       <c r="G179" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H179" s="50"/>
-      <c r="I179" s="51" t="s">
+      <c r="H179" s="51"/>
+      <c r="I179" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11449,7 +11470,7 @@
         <v>718</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>574</v>
+        <v>843</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>764</v>
@@ -11466,8 +11487,8 @@
       <c r="G180" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H180" s="50"/>
-      <c r="I180" s="51" t="s">
+      <c r="H180" s="51"/>
+      <c r="I180" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11476,7 +11497,7 @@
         <v>719</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>574</v>
+        <v>849</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>761</v>
@@ -11493,8 +11514,8 @@
       <c r="G181" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H181" s="50"/>
-      <c r="I181" s="51" t="s">
+      <c r="H181" s="51"/>
+      <c r="I181" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11503,7 +11524,7 @@
         <v>720</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>574</v>
+        <v>847</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>763</v>
@@ -11520,8 +11541,8 @@
       <c r="G182" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H182" s="50"/>
-      <c r="I182" s="51" t="s">
+      <c r="H182" s="51"/>
+      <c r="I182" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11530,7 +11551,7 @@
         <v>721</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>574</v>
+        <v>843</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>761</v>
@@ -11547,8 +11568,8 @@
       <c r="G183" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H183" s="50"/>
-      <c r="I183" s="51" t="s">
+      <c r="H183" s="51"/>
+      <c r="I183" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11557,7 +11578,7 @@
         <v>722</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>574</v>
+        <v>844</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>759</v>
@@ -11574,8 +11595,8 @@
       <c r="G184" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H184" s="50"/>
-      <c r="I184" s="51" t="s">
+      <c r="H184" s="51"/>
+      <c r="I184" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11584,7 +11605,7 @@
         <v>723</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>574</v>
+        <v>844</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>756</v>
@@ -11601,8 +11622,8 @@
       <c r="G185" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H185" s="50"/>
-      <c r="I185" s="51" t="s">
+      <c r="H185" s="51"/>
+      <c r="I185" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11611,7 +11632,7 @@
         <v>724</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>574</v>
+        <v>845</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>753</v>
@@ -11628,8 +11649,8 @@
       <c r="G186" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H186" s="50"/>
-      <c r="I186" s="51" t="s">
+      <c r="H186" s="51"/>
+      <c r="I186" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11638,7 +11659,7 @@
         <v>725</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>574</v>
+        <v>846</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>758</v>
@@ -11655,8 +11676,8 @@
       <c r="G187" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="H187" s="50"/>
-      <c r="I187" s="51" t="s">
+      <c r="H187" s="51"/>
+      <c r="I187" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11708,13 +11729,13 @@
       <c r="F189" s="27" t="s">
         <v>615</v>
       </c>
-      <c r="G189" s="37" t="s">
+      <c r="G189" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="H189" s="44" t="s">
+      <c r="H189" s="45" t="s">
         <v>645</v>
       </c>
-      <c r="I189" s="51" t="s">
+      <c r="I189" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11735,9 +11756,9 @@
       <c r="F190" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="G190" s="38"/>
-      <c r="H190" s="45"/>
-      <c r="I190" s="51" t="s">
+      <c r="G190" s="39"/>
+      <c r="H190" s="46"/>
+      <c r="I190" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11758,9 +11779,9 @@
       <c r="F191" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="G191" s="38"/>
-      <c r="H191" s="45"/>
-      <c r="I191" s="51" t="s">
+      <c r="G191" s="39"/>
+      <c r="H191" s="46"/>
+      <c r="I191" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11781,9 +11802,9 @@
       <c r="F192" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="G192" s="38"/>
-      <c r="H192" s="45"/>
-      <c r="I192" s="51" t="s">
+      <c r="G192" s="39"/>
+      <c r="H192" s="46"/>
+      <c r="I192" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11804,9 +11825,9 @@
       <c r="F193" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="G193" s="38"/>
-      <c r="H193" s="45"/>
-      <c r="I193" s="51" t="s">
+      <c r="G193" s="39"/>
+      <c r="H193" s="46"/>
+      <c r="I193" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11827,9 +11848,9 @@
       <c r="F194" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="G194" s="38"/>
-      <c r="H194" s="45"/>
-      <c r="I194" s="51" t="s">
+      <c r="G194" s="39"/>
+      <c r="H194" s="46"/>
+      <c r="I194" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11850,9 +11871,9 @@
       <c r="F195" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="G195" s="38"/>
-      <c r="H195" s="45"/>
-      <c r="I195" s="51" t="s">
+      <c r="G195" s="39"/>
+      <c r="H195" s="46"/>
+      <c r="I195" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11873,9 +11894,9 @@
       <c r="F196" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="G196" s="38"/>
-      <c r="H196" s="45"/>
-      <c r="I196" s="51" t="s">
+      <c r="G196" s="39"/>
+      <c r="H196" s="46"/>
+      <c r="I196" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11896,9 +11917,9 @@
       <c r="F197" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="G197" s="38"/>
-      <c r="H197" s="45"/>
-      <c r="I197" s="51" t="s">
+      <c r="G197" s="39"/>
+      <c r="H197" s="46"/>
+      <c r="I197" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11919,9 +11940,9 @@
       <c r="F198" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="G198" s="38"/>
-      <c r="H198" s="45"/>
-      <c r="I198" s="51" t="s">
+      <c r="G198" s="39"/>
+      <c r="H198" s="46"/>
+      <c r="I198" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11942,9 +11963,9 @@
       <c r="F199" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="G199" s="38"/>
-      <c r="H199" s="45"/>
-      <c r="I199" s="51" t="s">
+      <c r="G199" s="39"/>
+      <c r="H199" s="46"/>
+      <c r="I199" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11965,9 +11986,9 @@
       <c r="F200" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="G200" s="38"/>
-      <c r="H200" s="45"/>
-      <c r="I200" s="51" t="s">
+      <c r="G200" s="39"/>
+      <c r="H200" s="46"/>
+      <c r="I200" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -11990,9 +12011,9 @@
       <c r="F201" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="G201" s="38"/>
-      <c r="H201" s="45"/>
-      <c r="I201" s="51" t="s">
+      <c r="G201" s="39"/>
+      <c r="H201" s="46"/>
+      <c r="I201" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12015,9 +12036,9 @@
       <c r="F202" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="G202" s="38"/>
-      <c r="H202" s="45"/>
-      <c r="I202" s="51" t="s">
+      <c r="G202" s="39"/>
+      <c r="H202" s="46"/>
+      <c r="I202" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12038,9 +12059,9 @@
       <c r="F203" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G203" s="38"/>
-      <c r="H203" s="45"/>
-      <c r="I203" s="51" t="s">
+      <c r="G203" s="39"/>
+      <c r="H203" s="46"/>
+      <c r="I203" s="37" t="s">
         <v>839</v>
       </c>
     </row>
@@ -12063,9 +12084,9 @@
       <c r="F204" s="17" t="s">
         <v>629</v>
       </c>
-      <c r="G204" s="39"/>
-      <c r="H204" s="46"/>
-      <c r="I204" s="51" t="s">
+      <c r="G204" s="40"/>
+      <c r="H204" s="47"/>
+      <c r="I204" s="37" t="s">
         <v>839</v>
       </c>
     </row>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D029548F-D10A-4763-8D53-ADDA1118DBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8652DDBA-2F2B-480E-AD3D-1268AE9352FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="852">
   <si>
     <t>家里</t>
   </si>
@@ -5976,19 +5976,25 @@
     <t>250，待测，待测</t>
   </si>
   <si>
-    <t>500，待测，待测</t>
-  </si>
-  <si>
     <t>300，待测，待测</t>
   </si>
   <si>
-    <t>400，待测，待测</t>
-  </si>
-  <si>
     <t>180，待测，待测</t>
   </si>
   <si>
-    <t>220，待测，待测</t>
+    <t>400，500，待测</t>
+  </si>
+  <si>
+    <t>250，400，待测</t>
+  </si>
+  <si>
+    <t>500，700，待测</t>
+  </si>
+  <si>
+    <t>200，250，待测</t>
+  </si>
+  <si>
+    <t>220，300，待测</t>
   </si>
 </sst>
 </file>
@@ -11389,7 +11395,7 @@
         <v>715</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>770</v>
@@ -11416,7 +11422,7 @@
         <v>716</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>768</v>
@@ -11443,7 +11449,7 @@
         <v>717</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>766</v>
@@ -11497,7 +11503,7 @@
         <v>719</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>761</v>
@@ -11578,7 +11584,7 @@
         <v>722</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>759</v>
@@ -11632,7 +11638,7 @@
         <v>724</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>753</v>
@@ -11659,7 +11665,7 @@
         <v>725</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>758</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8652DDBA-2F2B-480E-AD3D-1268AE9352FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556470F5-98A9-49A2-B904-A03D7D4F8565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7530,7 +7530,7 @@
         <v>50</v>
       </c>
       <c r="B24" s="2">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -7701,7 +7701,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="2">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="C31" s="2">
         <v>38</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556470F5-98A9-49A2-B904-A03D7D4F8565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3C4C90-B9C3-44A4-918F-70613C992914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9357,13 +9357,13 @@
         <v>186</v>
       </c>
       <c r="B97" s="2">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="C97" s="2">
         <v>63</v>
       </c>
       <c r="D97" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3C4C90-B9C3-44A4-918F-70613C992914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB983858-54D7-4C04-BFEA-ADCF44C37891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -597,9 +597,6 @@
   </si>
   <si>
     <t>仆人</t>
-  </si>
-  <si>
-    <t>马克思的记忆“过去的幽灵”</t>
   </si>
   <si>
     <t>主线第四章：过去的鬼魂</t>
@@ -5995,6 +5992,9 @@
   </si>
   <si>
     <t>220，300，待测</t>
+  </si>
+  <si>
+    <t>马克斯的记忆“过去的幽灵”</t>
   </si>
 </sst>
 </file>
@@ -6980,7 +6980,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="41" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -7005,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>4</v>
@@ -7014,10 +7014,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="19" t="s">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -7059,7 +7059,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>4</v>
@@ -7068,10 +7068,10 @@
         <v>5</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B10" s="2">
         <v>90</v>
@@ -7209,11 +7209,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7255,11 +7255,11 @@
       <c r="E12" s="2"/>
       <c r="F12" s="19"/>
       <c r="G12" s="21" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7278,11 +7278,11 @@
       <c r="E13" s="2"/>
       <c r="F13" s="19"/>
       <c r="G13" s="21" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7301,11 +7301,11 @@
         <v>28</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -7324,11 +7324,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="19"/>
       <c r="G15" s="21" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7397,11 +7397,11 @@
         <v>36</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7445,11 +7445,11 @@
         <v>41</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7468,11 +7468,11 @@
       <c r="E21" s="2"/>
       <c r="F21" s="19"/>
       <c r="G21" s="21" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7486,18 +7486,18 @@
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="19" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -7511,7 +7511,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="19" t="s">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -7543,11 +7543,11 @@
         <v>51</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7568,11 +7568,11 @@
         <v>53</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7593,11 +7593,11 @@
         <v>55</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -7618,11 +7618,11 @@
         <v>57</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -7636,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -7739,11 +7739,11 @@
         <v>72</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H32" s="32"/>
       <c r="I32" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7751,10 +7751,10 @@
         <v>73</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -7785,7 +7785,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>4</v>
@@ -7794,10 +7794,10 @@
         <v>5</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -7816,13 +7816,13 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="19" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H35" s="48" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -7864,11 +7864,11 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="19" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -7889,11 +7889,11 @@
         <v>81</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -7912,11 +7912,11 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H39" s="49"/>
       <c r="I39" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7930,18 +7930,18 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -7960,11 +7960,11 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="19" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
@@ -7983,11 +7983,11 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="19" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -8008,16 +8008,16 @@
         <v>88</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -8033,16 +8033,16 @@
         <v>90</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -8058,16 +8058,16 @@
         <v>93</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -8083,11 +8083,11 @@
         <v>95</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8108,11 +8108,11 @@
         <v>97</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H47" s="49"/>
       <c r="I47" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8155,14 +8155,14 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8183,11 +8183,11 @@
         <v>105</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8208,11 +8208,11 @@
         <v>107</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8233,11 +8233,11 @@
         <v>109</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -8258,11 +8258,11 @@
         <v>111</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H53" s="50"/>
       <c r="I53" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -8279,7 +8279,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>4</v>
@@ -8288,15 +8288,15 @@
         <v>5</v>
       </c>
       <c r="H54" s="33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -8312,13 +8312,13 @@
         <v>114</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H55" s="48" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -8339,11 +8339,11 @@
         <v>116</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H56" s="49"/>
       <c r="I56" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8364,11 +8364,11 @@
         <v>118</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H57" s="49"/>
       <c r="I57" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8389,11 +8389,11 @@
         <v>114</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H58" s="49"/>
       <c r="I58" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8414,11 +8414,11 @@
         <v>121</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H59" s="49"/>
       <c r="I59" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8439,11 +8439,11 @@
         <v>123</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H60" s="49"/>
       <c r="I60" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -8464,11 +8464,11 @@
         <v>125</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H61" s="49"/>
       <c r="I61" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -8489,11 +8489,11 @@
         <v>127</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H62" s="49"/>
       <c r="I62" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -8514,11 +8514,11 @@
         <v>129</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H63" s="49"/>
       <c r="I63" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -8538,14 +8538,14 @@
         <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H64" s="49"/>
       <c r="I64" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="162.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -8559,18 +8559,18 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H65" s="50"/>
       <c r="I65" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -8587,7 +8587,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>4</v>
@@ -8596,10 +8596,10 @@
         <v>5</v>
       </c>
       <c r="H66" s="34" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I66" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -8617,16 +8617,16 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G67" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H67" s="51" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8644,14 +8644,14 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G68" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H68" s="49"/>
       <c r="I68" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.45">
@@ -8669,14 +8669,14 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G69" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H69" s="49"/>
       <c r="I69" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -8694,14 +8694,14 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H70" s="49"/>
       <c r="I70" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -8718,7 +8718,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>4</v>
@@ -8727,10 +8727,10 @@
         <v>5</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="H72" s="32"/>
       <c r="I72" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -8818,7 +8818,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>4</v>
@@ -8827,10 +8827,10 @@
         <v>5</v>
       </c>
       <c r="H75" s="33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8838,24 +8838,24 @@
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>822</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8863,24 +8863,24 @@
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>824</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
       <c r="I77" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8888,24 +8888,24 @@
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>826</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
       <c r="I78" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8913,24 +8913,24 @@
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
       <c r="I79" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8938,38 +8938,38 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
       <c r="I80" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
@@ -8980,32 +8980,32 @@
       </c>
       <c r="H81" s="32"/>
       <c r="I81" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>804</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
       <c r="I82" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9013,24 +9013,24 @@
         <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
       <c r="I83" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9038,24 +9038,24 @@
         <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -9063,13 +9063,13 @@
         <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="H85" s="32"/>
       <c r="I85" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -9088,29 +9088,29 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>815</v>
-      </c>
       <c r="D86" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A87" s="14" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -9119,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="H87" s="32"/>
       <c r="I87" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -9147,7 +9147,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>4</v>
@@ -9156,10 +9156,10 @@
         <v>5</v>
       </c>
       <c r="H88" s="34" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -9173,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="H90" s="32"/>
       <c r="I90" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="H91" s="32"/>
       <c r="I91" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="H92" s="32"/>
       <c r="I92" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H93" s="32"/>
       <c r="I93" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="H94" s="32"/>
       <c r="I94" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="H95" s="32"/>
       <c r="I95" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>186</v>
+        <v>851</v>
       </c>
       <c r="B97" s="2">
         <v>600</v>
@@ -9368,16 +9368,16 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -9386,24 +9386,24 @@
         <v>0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -9413,19 +9413,19 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B100" s="2">
         <v>150</v>
@@ -9438,19 +9438,19 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G100" s="19" t="s">
         <v>193</v>
-      </c>
-      <c r="G100" s="19" t="s">
-        <v>194</v>
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B101" s="2">
         <v>110</v>
@@ -9463,19 +9463,19 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G101" s="19" t="s">
         <v>196</v>
-      </c>
-      <c r="G101" s="19" t="s">
-        <v>197</v>
       </c>
       <c r="H101" s="32"/>
       <c r="I101" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B102" s="2">
         <v>185</v>
@@ -9488,19 +9488,19 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H102" s="32"/>
       <c r="I102" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B103" s="2">
         <v>300</v>
@@ -9509,23 +9509,23 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G103" s="19" t="s">
         <v>201</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>202</v>
       </c>
       <c r="H103" s="32"/>
       <c r="I103" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B104" s="2">
         <v>300</v>
@@ -9539,22 +9539,22 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A105" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B105" s="2">
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -9562,19 +9562,19 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -9585,22 +9585,22 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D107" s="2">
         <v>72</v>
@@ -9608,39 +9608,39 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B109" s="2">
         <v>300</v>
@@ -9654,16 +9654,16 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B110" s="2">
         <v>600</v>
@@ -9677,16 +9677,16 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B111" s="2">
         <v>1000</v>
@@ -9700,16 +9700,16 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B112" s="2">
         <v>450</v>
@@ -9718,23 +9718,23 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G112" s="19" t="s">
         <v>219</v>
-      </c>
-      <c r="G112" s="19" t="s">
-        <v>220</v>
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B113" s="2">
         <v>2500</v>
@@ -9747,19 +9747,19 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B114" s="2">
         <v>9000</v>
@@ -9772,19 +9772,19 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G114" s="19" t="s">
         <v>224</v>
-      </c>
-      <c r="G114" s="19" t="s">
-        <v>225</v>
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B115" s="2">
         <v>10500</v>
@@ -9793,23 +9793,23 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G115" s="19" t="s">
         <v>228</v>
-      </c>
-      <c r="G115" s="19" t="s">
-        <v>229</v>
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="121.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A116" s="14" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -9822,19 +9822,19 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -9846,7 +9846,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>4</v>
@@ -9855,15 +9855,15 @@
         <v>5</v>
       </c>
       <c r="H117" s="35" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -9872,23 +9872,23 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="G118" s="19" t="s">
         <v>587</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>588</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" s="11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -9901,19 +9901,19 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" s="11" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -9922,23 +9922,23 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B121" s="2">
         <v>150</v>
@@ -9951,19 +9951,19 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H121" s="32"/>
       <c r="I121" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B122" s="2">
         <v>300</v>
@@ -9976,19 +9976,19 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -9997,23 +9997,23 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H123" s="32"/>
       <c r="I123" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -10022,23 +10022,23 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H124" s="32"/>
       <c r="I124" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -10051,19 +10051,19 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H125" s="32"/>
       <c r="I125" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -10076,19 +10076,19 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H126" s="32"/>
       <c r="I126" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -10097,23 +10097,23 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H127" s="32"/>
       <c r="I127" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A128" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -10126,19 +10126,19 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H128" s="32"/>
       <c r="I128" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>1</v>
@@ -10150,7 +10150,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>4</v>
@@ -10159,15 +10159,15 @@
         <v>5</v>
       </c>
       <c r="H129" s="34" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B130" s="2">
         <v>50</v>
@@ -10176,18 +10176,18 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G130" s="19" t="s">
         <v>234</v>
-      </c>
-      <c r="G130" s="19" t="s">
-        <v>235</v>
       </c>
       <c r="H130" s="32"/>
       <c r="I130" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.45">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="H131" s="32"/>
       <c r="I131" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B132" s="2">
         <v>100</v>
@@ -10224,21 +10224,21 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H132" s="32"/>
       <c r="I132" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B133" s="2">
         <v>45</v>
@@ -10251,42 +10251,42 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G133" s="19" t="s">
         <v>243</v>
-      </c>
-      <c r="G133" s="19" t="s">
-        <v>244</v>
       </c>
       <c r="H133" s="32"/>
       <c r="I133" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B134" s="2">
         <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H134" s="32"/>
       <c r="I134" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B135" s="2">
         <v>600</v>
@@ -10295,23 +10295,23 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H135" s="32"/>
       <c r="I135" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B136" s="2">
         <v>1500</v>
@@ -10320,23 +10320,23 @@
         <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G136" s="19" t="s">
         <v>249</v>
-      </c>
-      <c r="G136" s="19" t="s">
-        <v>250</v>
       </c>
       <c r="H136" s="32"/>
       <c r="I136" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
@@ -10348,22 +10348,22 @@
         <v>100</v>
       </c>
       <c r="E137" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="G137" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H137" s="32"/>
       <c r="I137" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B138" s="2">
         <v>1000</v>
@@ -10376,19 +10376,19 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G138" s="19" t="s">
         <v>255</v>
-      </c>
-      <c r="G138" s="19" t="s">
-        <v>256</v>
       </c>
       <c r="H138" s="32"/>
       <c r="I138" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B139" s="2">
         <v>120</v>
@@ -10397,23 +10397,23 @@
         <v>13</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="G139" s="19" t="s">
         <v>697</v>
-      </c>
-      <c r="G139" s="19" t="s">
-        <v>698</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B140" s="2">
         <v>750</v>
@@ -10429,16 +10429,16 @@
         <v>69</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H140" s="32"/>
       <c r="I140" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B141" s="2">
         <v>150</v>
@@ -10451,19 +10451,19 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G141" s="19" t="s">
         <v>260</v>
-      </c>
-      <c r="G141" s="19" t="s">
-        <v>261</v>
       </c>
       <c r="H141" s="32"/>
       <c r="I141" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B142" s="2">
         <v>720</v>
@@ -10476,19 +10476,19 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G142" s="19" t="s">
         <v>263</v>
-      </c>
-      <c r="G142" s="19" t="s">
-        <v>264</v>
       </c>
       <c r="H142" s="32"/>
       <c r="I142" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A143" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B143" s="2">
         <v>2000</v>
@@ -10501,19 +10501,19 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H143" s="32"/>
       <c r="I143" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>1</v>
@@ -10525,7 +10525,7 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>4</v>
@@ -10534,161 +10534,161 @@
         <v>5</v>
       </c>
       <c r="H144" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I144" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H145" s="32"/>
       <c r="I145" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H146" s="32"/>
       <c r="I146" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H147" s="32"/>
       <c r="I147" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H148" s="32"/>
       <c r="I148" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H149" s="32"/>
       <c r="I149" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A150" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>791</v>
-      </c>
       <c r="D150" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H150" s="32"/>
       <c r="I150" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -10700,7 +10700,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>4</v>
@@ -10709,391 +10709,391 @@
         <v>5</v>
       </c>
       <c r="H151" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C152" s="2">
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G152" s="19" t="s">
         <v>283</v>
-      </c>
-      <c r="G152" s="19" t="s">
-        <v>284</v>
       </c>
       <c r="H152" s="32"/>
       <c r="I152" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>648</v>
-      </c>
       <c r="D153" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G153" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H153" s="32"/>
       <c r="I153" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D154" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E154" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F154" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="G154" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H154" s="32"/>
       <c r="I154" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D155" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G155" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H155" s="32"/>
       <c r="I155" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="G156" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H156" s="32"/>
       <c r="I156" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="19" t="s">
         <v>297</v>
-      </c>
-      <c r="G157" s="19" t="s">
-        <v>298</v>
       </c>
       <c r="H157" s="32"/>
       <c r="I157" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H158" s="32"/>
       <c r="I158" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D159" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H159" s="32"/>
       <c r="I159" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D161" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G161" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H161" s="32"/>
       <c r="I161" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="D162" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G162" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H162" s="32"/>
       <c r="I162" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E163" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="F163" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H163" s="32"/>
       <c r="I163" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="D164" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E164" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>317</v>
-      </c>
       <c r="F164" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H164" s="32"/>
       <c r="I164" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="202.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A165" s="14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E165" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F165" s="2" t="s">
-        <v>664</v>
-      </c>
       <c r="G165" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H165" s="32"/>
       <c r="I165" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -11105,7 +11105,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>4</v>
@@ -11114,231 +11114,231 @@
         <v>5</v>
       </c>
       <c r="H166" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I166" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D167" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E167" s="6" t="s">
         <v>727</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>728</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H167" s="51" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="I167" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="E168" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="E168" s="6" t="s">
-        <v>728</v>
-      </c>
       <c r="F168" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G168" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H168" s="51"/>
       <c r="I168" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G169" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H169" s="51"/>
       <c r="I169" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>735</v>
-      </c>
       <c r="D170" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H170" s="51"/>
       <c r="I170" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D171" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E171" s="6" t="s">
         <v>737</v>
       </c>
-      <c r="E171" s="6" t="s">
-        <v>738</v>
-      </c>
       <c r="F171" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H171" s="51"/>
       <c r="I171" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="E172" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="E172" s="6" t="s">
-        <v>744</v>
-      </c>
       <c r="F172" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H172" s="51"/>
       <c r="I172" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G173" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H173" s="51"/>
       <c r="I173" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="E174" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="E174" s="6" t="s">
-        <v>747</v>
-      </c>
       <c r="F174" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G174" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H174" s="51"/>
       <c r="I174" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>4</v>
@@ -11360,336 +11360,336 @@
       </c>
       <c r="H175" s="51"/>
       <c r="I175" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H176" s="51"/>
       <c r="I176" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G177" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H177" s="51"/>
       <c r="I177" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G178" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H178" s="51"/>
       <c r="I178" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G179" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H179" s="51"/>
       <c r="I179" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G180" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H180" s="51"/>
       <c r="I180" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C181" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D181" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="D181" s="2" t="s">
-        <v>762</v>
-      </c>
       <c r="E181" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G181" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H181" s="51"/>
       <c r="I181" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G182" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H182" s="51"/>
       <c r="I182" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H183" s="51"/>
       <c r="I183" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G184" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H184" s="51"/>
       <c r="I184" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E185" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="E185" s="7" t="s">
-        <v>755</v>
-      </c>
       <c r="F185" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G185" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H185" s="51"/>
       <c r="I185" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G186" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H186" s="51"/>
       <c r="I186" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A187" s="14" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G187" s="29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H187" s="51"/>
       <c r="I187" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" s="24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>4</v>
@@ -11710,15 +11710,15 @@
         <v>5</v>
       </c>
       <c r="H188" s="36" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I188" s="31" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A189" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B189" s="27">
         <v>120</v>
@@ -11733,21 +11733,21 @@
         <v>154</v>
       </c>
       <c r="F189" s="27" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G189" s="38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H189" s="45" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I189" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B190" s="2">
         <v>120</v>
@@ -11760,17 +11760,17 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G190" s="39"/>
       <c r="H190" s="46"/>
       <c r="I190" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B191" s="2">
         <v>200</v>
@@ -11783,17 +11783,17 @@
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G191" s="39"/>
       <c r="H191" s="46"/>
       <c r="I191" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B192" s="2">
         <v>200</v>
@@ -11806,17 +11806,17 @@
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G192" s="39"/>
       <c r="H192" s="46"/>
       <c r="I192" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A193" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B193" s="2">
         <v>200</v>
@@ -11829,17 +11829,17 @@
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G193" s="39"/>
       <c r="H193" s="46"/>
       <c r="I193" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B194" s="2">
         <v>200</v>
@@ -11852,17 +11852,17 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G194" s="39"/>
       <c r="H194" s="46"/>
       <c r="I194" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A195" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B195" s="2">
         <v>200</v>
@@ -11875,17 +11875,17 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G195" s="39"/>
       <c r="H195" s="46"/>
       <c r="I195" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B196" s="2">
         <v>200</v>
@@ -11898,17 +11898,17 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G196" s="39"/>
       <c r="H196" s="46"/>
       <c r="I196" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B197" s="2">
         <v>200</v>
@@ -11921,17 +11921,17 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G197" s="39"/>
       <c r="H197" s="46"/>
       <c r="I197" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B198" s="2">
         <v>120</v>
@@ -11940,21 +11940,21 @@
         <v>55</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G198" s="39"/>
       <c r="H198" s="46"/>
       <c r="I198" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B199" s="2">
         <v>200</v>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G199" s="39"/>
       <c r="H199" s="46"/>
       <c r="I199" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A200" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B200" s="2">
         <v>250</v>
@@ -11990,17 +11990,17 @@
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G200" s="39"/>
       <c r="H200" s="46"/>
       <c r="I200" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A201" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B201" s="2">
         <v>200</v>
@@ -12012,20 +12012,20 @@
         <v>64</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G201" s="39"/>
       <c r="H201" s="46"/>
       <c r="I201" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A202" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B202" s="2">
         <v>250</v>
@@ -12037,20 +12037,20 @@
         <v>60</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G202" s="39"/>
       <c r="H202" s="46"/>
       <c r="I202" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B203" s="2">
         <v>500</v>
@@ -12059,21 +12059,21 @@
         <v>0</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G203" s="39"/>
       <c r="H203" s="46"/>
       <c r="I203" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B204" s="17">
         <v>500</v>
@@ -12085,15 +12085,15 @@
         <v>130</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G204" s="40"/>
       <c r="H204" s="47"/>
       <c r="I204" s="37" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -12126,24 +12126,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -12152,15 +12152,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -12169,32 +12169,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>21</v>
@@ -12203,7 +12203,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
@@ -12211,7 +12211,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>25</v>
@@ -12220,15 +12220,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -12237,15 +12237,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -12254,7 +12254,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
@@ -12262,7 +12262,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -12271,15 +12271,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
@@ -12288,7 +12288,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>41</v>
@@ -12296,7 +12296,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
@@ -12305,7 +12305,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
@@ -12313,7 +12313,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>50</v>
@@ -12322,15 +12322,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
@@ -12339,15 +12339,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>52</v>
@@ -12356,7 +12356,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>53</v>
@@ -12364,7 +12364,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>54</v>
@@ -12373,15 +12373,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>56</v>
@@ -12390,15 +12390,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>56</v>
@@ -12407,7 +12407,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>57</v>
@@ -12415,7 +12415,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>60</v>
@@ -12424,15 +12424,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>65</v>
@@ -12441,15 +12441,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>65</v>
@@ -12458,7 +12458,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>66</v>
@@ -12466,7 +12466,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>68</v>
@@ -12475,15 +12475,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>68</v>
@@ -12492,7 +12492,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>69</v>
@@ -12500,7 +12500,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>71</v>
@@ -12509,15 +12509,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>71</v>
@@ -12534,7 +12534,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>76</v>
@@ -12543,15 +12543,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>79</v>
@@ -12560,15 +12560,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>82</v>
@@ -12577,15 +12577,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>85</v>
@@ -12594,15 +12594,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>87</v>
@@ -12611,15 +12611,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>89</v>
@@ -12628,15 +12628,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>89</v>
@@ -12653,7 +12653,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>89</v>
@@ -12662,7 +12662,7 @@
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>91</v>
@@ -12670,7 +12670,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
@@ -12679,15 +12679,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>92</v>
@@ -12696,7 +12696,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>93</v>
@@ -12704,7 +12704,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>94</v>
@@ -12713,15 +12713,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>94</v>
@@ -12730,7 +12730,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>95</v>
@@ -12738,7 +12738,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>96</v>
@@ -12747,15 +12747,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>96</v>
@@ -12764,7 +12764,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>97</v>
@@ -12772,7 +12772,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -12781,15 +12781,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>100</v>
@@ -12798,7 +12798,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>102</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>100</v>
@@ -12815,7 +12815,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>103</v>
@@ -12823,7 +12823,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>104</v>
@@ -12832,15 +12832,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>104</v>
@@ -12849,7 +12849,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>105</v>
@@ -12857,7 +12857,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -12866,15 +12866,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>106</v>
@@ -12883,15 +12883,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>108</v>
@@ -12900,15 +12900,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>108</v>
@@ -12917,15 +12917,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>110</v>
@@ -12934,15 +12934,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>110</v>
@@ -12951,15 +12951,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>110</v>
@@ -12968,7 +12968,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>111</v>
@@ -12976,7 +12976,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>113</v>
@@ -12985,15 +12985,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>115</v>
@@ -13002,7 +13002,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>116</v>
@@ -13010,7 +13010,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>117</v>
@@ -13027,7 +13027,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>120</v>
@@ -13036,7 +13036,7 @@
         <v>4</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>121</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>122</v>
@@ -13053,15 +13053,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>124</v>
@@ -13070,15 +13070,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>126</v>
@@ -13087,15 +13087,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>128</v>
@@ -13104,15 +13104,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>128</v>
@@ -13121,7 +13121,7 @@
         <v>4</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>129</v>
@@ -13129,7 +13129,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>130</v>
@@ -13138,15 +13138,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>130</v>
@@ -13155,7 +13155,7 @@
         <v>4</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>131</v>
@@ -13163,24 +13163,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>134</v>
@@ -13189,15 +13189,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>134</v>
@@ -13206,7 +13206,7 @@
         <v>4</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>135</v>
@@ -13214,7 +13214,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>137</v>
@@ -13223,7 +13223,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>138</v>
@@ -13231,7 +13231,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>139</v>
@@ -13240,15 +13240,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>139</v>
@@ -13257,7 +13257,7 @@
         <v>4</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>140</v>
@@ -13265,7 +13265,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>141</v>
@@ -13274,15 +13274,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>141</v>
@@ -13291,7 +13291,7 @@
         <v>4</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>142</v>
@@ -13299,262 +13299,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>160</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>168</v>
@@ -13563,7 +13563,7 @@
         <v>5</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>169</v>
@@ -13571,7 +13571,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>170</v>
@@ -13580,15 +13580,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>172</v>
@@ -13597,15 +13597,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>174</v>
@@ -13614,15 +13614,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>175</v>
@@ -13631,15 +13631,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>176</v>
@@ -13648,7 +13648,7 @@
         <v>4</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>178</v>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>180</v>
@@ -13665,508 +13665,508 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D105" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>60</v>
@@ -14175,245 +14175,245 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D124" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D126" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D127" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>69</v>
@@ -14421,1379 +14421,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D144" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D145" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D207" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D214" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB983858-54D7-4C04-BFEA-ADCF44C37891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D5053-DC43-4DD2-AEBB-CC35C8B67A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9360,7 +9360,7 @@
         <v>600</v>
       </c>
       <c r="C97" s="2">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="D97" s="2">
         <v>66</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D5053-DC43-4DD2-AEBB-CC35C8B67A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF83A5E8-876C-4E65-99BE-D4210C78228F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="853">
   <si>
     <t>家里</t>
   </si>
@@ -654,12 +654,6 @@
   </si>
   <si>
     <t>强盗首领</t>
-  </si>
-  <si>
-    <t>38(任务1), 62(任务2)</t>
-  </si>
-  <si>
-    <t>主线第三章：北方</t>
   </si>
   <si>
     <t>伊万领主（NPC）</t>
@@ -5995,6 +5989,15 @@
   </si>
   <si>
     <t>马克斯的记忆“过去的幽灵”</t>
+  </si>
+  <si>
+    <t>故事人物：如何消灭死亡</t>
+  </si>
+  <si>
+    <t>主线第三章：怪物出现；如何消灭死亡</t>
+  </si>
+  <si>
+    <t>37.5(怪物出现)/62.5(如何消灭死亡)</t>
   </si>
 </sst>
 </file>
@@ -6980,7 +6983,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -7005,7 +7008,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>4</v>
@@ -7014,10 +7017,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7031,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="19" t="s">
@@ -7042,7 +7045,7 @@
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -7059,7 +7062,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>4</v>
@@ -7068,10 +7071,10 @@
         <v>5</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -7094,7 +7097,7 @@
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -7117,7 +7120,7 @@
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -7140,7 +7143,7 @@
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -7163,7 +7166,7 @@
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -7188,12 +7191,12 @@
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B10" s="2">
         <v>90</v>
@@ -7209,11 +7212,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
@@ -7236,7 +7239,7 @@
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7255,11 +7258,11 @@
       <c r="E12" s="2"/>
       <c r="F12" s="19"/>
       <c r="G12" s="21" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7278,11 +7281,11 @@
       <c r="E13" s="2"/>
       <c r="F13" s="19"/>
       <c r="G13" s="21" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7301,11 +7304,11 @@
         <v>28</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -7324,11 +7327,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="19"/>
       <c r="G15" s="21" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -7353,7 +7356,7 @@
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7376,7 +7379,7 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7397,11 +7400,11 @@
         <v>36</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -7424,7 +7427,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7445,11 +7448,11 @@
         <v>41</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7468,11 +7471,11 @@
       <c r="E21" s="2"/>
       <c r="F21" s="19"/>
       <c r="G21" s="21" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7486,18 +7489,18 @@
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="19" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -7511,7 +7514,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="19" t="s">
@@ -7522,7 +7525,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -7543,11 +7546,11 @@
         <v>51</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7568,11 +7571,11 @@
         <v>53</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7593,11 +7596,11 @@
         <v>55</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -7618,11 +7621,11 @@
         <v>57</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -7636,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -7645,7 +7648,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -7668,7 +7671,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -7693,7 +7696,7 @@
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -7718,7 +7721,7 @@
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -7739,11 +7742,11 @@
         <v>72</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H32" s="32"/>
       <c r="I32" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7751,10 +7754,10 @@
         <v>73</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -7768,12 +7771,12 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -7785,7 +7788,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>4</v>
@@ -7794,10 +7797,10 @@
         <v>5</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -7816,13 +7819,13 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H35" s="48" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -7845,7 +7848,7 @@
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -7864,11 +7867,11 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -7889,11 +7892,11 @@
         <v>81</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -7912,11 +7915,11 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="19" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H39" s="49"/>
       <c r="I39" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7930,18 +7933,18 @@
         <v>0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -7960,11 +7963,11 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
@@ -7983,11 +7986,11 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -8008,16 +8011,16 @@
         <v>88</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="12" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B44" s="2">
         <v>400</v>
@@ -8033,16 +8036,16 @@
         <v>90</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
@@ -8058,16 +8061,16 @@
         <v>93</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -8083,11 +8086,11 @@
         <v>95</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8108,11 +8111,11 @@
         <v>97</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H47" s="49"/>
       <c r="I47" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -8137,7 +8140,7 @@
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8155,14 +8158,14 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8183,11 +8186,11 @@
         <v>105</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8208,11 +8211,11 @@
         <v>107</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8233,11 +8236,11 @@
         <v>109</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -8258,11 +8261,11 @@
         <v>111</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="H53" s="50"/>
       <c r="I53" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -8279,7 +8282,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>4</v>
@@ -8288,15 +8291,15 @@
         <v>5</v>
       </c>
       <c r="H54" s="33" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -8312,13 +8315,13 @@
         <v>114</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H55" s="48" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -8339,11 +8342,11 @@
         <v>116</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H56" s="49"/>
       <c r="I56" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8364,11 +8367,11 @@
         <v>118</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H57" s="49"/>
       <c r="I57" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8389,11 +8392,11 @@
         <v>114</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="H58" s="49"/>
       <c r="I58" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8414,11 +8417,11 @@
         <v>121</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H59" s="49"/>
       <c r="I59" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8439,11 +8442,11 @@
         <v>123</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H60" s="49"/>
       <c r="I60" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -8464,11 +8467,11 @@
         <v>125</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H61" s="49"/>
       <c r="I61" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -8489,11 +8492,11 @@
         <v>127</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H62" s="49"/>
       <c r="I62" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -8514,11 +8517,11 @@
         <v>129</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H63" s="49"/>
       <c r="I63" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -8538,14 +8541,14 @@
         <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H64" s="49"/>
       <c r="I64" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="162.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -8559,18 +8562,18 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H65" s="50"/>
       <c r="I65" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -8587,7 +8590,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>4</v>
@@ -8596,10 +8599,10 @@
         <v>5</v>
       </c>
       <c r="H66" s="34" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I66" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -8617,16 +8620,16 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G67" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H67" s="51" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8644,14 +8647,14 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G68" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H68" s="49"/>
       <c r="I68" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.45">
@@ -8669,14 +8672,14 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G69" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H69" s="49"/>
       <c r="I69" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -8694,14 +8697,14 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H70" s="49"/>
       <c r="I70" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -8718,7 +8721,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>4</v>
@@ -8727,10 +8730,10 @@
         <v>5</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -8753,7 +8756,7 @@
       </c>
       <c r="H72" s="32"/>
       <c r="I72" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -8776,7 +8779,7 @@
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8801,7 +8804,7 @@
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -8818,7 +8821,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>4</v>
@@ -8827,10 +8830,10 @@
         <v>5</v>
       </c>
       <c r="H75" s="33" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8838,24 +8841,24 @@
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8863,24 +8866,24 @@
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>824</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
       <c r="I77" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8888,24 +8891,24 @@
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
       <c r="I78" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8913,24 +8916,24 @@
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
       <c r="I79" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8938,38 +8941,38 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
       <c r="I80" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81" s="11" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
@@ -8980,32 +8983,32 @@
       </c>
       <c r="H81" s="32"/>
       <c r="I81" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A82" s="11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
       <c r="I82" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9013,24 +9016,24 @@
         <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
       <c r="I83" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9038,24 +9041,24 @@
         <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>809</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -9063,13 +9066,13 @@
         <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -9080,7 +9083,7 @@
       </c>
       <c r="H85" s="32"/>
       <c r="I85" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -9088,29 +9091,29 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A87" s="14" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -9119,7 +9122,7 @@
         <v>0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
@@ -9130,7 +9133,7 @@
       </c>
       <c r="H87" s="32"/>
       <c r="I87" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -9147,7 +9150,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>4</v>
@@ -9156,10 +9159,10 @@
         <v>5</v>
       </c>
       <c r="H88" s="34" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -9173,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
@@ -9184,7 +9187,7 @@
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -9207,7 +9210,7 @@
       </c>
       <c r="H90" s="32"/>
       <c r="I90" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -9230,7 +9233,7 @@
       </c>
       <c r="H91" s="32"/>
       <c r="I91" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -9253,7 +9256,7 @@
       </c>
       <c r="H92" s="32"/>
       <c r="I92" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -9276,7 +9279,7 @@
       </c>
       <c r="H93" s="32"/>
       <c r="I93" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -9301,7 +9304,7 @@
       </c>
       <c r="H94" s="32"/>
       <c r="I94" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -9324,7 +9327,7 @@
       </c>
       <c r="H95" s="32"/>
       <c r="I95" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -9349,12 +9352,12 @@
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B97" s="2">
         <v>600</v>
@@ -9372,12 +9375,12 @@
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -9395,15 +9398,15 @@
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -9420,7 +9423,7 @@
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -9445,7 +9448,7 @@
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
@@ -9470,7 +9473,7 @@
       </c>
       <c r="H101" s="32"/>
       <c r="I101" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -9495,7 +9498,7 @@
       </c>
       <c r="H102" s="32"/>
       <c r="I102" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
@@ -9509,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
@@ -9520,7 +9523,7 @@
       </c>
       <c r="H103" s="32"/>
       <c r="I103" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
@@ -9543,10 +9546,10 @@
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="37" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="27" x14ac:dyDescent="0.45">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A105" s="11" t="s">
         <v>204</v>
       </c>
@@ -9554,7 +9557,7 @@
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>205</v>
+        <v>852</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -9562,19 +9565,19 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>206</v>
+        <v>851</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -9585,22 +9588,22 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>208</v>
+        <v>850</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D107" s="2">
         <v>72</v>
@@ -9608,39 +9611,39 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B109" s="2">
         <v>300</v>
@@ -9654,16 +9657,16 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="19" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B110" s="2">
         <v>600</v>
@@ -9677,16 +9680,16 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="19" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B111" s="2">
         <v>1000</v>
@@ -9700,16 +9703,16 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="19" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B112" s="2">
         <v>450</v>
@@ -9718,23 +9721,23 @@
         <v>69</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B113" s="2">
         <v>2500</v>
@@ -9747,19 +9750,19 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G113" s="19" t="s">
         <v>193</v>
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B114" s="2">
         <v>9000</v>
@@ -9772,19 +9775,19 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B115" s="2">
         <v>10500</v>
@@ -9793,23 +9796,23 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="121.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A116" s="14" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B116" s="2">
         <v>1700</v>
@@ -9822,19 +9825,19 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117" s="10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>1</v>
@@ -9846,7 +9849,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>4</v>
@@ -9855,15 +9858,15 @@
         <v>5</v>
       </c>
       <c r="H117" s="35" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" s="11" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B118" s="2">
         <v>75</v>
@@ -9872,23 +9875,23 @@
         <v>0</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" s="11" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B119" s="2">
         <v>45</v>
@@ -9901,19 +9904,19 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" s="11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B120" s="2">
         <v>100</v>
@@ -9922,23 +9925,23 @@
         <v>0</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B121" s="2">
         <v>150</v>
@@ -9951,19 +9954,19 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H121" s="32"/>
       <c r="I121" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B122" s="2">
         <v>300</v>
@@ -9976,19 +9979,19 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123" s="11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B123" s="2">
         <v>150</v>
@@ -9997,23 +10000,23 @@
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H123" s="32"/>
       <c r="I123" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124" s="11" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B124" s="2">
         <v>200</v>
@@ -10022,23 +10025,23 @@
         <v>0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H124" s="32"/>
       <c r="I124" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125" s="12" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B125" s="2">
         <v>215</v>
@@ -10051,19 +10054,19 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H125" s="32"/>
       <c r="I125" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A126" s="12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B126" s="2">
         <v>200</v>
@@ -10076,19 +10079,19 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H126" s="32"/>
       <c r="I126" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A127" s="13" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B127" s="2">
         <v>600</v>
@@ -10097,23 +10100,23 @@
         <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G127" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H127" s="32"/>
       <c r="I127" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A128" s="13" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B128" s="2">
         <v>2000</v>
@@ -10126,19 +10129,19 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G128" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H128" s="32"/>
       <c r="I128" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>1</v>
@@ -10150,7 +10153,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>4</v>
@@ -10159,15 +10162,15 @@
         <v>5</v>
       </c>
       <c r="H129" s="34" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B130" s="2">
         <v>50</v>
@@ -10176,18 +10179,18 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G130" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H130" s="32"/>
       <c r="I130" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.45">
@@ -10210,12 +10213,12 @@
       </c>
       <c r="H131" s="32"/>
       <c r="I131" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B132" s="2">
         <v>100</v>
@@ -10224,21 +10227,21 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H132" s="32"/>
       <c r="I132" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B133" s="2">
         <v>45</v>
@@ -10251,42 +10254,42 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G133" s="19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H133" s="32"/>
       <c r="I133" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B134" s="2">
         <v>200</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H134" s="32"/>
       <c r="I134" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B135" s="2">
         <v>600</v>
@@ -10295,23 +10298,23 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G135" s="19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H135" s="32"/>
       <c r="I135" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A136" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B136" s="2">
         <v>1500</v>
@@ -10320,23 +10323,23 @@
         <v>52</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G136" s="19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H136" s="32"/>
       <c r="I136" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B137" s="2">
         <v>1500</v>
@@ -10348,22 +10351,22 @@
         <v>100</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G137" s="19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H137" s="32"/>
       <c r="I137" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138" s="13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B138" s="2">
         <v>1000</v>
@@ -10376,19 +10379,19 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G138" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H138" s="32"/>
       <c r="I138" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B139" s="2">
         <v>120</v>
@@ -10397,23 +10400,23 @@
         <v>13</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B140" s="2">
         <v>750</v>
@@ -10429,16 +10432,16 @@
         <v>69</v>
       </c>
       <c r="G140" s="19" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H140" s="32"/>
       <c r="I140" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B141" s="2">
         <v>150</v>
@@ -10451,19 +10454,19 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H141" s="32"/>
       <c r="I141" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B142" s="2">
         <v>720</v>
@@ -10476,19 +10479,19 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G142" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H142" s="32"/>
       <c r="I142" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A143" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B143" s="2">
         <v>2000</v>
@@ -10501,19 +10504,19 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H143" s="32"/>
       <c r="I143" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>1</v>
@@ -10525,7 +10528,7 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>4</v>
@@ -10534,161 +10537,161 @@
         <v>5</v>
       </c>
       <c r="H144" s="36" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I144" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C145" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G145" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H145" s="32"/>
       <c r="I145" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H146" s="32"/>
       <c r="I146" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H147" s="32"/>
       <c r="I147" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H148" s="32"/>
       <c r="I148" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>790</v>
-      </c>
       <c r="D149" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G149" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H149" s="32"/>
       <c r="I149" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A150" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G150" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H150" s="32"/>
       <c r="I150" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -10700,7 +10703,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>4</v>
@@ -10709,391 +10712,391 @@
         <v>5</v>
       </c>
       <c r="H151" s="36" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C152" s="2">
         <v>0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G152" s="19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H152" s="32"/>
       <c r="I152" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E153" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D153" s="2" t="s">
+      <c r="F153" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="G153" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H153" s="32"/>
       <c r="I153" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C154" s="2" t="s">
+      <c r="D154" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E154" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D154" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F154" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G154" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H154" s="32"/>
       <c r="I154" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="G155" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H155" s="32"/>
       <c r="I155" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C156" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E156" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D156" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F156" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G156" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H156" s="32"/>
       <c r="I156" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G157" s="19" t="s">
         <v>295</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G157" s="19" t="s">
-        <v>297</v>
       </c>
       <c r="H157" s="32"/>
       <c r="I157" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C158" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E158" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D158" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F158" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G158" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H158" s="32"/>
       <c r="I158" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="13" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C159" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E159" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F159" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G159" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H159" s="32"/>
       <c r="I159" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="13" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C160" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E160" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F160" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G160" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="13" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C161" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E161" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F161" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G161" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H161" s="32"/>
       <c r="I161" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="13" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C162" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E162" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="F162" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G162" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H162" s="32"/>
       <c r="I162" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
       <c r="A163" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="D163" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E163" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="E163" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="F163" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G163" s="19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H163" s="32"/>
       <c r="I163" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A164" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="D164" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E164" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>316</v>
-      </c>
       <c r="F164" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G164" s="19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H164" s="32"/>
       <c r="I164" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="202.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A165" s="14" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G165" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H165" s="32"/>
       <c r="I165" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -11105,7 +11108,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>4</v>
@@ -11114,231 +11117,231 @@
         <v>5</v>
       </c>
       <c r="H166" s="36" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I166" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H167" s="51" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="I167" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G168" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H168" s="51"/>
       <c r="I168" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G169" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H169" s="51"/>
       <c r="I169" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H170" s="51"/>
       <c r="I170" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H171" s="51"/>
       <c r="I171" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="E172" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="D172" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="E172" s="6" t="s">
-        <v>743</v>
-      </c>
       <c r="F172" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H172" s="51"/>
       <c r="I172" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G173" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H173" s="51"/>
       <c r="I173" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="E174" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="D174" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="E174" s="6" t="s">
-        <v>746</v>
-      </c>
       <c r="F174" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G174" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H174" s="51"/>
       <c r="I174" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -11350,7 +11353,7 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>4</v>
@@ -11360,336 +11363,336 @@
       </c>
       <c r="H175" s="51"/>
       <c r="I175" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H176" s="51"/>
       <c r="I176" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G177" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H177" s="51"/>
       <c r="I177" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G178" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H178" s="51"/>
       <c r="I178" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G179" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H179" s="51"/>
       <c r="I179" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G180" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H180" s="51"/>
       <c r="I180" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G181" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H181" s="51"/>
       <c r="I181" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G182" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H182" s="51"/>
       <c r="I182" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H183" s="51"/>
       <c r="I183" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="G184" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H184" s="51"/>
       <c r="I184" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G185" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H185" s="51"/>
       <c r="I185" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G186" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H186" s="51"/>
       <c r="I186" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A187" s="14" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G187" s="29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H187" s="51"/>
       <c r="I187" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" s="24" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>1</v>
@@ -11701,7 +11704,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>4</v>
@@ -11710,15 +11713,15 @@
         <v>5</v>
       </c>
       <c r="H188" s="36" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="I188" s="31" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A189" s="26" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B189" s="27">
         <v>120</v>
@@ -11733,21 +11736,21 @@
         <v>154</v>
       </c>
       <c r="F189" s="27" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G189" s="38" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H189" s="45" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="I189" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B190" s="2">
         <v>120</v>
@@ -11760,17 +11763,17 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G190" s="39"/>
       <c r="H190" s="46"/>
       <c r="I190" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B191" s="2">
         <v>200</v>
@@ -11783,17 +11786,17 @@
       </c>
       <c r="E191" s="2"/>
       <c r="F191" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G191" s="39"/>
       <c r="H191" s="46"/>
       <c r="I191" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B192" s="2">
         <v>200</v>
@@ -11806,17 +11809,17 @@
       </c>
       <c r="E192" s="2"/>
       <c r="F192" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G192" s="39"/>
       <c r="H192" s="46"/>
       <c r="I192" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A193" s="11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B193" s="2">
         <v>200</v>
@@ -11829,17 +11832,17 @@
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G193" s="39"/>
       <c r="H193" s="46"/>
       <c r="I193" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B194" s="2">
         <v>200</v>
@@ -11852,17 +11855,17 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G194" s="39"/>
       <c r="H194" s="46"/>
       <c r="I194" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A195" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B195" s="2">
         <v>200</v>
@@ -11875,17 +11878,17 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G195" s="39"/>
       <c r="H195" s="46"/>
       <c r="I195" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B196" s="2">
         <v>200</v>
@@ -11898,17 +11901,17 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G196" s="39"/>
       <c r="H196" s="46"/>
       <c r="I196" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B197" s="2">
         <v>200</v>
@@ -11921,17 +11924,17 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G197" s="39"/>
       <c r="H197" s="46"/>
       <c r="I197" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B198" s="2">
         <v>120</v>
@@ -11940,21 +11943,21 @@
         <v>55</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G198" s="39"/>
       <c r="H198" s="46"/>
       <c r="I198" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B199" s="2">
         <v>200</v>
@@ -11967,17 +11970,17 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G199" s="39"/>
       <c r="H199" s="46"/>
       <c r="I199" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A200" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B200" s="2">
         <v>250</v>
@@ -11990,17 +11993,17 @@
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G200" s="39"/>
       <c r="H200" s="46"/>
       <c r="I200" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="54" x14ac:dyDescent="0.45">
       <c r="A201" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B201" s="2">
         <v>200</v>
@@ -12012,20 +12015,20 @@
         <v>64</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G201" s="39"/>
       <c r="H201" s="46"/>
       <c r="I201" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A202" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B202" s="2">
         <v>250</v>
@@ -12037,20 +12040,20 @@
         <v>60</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G202" s="39"/>
       <c r="H202" s="46"/>
       <c r="I202" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B203" s="2">
         <v>500</v>
@@ -12059,21 +12062,21 @@
         <v>0</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G203" s="39"/>
       <c r="H203" s="46"/>
       <c r="I203" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B204" s="17">
         <v>500</v>
@@ -12085,15 +12088,15 @@
         <v>130</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G204" s="40"/>
       <c r="H204" s="47"/>
       <c r="I204" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -12126,24 +12129,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -12152,15 +12155,15 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -12169,32 +12172,32 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>21</v>
@@ -12203,7 +12206,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
@@ -12211,7 +12214,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>25</v>
@@ -12220,15 +12223,15 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -12237,15 +12240,15 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>30</v>
@@ -12254,7 +12257,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
@@ -12262,7 +12265,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>35</v>
@@ -12271,15 +12274,15 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
@@ -12288,7 +12291,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>41</v>
@@ -12296,7 +12299,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
@@ -12305,7 +12308,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
@@ -12313,7 +12316,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>50</v>
@@ -12322,15 +12325,15 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
@@ -12339,15 +12342,15 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>52</v>
@@ -12356,7 +12359,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>53</v>
@@ -12364,7 +12367,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>54</v>
@@ -12373,15 +12376,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>56</v>
@@ -12390,15 +12393,15 @@
         <v>2</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>56</v>
@@ -12407,7 +12410,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>57</v>
@@ -12415,7 +12418,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>60</v>
@@ -12424,15 +12427,15 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>65</v>
@@ -12441,15 +12444,15 @@
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>65</v>
@@ -12458,7 +12461,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>66</v>
@@ -12466,7 +12469,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>68</v>
@@ -12475,15 +12478,15 @@
         <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>68</v>
@@ -12492,7 +12495,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>69</v>
@@ -12500,7 +12503,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>71</v>
@@ -12509,15 +12512,15 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>71</v>
@@ -12534,7 +12537,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>76</v>
@@ -12543,15 +12546,15 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>79</v>
@@ -12560,15 +12563,15 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>82</v>
@@ -12577,15 +12580,15 @@
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>85</v>
@@ -12594,15 +12597,15 @@
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>87</v>
@@ -12611,15 +12614,15 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>89</v>
@@ -12628,15 +12631,15 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>89</v>
@@ -12653,7 +12656,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>89</v>
@@ -12662,7 +12665,7 @@
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>91</v>
@@ -12670,7 +12673,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>92</v>
@@ -12679,15 +12682,15 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>92</v>
@@ -12696,7 +12699,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>93</v>
@@ -12704,7 +12707,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>94</v>
@@ -12713,15 +12716,15 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>94</v>
@@ -12730,7 +12733,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>95</v>
@@ -12738,7 +12741,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>96</v>
@@ -12747,15 +12750,15 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>96</v>
@@ -12764,7 +12767,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>97</v>
@@ -12772,7 +12775,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -12781,15 +12784,15 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>100</v>
@@ -12798,7 +12801,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>102</v>
@@ -12806,7 +12809,7 @@
     </row>
     <row r="41" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>100</v>
@@ -12815,7 +12818,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>103</v>
@@ -12823,7 +12826,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>104</v>
@@ -12832,15 +12835,15 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>104</v>
@@ -12849,7 +12852,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>105</v>
@@ -12857,7 +12860,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -12866,15 +12869,15 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>106</v>
@@ -12883,15 +12886,15 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>108</v>
@@ -12900,15 +12903,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>108</v>
@@ -12917,15 +12920,15 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>110</v>
@@ -12934,15 +12937,15 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>110</v>
@@ -12951,15 +12954,15 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>110</v>
@@ -12968,7 +12971,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>111</v>
@@ -12976,7 +12979,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>113</v>
@@ -12985,15 +12988,15 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>115</v>
@@ -13002,7 +13005,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>116</v>
@@ -13010,7 +13013,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>117</v>
@@ -13027,7 +13030,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>120</v>
@@ -13036,7 +13039,7 @@
         <v>4</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>121</v>
@@ -13044,7 +13047,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>122</v>
@@ -13053,15 +13056,15 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>124</v>
@@ -13070,15 +13073,15 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>126</v>
@@ -13087,15 +13090,15 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>128</v>
@@ -13104,15 +13107,15 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>128</v>
@@ -13121,7 +13124,7 @@
         <v>4</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>129</v>
@@ -13129,7 +13132,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>130</v>
@@ -13138,15 +13141,15 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>130</v>
@@ -13155,7 +13158,7 @@
         <v>4</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>131</v>
@@ -13163,24 +13166,24 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>134</v>
@@ -13189,15 +13192,15 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>134</v>
@@ -13206,7 +13209,7 @@
         <v>4</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>135</v>
@@ -13214,7 +13217,7 @@
     </row>
     <row r="65" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>137</v>
@@ -13223,7 +13226,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>138</v>
@@ -13231,7 +13234,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>139</v>
@@ -13240,15 +13243,15 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>139</v>
@@ -13257,7 +13260,7 @@
         <v>4</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>140</v>
@@ -13265,7 +13268,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>141</v>
@@ -13274,15 +13277,15 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>141</v>
@@ -13291,7 +13294,7 @@
         <v>4</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>142</v>
@@ -13299,262 +13302,262 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>153</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>160</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>162</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>168</v>
@@ -13563,7 +13566,7 @@
         <v>5</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>169</v>
@@ -13571,7 +13574,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>170</v>
@@ -13580,15 +13583,15 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>172</v>
@@ -13597,15 +13600,15 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>174</v>
@@ -13614,15 +13617,15 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>175</v>
@@ -13631,15 +13634,15 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>176</v>
@@ -13648,7 +13651,7 @@
         <v>4</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>178</v>
@@ -13656,7 +13659,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>180</v>
@@ -13665,49 +13668,49 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>191</v>
@@ -13716,15 +13719,15 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>191</v>
@@ -13733,15 +13736,15 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>191</v>
@@ -13750,7 +13753,7 @@
         <v>4</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>192</v>
@@ -13758,7 +13761,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>194</v>
@@ -13767,15 +13770,15 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>194</v>
@@ -13784,7 +13787,7 @@
         <v>4</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>195</v>
@@ -13792,7 +13795,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>197</v>
@@ -13801,15 +13804,15 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>197</v>
@@ -13818,7 +13821,7 @@
         <v>4</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>198</v>
@@ -13826,7 +13829,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>199</v>
@@ -13835,7 +13838,7 @@
         <v>4</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>200</v>
@@ -13843,7 +13846,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>202</v>
@@ -13852,321 +13855,321 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>60</v>
@@ -14175,245 +14178,245 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>69</v>
@@ -14421,1379 +14424,1379 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D136" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="108" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="81" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="40.5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="54" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="27" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF83A5E8-876C-4E65-99BE-D4210C78228F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19891434-0964-4506-BC77-6B7BDA22BB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="852">
   <si>
     <t>家里</t>
   </si>
@@ -5961,33 +5961,6 @@
     </r>
   </si>
   <si>
-    <t>200，待测，待测</t>
-  </si>
-  <si>
-    <t>250，待测，待测</t>
-  </si>
-  <si>
-    <t>300，待测，待测</t>
-  </si>
-  <si>
-    <t>180，待测，待测</t>
-  </si>
-  <si>
-    <t>400，500，待测</t>
-  </si>
-  <si>
-    <t>250，400，待测</t>
-  </si>
-  <si>
-    <t>500，700，待测</t>
-  </si>
-  <si>
-    <t>200，250，待测</t>
-  </si>
-  <si>
-    <t>220，300，待测</t>
-  </si>
-  <si>
     <t>马克斯的记忆“过去的幽灵”</t>
   </si>
   <si>
@@ -5998,6 +5971,30 @@
   </si>
   <si>
     <t>37.5(怪物出现)/62.5(如何消灭死亡)</t>
+  </si>
+  <si>
+    <t>300，500，1000</t>
+  </si>
+  <si>
+    <t>250，400，800</t>
+  </si>
+  <si>
+    <t>500，700，1400</t>
+  </si>
+  <si>
+    <t>400，500，1000</t>
+  </si>
+  <si>
+    <t>220，300，600</t>
+  </si>
+  <si>
+    <t>200，300，600</t>
+  </si>
+  <si>
+    <t>180，250，500</t>
+  </si>
+  <si>
+    <t>200，250，500</t>
   </si>
 </sst>
 </file>
@@ -9357,7 +9354,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="B97" s="2">
         <v>600</v>
@@ -9557,7 +9554,7 @@
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -9565,7 +9562,7 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="37" t="s">
@@ -9588,7 +9585,7 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="37" t="s">
@@ -11371,7 +11368,7 @@
         <v>711</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>767</v>
@@ -11398,7 +11395,7 @@
         <v>712</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>767</v>
@@ -11425,7 +11422,7 @@
         <v>713</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>765</v>
@@ -11452,7 +11449,7 @@
         <v>714</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>763</v>
@@ -11479,7 +11476,7 @@
         <v>715</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>761</v>
@@ -11533,7 +11530,7 @@
         <v>717</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>760</v>
@@ -11560,7 +11557,7 @@
         <v>718</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>758</v>
@@ -11614,7 +11611,7 @@
         <v>720</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>753</v>
@@ -11668,7 +11665,7 @@
         <v>722</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>755</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19891434-0964-4506-BC77-6B7BDA22BB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7C7E30-E923-4D49-8373-33CAAF47F13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="855">
   <si>
     <t>家里</t>
   </si>
@@ -5995,6 +5995,15 @@
   </si>
   <si>
     <t>200，250，500</t>
+  </si>
+  <si>
+    <t>450，450，450</t>
+  </si>
+  <si>
+    <t>0，48，69</t>
+  </si>
+  <si>
+    <t>变节者阿尔布雷希特</t>
   </si>
 </sst>
 </file>
@@ -9709,13 +9718,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="B112" s="2">
-        <v>450</v>
-      </c>
-      <c r="C112" s="2">
-        <v>69</v>
+        <v>854</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>853</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>577</v>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7C7E30-E923-4D49-8373-33CAAF47F13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2194E1B-4A8A-4124-82DC-7B9519C9E0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6003,7 +6003,7 @@
     <t>0，48，69</t>
   </si>
   <si>
-    <t>变节者阿尔布雷希特</t>
+    <t>变节者阿尔布雷希特（死灵法师）</t>
   </si>
 </sst>
 </file>
@@ -9716,7 +9716,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
         <v>854</v>
       </c>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2194E1B-4A8A-4124-82DC-7B9519C9E0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E50D1F-3B66-42F1-AE72-85BCC0294311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1960,11 +1960,6 @@
 【腐化痕迹】地面上散布着腐化痕迹,踩上去持续掉血。</t>
   </si>
   <si>
-    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
-复活药1瓶；他的武器可以禁疗；受伤后回血,单次上限100(超出部分每5秒补一次),累计400
-可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；无元素抗性</t>
-  </si>
-  <si>
     <t>120~1480（近战）
 180（远程）</t>
   </si>
@@ -2030,41 +2025,6 @@
   </si>
   <si>
     <t>永恒噩梦</t>
-  </si>
-  <si>
-    <t>【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
-【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
-【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文使玩家恐惧5秒；信号符文踩中会吸引附近敌人。
-【英雄模式buff和debuff介绍】英雄模式的增益和减益组合通常为：玩家增益+玩家减益+敌方强化；他们分别的介绍如下：
-【英雄模式玩家增益】
-1.	良好体魄：玩家最大生命值增加40点
-2.	训练警报：帐篷中的敌人没那么致命
-3.	刺骨寒冰：敌人更容易受到寒冷伤害（+50%）
-4.	炽焰：敌人更容易受到火焰伤害（+50%）
-5.	衰败之触：敌人更容易受到衰败伤害（+50%）
-6.	高效治疗：玩家治疗效果提高20%
-7.	治疗之风：每4秒恢复5生命值
-8.	尖锐尖刺：敌人在攻击你时会受到固定10点伤害
-9.	强力重击：玩家攻击造成额外20点伤害
-【英雄模式玩家减益】
-1.	损坏的药水：无法使用药水（包括投掷药水）
-2.	泛黄的卷轴：无法使用卷轴
-3.	胆小的动物：你的恐狼会逃跑，猫咪的被动技能不起作用
-4.	严格饮食：无法使用食物或水
-5.	开放性伤口：受到的治疗效果降低3倍
-6.	被感染的空气：玩家最大生命值减少40点
-7.	生锈护甲：玩家护甲（防御力）降低25%
-8.	无用的陷阱：无法使用陷阱或符文
-9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧
-【英雄模式敌方强化】
-1.	强健体魄：敌人的生命值提高10%，治疗效果也提高
-2.	全速奔跑：敌人移动速度提高40%
-3.	警觉的守卫：敌人视野范围增加30%
-4.	绝处逢生：敌人有20%概率避免死亡并恢复生命值（两条命）
-5.	沉重打击：敌人造成的伤害增加20%
-6.	强悍护甲：敌人防御力提升35%
-7.	符文陷阱：地点中的符文数量增加
-8.	超自然反应：敌人有20%的机会躲避攻击</t>
   </si>
   <si>
     <t>800，2500，5000</t>
@@ -6004,6 +5964,47 @@
   </si>
   <si>
     <t>变节者阿尔布雷希特（死灵法师）</t>
+  </si>
+  <si>
+    <t>装备：金色护卫火剑，尖刺套装；免疫陷阱、冰冻、减速、流血；
+复活药1瓶；他的武器可以禁疗；受伤后回血,单次上限100(超出部分每5秒补一次),累计400
+可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；有元素抗性</t>
+  </si>
+  <si>
+    <t>【副本介绍】大车炮台一共13个帐篷，其中5个为蓝色名字的中尉，只有打死所有中尉才能开启宝箱；大车炮台目前有普通和英雄两种模式，普通模式下玩家进入大门后，大门不会关闭，此外，玩家可在副本内更换随行的恐狼；然后英雄模式下会关闭大门，若是意外死亡，则副本会刷新，丢失所有物品。英雄模式有一共26种buff和debuff组合，下面会详细列出，且英雄模式会出现4种符文作为陷阱，符文在夜晚很难肉眼发现，建议使用夜视药水；另外，普通模式中概率出现的裸体中尉咸味，在英雄模式中他将身着全套尖刺套装出现，概率掉落金色护卫弗兰贝尔格（火焰大剑），奖励可以回档刷取；另外，英雄模式中，请注意从帐篷中走出的敌人会呼叫附近同伴支援
+【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
+【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
+【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文踩中会造成少量伤害，并使玩家恐惧5秒；信号符文踩中会造成少量伤害，并额外召唤一名敌人。
+【英雄模式buff和debuff介绍】英雄模式的增益和减益组合通常为：玩家增益+玩家减益+敌方强化，在8.5.0的更新中做了一些更改，一些特别困难的组合不会同时出现，例如“生锈护甲”和“沉重打击”，即流亡者护甲降低和敌人伤害增加不会同时出现，这些buff和debuff分别的介绍如下：
+【英雄模式玩家增益】
+1.	良好体魄：玩家最大生命值增加40点
+2.	训练警报：帐篷中的敌人没那么致命
+3.	刺骨寒冰：敌人更容易受到寒冷伤害（+50%）
+4.	炽焰：敌人更容易受到火焰伤害（+50%）
+5.	衰败之触：敌人更容易受到衰败伤害（+50%）
+6.	高效治疗：玩家治疗效果提高50%
+7.	治疗之风：每2秒恢复10生命值
+8.	尖锐尖刺：敌人在攻击你时会受到固定10点伤害
+9.	强力重击：玩家攻击造成额外30点伤害
+【英雄模式玩家减益】
+1.	损坏的药水：无法使用药水（包括投掷药水）
+2.	泛黄的卷轴：无法使用卷轴
+3.	胆小的动物：你的恐狼会逃跑，猫咪的被动技能不起作用
+4.	严格饮食：无法使用食物或水
+5.	开放性伤口：受到的治疗效果降低2倍
+6.	被感染的空气：玩家最大生命值减少40点
+7.	生锈护甲：玩家护甲（防御力）减少400
+8.	无用的陷阱：无法使用陷阱或符文
+9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧
+【英雄模式敌方强化】
+1.	强健体魄：敌人的生命值提高10%，治疗效果也提高
+2.	全速奔跑：敌人移动速度和攻击速度都提高40%
+3.	警觉的守卫：敌人视野范围增加30%，无法偷袭敌人
+4.	绝处逢生：敌人有25%概率避免死亡并恢复生命值（两条命）
+5.	沉重打击：敌人造成的伤害增加20%
+6.	强悍护甲：敌人护甲提高200
+7.	符文陷阱：地点中的符文数量增加
+8.	超自然反应：敌人有25%的机会躲避攻击</t>
   </si>
 </sst>
 </file>
@@ -6989,7 +6990,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="41" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -7014,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>4</v>
@@ -7026,7 +7027,7 @@
         <v>624</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7051,7 +7052,7 @@
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -7068,7 +7069,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>4</v>
@@ -7080,7 +7081,7 @@
         <v>624</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -7103,7 +7104,7 @@
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -7126,7 +7127,7 @@
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -7149,7 +7150,7 @@
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -7172,7 +7173,7 @@
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -7197,12 +7198,12 @@
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B10" s="2">
         <v>90</v>
@@ -7218,11 +7219,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
@@ -7245,7 +7246,7 @@
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7264,11 +7265,11 @@
       <c r="E12" s="2"/>
       <c r="F12" s="19"/>
       <c r="G12" s="21" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7287,11 +7288,11 @@
       <c r="E13" s="2"/>
       <c r="F13" s="19"/>
       <c r="G13" s="21" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7310,11 +7311,11 @@
         <v>28</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -7333,11 +7334,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="19"/>
       <c r="G15" s="21" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -7362,7 +7363,7 @@
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7385,7 +7386,7 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7406,11 +7407,11 @@
         <v>36</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -7433,7 +7434,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7458,7 +7459,7 @@
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7477,11 +7478,11 @@
       <c r="E21" s="2"/>
       <c r="F21" s="19"/>
       <c r="G21" s="21" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7495,18 +7496,18 @@
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="19" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -7520,7 +7521,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="19" t="s">
@@ -7531,7 +7532,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -7552,11 +7553,11 @@
         <v>51</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7577,11 +7578,11 @@
         <v>53</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7602,11 +7603,11 @@
         <v>55</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -7627,11 +7628,11 @@
         <v>57</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -7645,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -7654,7 +7655,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -7677,7 +7678,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -7702,7 +7703,7 @@
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -7727,7 +7728,7 @@
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -7748,11 +7749,11 @@
         <v>72</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H32" s="32"/>
       <c r="I32" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7777,12 +7778,12 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -7794,7 +7795,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>4</v>
@@ -7806,7 +7807,7 @@
         <v>624</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -7825,13 +7826,13 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H35" s="48" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -7854,7 +7855,7 @@
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -7873,11 +7874,11 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="19" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -7898,11 +7899,11 @@
         <v>81</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -7921,11 +7922,11 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H39" s="49"/>
       <c r="I39" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7946,11 +7947,11 @@
         <v>84</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -7969,11 +7970,11 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="19" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
@@ -7992,11 +7993,11 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="19" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -8017,11 +8018,11 @@
         <v>88</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
@@ -8042,11 +8043,11 @@
         <v>90</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8067,11 +8068,11 @@
         <v>93</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8092,11 +8093,11 @@
         <v>95</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8117,11 +8118,11 @@
         <v>97</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H47" s="49"/>
       <c r="I47" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -8146,7 +8147,7 @@
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8164,14 +8165,14 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8192,11 +8193,11 @@
         <v>105</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8217,11 +8218,11 @@
         <v>107</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8242,11 +8243,11 @@
         <v>109</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -8267,11 +8268,11 @@
         <v>111</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H53" s="50"/>
       <c r="I53" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -8288,7 +8289,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>4</v>
@@ -8300,12 +8301,12 @@
         <v>624</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -8321,13 +8322,13 @@
         <v>114</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H55" s="48" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -8348,11 +8349,11 @@
         <v>116</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H56" s="49"/>
       <c r="I56" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8373,11 +8374,11 @@
         <v>118</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H57" s="49"/>
       <c r="I57" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8398,11 +8399,11 @@
         <v>114</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H58" s="49"/>
       <c r="I58" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8423,11 +8424,11 @@
         <v>121</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H59" s="49"/>
       <c r="I59" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8448,11 +8449,11 @@
         <v>123</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H60" s="49"/>
       <c r="I60" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -8473,11 +8474,11 @@
         <v>125</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H61" s="49"/>
       <c r="I61" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -8498,11 +8499,11 @@
         <v>127</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="H62" s="49"/>
       <c r="I62" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -8523,11 +8524,11 @@
         <v>129</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H63" s="49"/>
       <c r="I63" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -8547,14 +8548,14 @@
         <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H64" s="49"/>
       <c r="I64" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="162.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -8568,18 +8569,18 @@
         <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H65" s="50"/>
       <c r="I65" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -8596,7 +8597,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>4</v>
@@ -8608,7 +8609,7 @@
         <v>624</v>
       </c>
       <c r="I66" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -8626,7 +8627,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G67" s="19" t="s">
         <v>136</v>
@@ -8635,7 +8636,7 @@
         <v>625</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8653,14 +8654,14 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G68" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H68" s="49"/>
       <c r="I68" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.45">
@@ -8678,14 +8679,14 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G69" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H69" s="49"/>
       <c r="I69" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -8703,14 +8704,14 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>136</v>
       </c>
       <c r="H70" s="49"/>
       <c r="I70" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -8727,7 +8728,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>4</v>
@@ -8739,7 +8740,7 @@
         <v>624</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -8762,7 +8763,7 @@
       </c>
       <c r="H72" s="32"/>
       <c r="I72" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -8785,7 +8786,7 @@
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8810,7 +8811,7 @@
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -8827,7 +8828,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>4</v>
@@ -8839,7 +8840,7 @@
         <v>624</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8847,24 +8848,24 @@
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8872,24 +8873,24 @@
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>822</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
       <c r="I77" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8897,24 +8898,24 @@
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
       <c r="I78" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8922,24 +8923,24 @@
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
       <c r="I79" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8947,24 +8948,24 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
       <c r="I80" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
@@ -8972,13 +8973,13 @@
         <v>595</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
@@ -8989,7 +8990,7 @@
       </c>
       <c r="H81" s="32"/>
       <c r="I81" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8997,24 +8998,24 @@
         <v>596</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
       <c r="I82" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9022,24 +9023,24 @@
         <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
       <c r="I83" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9047,24 +9048,24 @@
         <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>807</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -9072,13 +9073,13 @@
         <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -9089,7 +9090,7 @@
       </c>
       <c r="H85" s="32"/>
       <c r="I85" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -9097,29 +9098,29 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A87" s="14" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B87" s="2">
         <v>250</v>
@@ -9139,7 +9140,7 @@
       </c>
       <c r="H87" s="32"/>
       <c r="I87" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -9156,7 +9157,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>4</v>
@@ -9168,7 +9169,7 @@
         <v>624</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -9193,7 +9194,7 @@
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -9216,7 +9217,7 @@
       </c>
       <c r="H90" s="32"/>
       <c r="I90" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -9239,7 +9240,7 @@
       </c>
       <c r="H91" s="32"/>
       <c r="I91" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -9262,7 +9263,7 @@
       </c>
       <c r="H92" s="32"/>
       <c r="I92" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -9285,7 +9286,7 @@
       </c>
       <c r="H93" s="32"/>
       <c r="I93" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -9310,7 +9311,7 @@
       </c>
       <c r="H94" s="32"/>
       <c r="I94" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -9333,7 +9334,7 @@
       </c>
       <c r="H95" s="32"/>
       <c r="I95" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -9358,12 +9359,12 @@
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B97" s="2">
         <v>600</v>
@@ -9381,12 +9382,12 @@
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B98" s="2">
         <v>40</v>
@@ -9404,12 +9405,12 @@
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>578</v>
@@ -9429,7 +9430,7 @@
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -9454,7 +9455,7 @@
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
@@ -9479,7 +9480,7 @@
       </c>
       <c r="H101" s="32"/>
       <c r="I101" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -9504,7 +9505,7 @@
       </c>
       <c r="H102" s="32"/>
       <c r="I102" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
@@ -9529,7 +9530,7 @@
       </c>
       <c r="H103" s="32"/>
       <c r="I103" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
@@ -9552,7 +9553,7 @@
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -9563,7 +9564,7 @@
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -9571,11 +9572,11 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
@@ -9594,11 +9595,11 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -9621,7 +9622,7 @@
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
@@ -9644,7 +9645,7 @@
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
@@ -9667,7 +9668,7 @@
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
@@ -9690,7 +9691,7 @@
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -9713,18 +9714,18 @@
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>577</v>
@@ -9738,7 +9739,7 @@
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9756,14 +9757,14 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G113" s="19" t="s">
         <v>193</v>
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
@@ -9788,7 +9789,7 @@
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
@@ -9813,7 +9814,7 @@
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="121.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -9831,14 +9832,14 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G116" s="19" t="s">
         <v>228</v>
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
@@ -9855,7 +9856,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>4</v>
@@ -9867,7 +9868,7 @@
         <v>624</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
@@ -9892,7 +9893,7 @@
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
@@ -9917,7 +9918,7 @@
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
@@ -9942,7 +9943,7 @@
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
@@ -9967,7 +9968,7 @@
       </c>
       <c r="H121" s="32"/>
       <c r="I121" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.45">
@@ -9992,7 +9993,7 @@
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.45">
@@ -10017,7 +10018,7 @@
       </c>
       <c r="H123" s="32"/>
       <c r="I123" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.45">
@@ -10042,7 +10043,7 @@
       </c>
       <c r="H124" s="32"/>
       <c r="I124" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.45">
@@ -10067,7 +10068,7 @@
       </c>
       <c r="H125" s="32"/>
       <c r="I125" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10092,7 +10093,7 @@
       </c>
       <c r="H126" s="32"/>
       <c r="I126" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10117,7 +10118,7 @@
       </c>
       <c r="H127" s="32"/>
       <c r="I127" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -10135,14 +10136,14 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>585</v>
       </c>
       <c r="H128" s="32"/>
       <c r="I128" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.45">
@@ -10159,7 +10160,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>4</v>
@@ -10171,7 +10172,7 @@
         <v>624</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.45">
@@ -10196,7 +10197,7 @@
       </c>
       <c r="H130" s="32"/>
       <c r="I130" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.45">
@@ -10219,7 +10220,7 @@
       </c>
       <c r="H131" s="32"/>
       <c r="I131" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.45">
@@ -10242,7 +10243,7 @@
       </c>
       <c r="H132" s="32"/>
       <c r="I132" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.45">
@@ -10267,7 +10268,7 @@
       </c>
       <c r="H133" s="32"/>
       <c r="I133" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.45">
@@ -10290,7 +10291,7 @@
       </c>
       <c r="H134" s="32"/>
       <c r="I134" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.45">
@@ -10315,7 +10316,7 @@
       </c>
       <c r="H135" s="32"/>
       <c r="I135" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -10340,7 +10341,7 @@
       </c>
       <c r="H136" s="32"/>
       <c r="I136" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.45">
@@ -10367,7 +10368,7 @@
       </c>
       <c r="H137" s="32"/>
       <c r="I137" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.45">
@@ -10392,12 +10393,12 @@
       </c>
       <c r="H138" s="32"/>
       <c r="I138" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B139" s="2">
         <v>120</v>
@@ -10410,14 +10411,14 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.45">
@@ -10442,7 +10443,7 @@
       </c>
       <c r="H140" s="32"/>
       <c r="I140" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.45">
@@ -10467,7 +10468,7 @@
       </c>
       <c r="H141" s="32"/>
       <c r="I141" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.45">
@@ -10492,7 +10493,7 @@
       </c>
       <c r="H142" s="32"/>
       <c r="I142" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -10517,7 +10518,7 @@
       </c>
       <c r="H143" s="32"/>
       <c r="I143" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.45">
@@ -10534,7 +10535,7 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>4</v>
@@ -10546,7 +10547,7 @@
         <v>624</v>
       </c>
       <c r="I144" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.45">
@@ -10554,13 +10555,13 @@
         <v>265</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C145" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -10571,7 +10572,7 @@
       </c>
       <c r="H145" s="32"/>
       <c r="I145" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.45">
@@ -10579,10 +10580,10 @@
         <v>267</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>577</v>
@@ -10596,7 +10597,7 @@
       </c>
       <c r="H146" s="32"/>
       <c r="I146" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -10604,13 +10605,13 @@
         <v>269</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -10619,7 +10620,7 @@
       </c>
       <c r="H147" s="32"/>
       <c r="I147" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -10627,13 +10628,13 @@
         <v>270</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -10642,7 +10643,7 @@
       </c>
       <c r="H148" s="32"/>
       <c r="I148" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.45">
@@ -10650,13 +10651,13 @@
         <v>271</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>788</v>
-      </c>
       <c r="D149" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -10667,7 +10668,7 @@
       </c>
       <c r="H149" s="32"/>
       <c r="I149" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10675,10 +10676,10 @@
         <v>273</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>577</v>
@@ -10692,12 +10693,12 @@
       </c>
       <c r="H150" s="32"/>
       <c r="I150" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -10709,7 +10710,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>4</v>
@@ -10721,7 +10722,7 @@
         <v>624</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.45">
@@ -10746,34 +10747,34 @@
       </c>
       <c r="H152" s="32"/>
       <c r="I152" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A153" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E153" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D153" s="2" t="s">
+      <c r="F153" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="G153" s="19" t="s">
         <v>276</v>
       </c>
       <c r="H153" s="32"/>
       <c r="I153" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10800,7 +10801,7 @@
       </c>
       <c r="H154" s="32"/>
       <c r="I154" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10827,7 +10828,7 @@
       </c>
       <c r="H155" s="32"/>
       <c r="I155" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10854,7 +10855,7 @@
       </c>
       <c r="H156" s="32"/>
       <c r="I156" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10881,7 +10882,7 @@
       </c>
       <c r="H157" s="32"/>
       <c r="I157" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10908,7 +10909,7 @@
       </c>
       <c r="H158" s="32"/>
       <c r="I158" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10935,7 +10936,7 @@
       </c>
       <c r="H159" s="32"/>
       <c r="I159" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10962,7 +10963,7 @@
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10989,7 +10990,7 @@
       </c>
       <c r="H161" s="32"/>
       <c r="I161" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11016,7 +11017,7 @@
       </c>
       <c r="H162" s="32"/>
       <c r="I162" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -11036,14 +11037,14 @@
         <v>309</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G163" s="19" t="s">
         <v>281</v>
       </c>
       <c r="H163" s="32"/>
       <c r="I163" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -11063,14 +11064,14 @@
         <v>314</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G164" s="19" t="s">
         <v>295</v>
       </c>
       <c r="H164" s="32"/>
       <c r="I164" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="202.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -11078,31 +11079,31 @@
         <v>570</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G165" s="19" t="s">
         <v>276</v>
       </c>
       <c r="H165" s="32"/>
       <c r="I165" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -11114,7 +11115,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>4</v>
@@ -11126,72 +11127,72 @@
         <v>624</v>
       </c>
       <c r="I166" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H167" s="51" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="I167" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="G168" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H168" s="51"/>
       <c r="I168" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>577</v>
@@ -11200,154 +11201,154 @@
         <v>577</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G169" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H169" s="51"/>
       <c r="I169" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>577</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H170" s="51"/>
       <c r="I170" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H171" s="51"/>
       <c r="I171" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="E172" s="6" t="s">
         <v>739</v>
       </c>
-      <c r="D172" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="E172" s="6" t="s">
-        <v>741</v>
-      </c>
       <c r="F172" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H172" s="51"/>
       <c r="I172" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>577</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G173" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H173" s="51"/>
       <c r="I173" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="E174" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="D174" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="E174" s="6" t="s">
-        <v>744</v>
-      </c>
       <c r="F174" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G174" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H174" s="51"/>
       <c r="I174" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -11359,7 +11360,7 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>4</v>
@@ -11369,331 +11370,331 @@
       </c>
       <c r="H175" s="51"/>
       <c r="I175" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H176" s="51"/>
       <c r="I176" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G177" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H177" s="51"/>
       <c r="I177" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G178" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H178" s="51"/>
       <c r="I178" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G179" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H179" s="51"/>
       <c r="I179" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G180" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H180" s="51"/>
       <c r="I180" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G181" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H181" s="51"/>
       <c r="I181" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="G182" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H182" s="51"/>
       <c r="I182" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H183" s="51"/>
       <c r="I183" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G184" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H184" s="51"/>
       <c r="I184" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G185" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H185" s="51"/>
       <c r="I185" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G186" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H186" s="51"/>
       <c r="I186" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A187" s="14" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G187" s="29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H187" s="51"/>
       <c r="I187" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11710,7 +11711,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>4</v>
@@ -11722,7 +11723,7 @@
         <v>624</v>
       </c>
       <c r="I188" s="31" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11748,10 +11749,10 @@
         <v>316</v>
       </c>
       <c r="H189" s="45" t="s">
-        <v>642</v>
+        <v>854</v>
       </c>
       <c r="I189" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11774,7 +11775,7 @@
       <c r="G190" s="39"/>
       <c r="H190" s="46"/>
       <c r="I190" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11797,7 +11798,7 @@
       <c r="G191" s="39"/>
       <c r="H191" s="46"/>
       <c r="I191" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11820,7 +11821,7 @@
       <c r="G192" s="39"/>
       <c r="H192" s="46"/>
       <c r="I192" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11838,12 +11839,12 @@
       </c>
       <c r="E193" s="2"/>
       <c r="F193" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G193" s="39"/>
       <c r="H193" s="46"/>
       <c r="I193" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11866,7 +11867,7 @@
       <c r="G194" s="39"/>
       <c r="H194" s="46"/>
       <c r="I194" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11889,7 +11890,7 @@
       <c r="G195" s="39"/>
       <c r="H195" s="46"/>
       <c r="I195" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11912,7 +11913,7 @@
       <c r="G196" s="39"/>
       <c r="H196" s="46"/>
       <c r="I196" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11935,7 +11936,7 @@
       <c r="G197" s="39"/>
       <c r="H197" s="46"/>
       <c r="I197" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11958,7 +11959,7 @@
       <c r="G198" s="39"/>
       <c r="H198" s="46"/>
       <c r="I198" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -11981,7 +11982,7 @@
       <c r="G199" s="39"/>
       <c r="H199" s="46"/>
       <c r="I199" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -12004,7 +12005,7 @@
       <c r="G200" s="39"/>
       <c r="H200" s="46"/>
       <c r="I200" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -12029,7 +12030,7 @@
       <c r="G201" s="39"/>
       <c r="H201" s="46"/>
       <c r="I201" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -12054,7 +12055,7 @@
       <c r="G202" s="39"/>
       <c r="H202" s="46"/>
       <c r="I202" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -12077,7 +12078,7 @@
       <c r="G203" s="39"/>
       <c r="H203" s="46"/>
       <c r="I203" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -12097,12 +12098,12 @@
         <v>606</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>626</v>
+        <v>853</v>
       </c>
       <c r="G204" s="40"/>
       <c r="H204" s="47"/>
       <c r="I204" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E50D1F-3B66-42F1-AE72-85BCC0294311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33177E14-6943-4B75-BCB7-E4BB58C93B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5995,13 +5995,13 @@
 6.	被感染的空气：玩家最大生命值减少40点
 7.	生锈护甲：玩家护甲（防御力）减少400
 8.	无用的陷阱：无法使用陷阱或符文
-9.	失控的狂怒：敌人免疫冻结、眩晕和恐惧
+9.	失控的狂怒：敌人免疫冻结，眩晕和恐惧
 【英雄模式敌方强化】
-1.	强健体魄：敌人的生命值提高10%，治疗效果也提高
+1.	强健体魄：敌人的生命值提高，治疗效果也提高
 2.	全速奔跑：敌人移动速度和攻击速度都提高40%
 3.	警觉的守卫：敌人视野范围增加30%，无法偷袭敌人
 4.	绝处逢生：敌人有25%概率避免死亡并恢复生命值（两条命）
-5.	沉重打击：敌人造成的伤害增加20%
+5.	沉重打击：敌人造成的伤害增加40%
 6.	强悍护甲：敌人护甲提高200
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有25%的机会躲避攻击</t>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33177E14-6943-4B75-BCB7-E4BB58C93B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0936DD2-A5BD-43D5-A425-1716F006DBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2187,15 +2187,6 @@
   </si>
   <si>
     <t>第一季红猎；普通被弃者地下城2层(少见)</t>
-  </si>
-  <si>
-    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，掷斧者，女祭司，屠宰者还有酷吏地下城；第二层的敌人包括痛苦者，猎头者，女祭司，惩罚者，残忍酷吏地下城和火焰守卫；第三层敌人主要就是领主卡恩。
-【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
-【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
-（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
-（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
-（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
-【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
   </si>
   <si>
     <t>被弃者地下城</t>
@@ -6005,6 +5996,15 @@
 6.	强悍护甲：敌人护甲提高200
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有25%的机会躲避攻击</t>
+  </si>
+  <si>
+    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，掷斧者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，猎头者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
+【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
+【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
+（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
+（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
+（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
+【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
   </si>
 </sst>
 </file>
@@ -6990,7 +6990,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="41" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F2" s="18" t="s">
         <v>4</v>
@@ -7027,7 +7027,7 @@
         <v>624</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -7069,7 +7069,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>4</v>
@@ -7081,7 +7081,7 @@
         <v>624</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="H31" s="32"/>
       <c r="I31" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="H32" s="32"/>
       <c r="I32" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>1</v>
@@ -7795,7 +7795,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>4</v>
@@ -7807,7 +7807,7 @@
         <v>624</v>
       </c>
       <c r="I34" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -7829,10 +7829,10 @@
         <v>676</v>
       </c>
       <c r="H35" s="48" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H39" s="49"/>
       <c r="I39" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="H40" s="49"/>
       <c r="I40" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="25.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="29.65" customHeight="1" x14ac:dyDescent="0.45">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="H43" s="49"/>
       <c r="I43" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="H44" s="49"/>
       <c r="I44" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H45" s="49"/>
       <c r="I45" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="H46" s="49"/>
       <c r="I46" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="H47" s="49"/>
       <c r="I47" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="H48" s="49"/>
       <c r="I48" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="H49" s="49"/>
       <c r="I49" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="H50" s="49"/>
       <c r="I50" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="H51" s="49"/>
       <c r="I51" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="33.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H52" s="49"/>
       <c r="I52" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="H53" s="50"/>
       <c r="I53" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -8289,7 +8289,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>4</v>
@@ -8301,12 +8301,12 @@
         <v>624</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A55" s="11" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B55" s="2">
         <v>180</v>
@@ -8322,16 +8322,16 @@
         <v>114</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H55" s="48" t="s">
-        <v>687</v>
+        <v>854</v>
       </c>
       <c r="I55" s="37" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="11" t="s">
         <v>115</v>
       </c>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="H56" s="49"/>
       <c r="I56" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="H57" s="49"/>
       <c r="I57" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="H58" s="49"/>
       <c r="I58" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="H59" s="49"/>
       <c r="I59" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="24.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="H60" s="49"/>
       <c r="I60" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="H61" s="49"/>
       <c r="I61" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="H62" s="49"/>
       <c r="I62" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="H63" s="49"/>
       <c r="I63" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -8548,14 +8548,14 @@
         <v>152</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G64" s="19" t="s">
         <v>670</v>
       </c>
       <c r="H64" s="49"/>
       <c r="I64" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="162.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="H65" s="50"/>
       <c r="I65" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -8597,7 +8597,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>4</v>
@@ -8609,7 +8609,7 @@
         <v>624</v>
       </c>
       <c r="I66" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -8636,7 +8636,7 @@
         <v>625</v>
       </c>
       <c r="I67" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H68" s="49"/>
       <c r="I68" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="81" x14ac:dyDescent="0.45">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="H69" s="49"/>
       <c r="I69" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="H70" s="49"/>
       <c r="I70" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
@@ -8728,7 +8728,7 @@
         <v>3</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>4</v>
@@ -8740,7 +8740,7 @@
         <v>624</v>
       </c>
       <c r="I71" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="H72" s="32"/>
       <c r="I72" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="H74" s="32"/>
       <c r="I74" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -8828,7 +8828,7 @@
         <v>3</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>4</v>
@@ -8840,7 +8840,7 @@
         <v>624</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8848,24 +8848,24 @@
         <v>149</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>817</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8873,24 +8873,24 @@
         <v>151</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H77" s="32"/>
       <c r="I77" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8898,24 +8898,24 @@
         <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>821</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H78" s="32"/>
       <c r="I78" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8923,24 +8923,24 @@
         <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G79" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H79" s="32"/>
       <c r="I79" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -8948,24 +8948,24 @@
         <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G80" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H80" s="32"/>
       <c r="I80" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
@@ -8973,13 +8973,13 @@
         <v>595</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H81" s="32"/>
       <c r="I81" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -8998,24 +8998,24 @@
         <v>596</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>799</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G82" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H82" s="32"/>
       <c r="I82" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9023,24 +9023,24 @@
         <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G83" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H83" s="32"/>
       <c r="I83" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -9048,24 +9048,24 @@
         <v>161</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G84" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="37" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -9073,13 +9073,13 @@
         <v>162</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="H85" s="32"/>
       <c r="I85" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="229.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -9098,24 +9098,24 @@
         <v>164</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>810</v>
-      </c>
       <c r="D86" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G86" s="19" t="s">
         <v>150</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="H87" s="32"/>
       <c r="I87" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -9157,7 +9157,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>4</v>
@@ -9169,7 +9169,7 @@
         <v>624</v>
       </c>
       <c r="I88" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="H90" s="32"/>
       <c r="I90" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="H91" s="32"/>
       <c r="I91" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="H92" s="32"/>
       <c r="I92" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H93" s="32"/>
       <c r="I93" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="H94" s="32"/>
       <c r="I94" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="H95" s="32"/>
       <c r="I95" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97" s="11" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B97" s="2">
         <v>600</v>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="27.4" customHeight="1" x14ac:dyDescent="0.45">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H100" s="32"/>
       <c r="I100" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H101" s="32"/>
       <c r="I101" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="H102" s="32"/>
       <c r="I102" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="H103" s="32"/>
       <c r="I103" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -9564,7 +9564,7 @@
         <v>500</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D105" s="2">
         <v>36</v>
@@ -9572,11 +9572,11 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="19" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
@@ -9595,11 +9595,11 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="19" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -9714,18 +9714,18 @@
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A112" s="13" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>850</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>851</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>577</v>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="88.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="121.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
@@ -9856,7 +9856,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>4</v>
@@ -9868,7 +9868,7 @@
         <v>624</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="H121" s="32"/>
       <c r="I121" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.45">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.45">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="H123" s="32"/>
       <c r="I123" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.45">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="H124" s="32"/>
       <c r="I124" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.45">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="H125" s="32"/>
       <c r="I125" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="H126" s="32"/>
       <c r="I126" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H127" s="32"/>
       <c r="I127" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="94.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="H128" s="32"/>
       <c r="I128" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.45">
@@ -10160,7 +10160,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>4</v>
@@ -10172,7 +10172,7 @@
         <v>624</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.45">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="H130" s="32"/>
       <c r="I130" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.45">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="H131" s="32"/>
       <c r="I131" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.45">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="H132" s="32"/>
       <c r="I132" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.45">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H133" s="32"/>
       <c r="I133" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.45">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="H134" s="32"/>
       <c r="I134" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.45">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="H135" s="32"/>
       <c r="I135" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="H136" s="32"/>
       <c r="I136" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.45">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H137" s="32"/>
       <c r="I137" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.45">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="H138" s="32"/>
       <c r="I138" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139" s="13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B139" s="2">
         <v>120</v>
@@ -10411,14 +10411,14 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G139" s="19" t="s">
         <v>692</v>
-      </c>
-      <c r="G139" s="19" t="s">
-        <v>693</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.45">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="H140" s="32"/>
       <c r="I140" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.45">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="H141" s="32"/>
       <c r="I141" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.45">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="H142" s="32"/>
       <c r="I142" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="27.4" thickBot="1" x14ac:dyDescent="0.5">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="H143" s="32"/>
       <c r="I143" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.45">
@@ -10535,7 +10535,7 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>4</v>
@@ -10547,7 +10547,7 @@
         <v>624</v>
       </c>
       <c r="I144" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.45">
@@ -10555,13 +10555,13 @@
         <v>265</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="H145" s="32"/>
       <c r="I145" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.45">
@@ -10580,10 +10580,10 @@
         <v>267</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>577</v>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="H146" s="32"/>
       <c r="I146" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -10605,13 +10605,13 @@
         <v>269</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="H147" s="32"/>
       <c r="I147" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -10628,13 +10628,13 @@
         <v>270</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="H148" s="32"/>
       <c r="I148" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.45">
@@ -10651,13 +10651,13 @@
         <v>271</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" s="2" t="s">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="H149" s="32"/>
       <c r="I149" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -10676,10 +10676,10 @@
         <v>273</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>577</v>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="H150" s="32"/>
       <c r="I150" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>1</v>
@@ -10710,7 +10710,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>4</v>
@@ -10722,7 +10722,7 @@
         <v>624</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.45">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="H152" s="32"/>
       <c r="I152" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="H153" s="32"/>
       <c r="I153" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H154" s="32"/>
       <c r="I154" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="H155" s="32"/>
       <c r="I155" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="H156" s="32"/>
       <c r="I156" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="H157" s="32"/>
       <c r="I157" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="H158" s="32"/>
       <c r="I158" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="H159" s="32"/>
       <c r="I159" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="H161" s="32"/>
       <c r="I161" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="H162" s="32"/>
       <c r="I162" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="67.5" x14ac:dyDescent="0.45">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="H163" s="32"/>
       <c r="I163" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="H164" s="32"/>
       <c r="I164" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="202.9" thickBot="1" x14ac:dyDescent="0.5">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H165" s="32"/>
       <c r="I165" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166" s="10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>1</v>
@@ -11115,7 +11115,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>4</v>
@@ -11127,72 +11127,72 @@
         <v>624</v>
       </c>
       <c r="I166" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A167" s="11" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D167" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E167" s="6" t="s">
         <v>722</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>723</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H167" s="51" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="I167" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.45">
       <c r="A168" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E168" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="E168" s="6" t="s">
-        <v>723</v>
-      </c>
       <c r="F168" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G168" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H168" s="51"/>
       <c r="I168" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="94.5" x14ac:dyDescent="0.45">
       <c r="A169" s="11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>577</v>
@@ -11201,154 +11201,154 @@
         <v>577</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G169" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H169" s="51"/>
       <c r="I169" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="81" x14ac:dyDescent="0.45">
       <c r="A170" s="11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>577</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H170" s="51"/>
       <c r="I170" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="95.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A171" s="11" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D171" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E171" s="6" t="s">
         <v>732</v>
       </c>
-      <c r="E171" s="6" t="s">
-        <v>733</v>
-      </c>
       <c r="F171" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G171" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H171" s="51"/>
       <c r="I171" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="E172" s="6" t="s">
         <v>738</v>
       </c>
-      <c r="E172" s="6" t="s">
-        <v>739</v>
-      </c>
       <c r="F172" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H172" s="51"/>
       <c r="I172" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="13" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>577</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G173" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H173" s="51"/>
       <c r="I173" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="13" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C174" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="D174" s="2" t="s">
+      <c r="E174" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="E174" s="6" t="s">
-        <v>742</v>
-      </c>
       <c r="F174" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G174" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H174" s="51"/>
       <c r="I174" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>1</v>
@@ -11360,7 +11360,7 @@
         <v>3</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>4</v>
@@ -11370,331 +11370,331 @@
       </c>
       <c r="H175" s="51"/>
       <c r="I175" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G176" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H176" s="51"/>
       <c r="I176" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G177" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H177" s="51"/>
       <c r="I177" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G178" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H178" s="51"/>
       <c r="I178" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G179" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H179" s="51"/>
       <c r="I179" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="135.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G180" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H180" s="51"/>
       <c r="I180" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A181" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C181" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D181" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G181" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H181" s="51"/>
       <c r="I181" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="139.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A182" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G182" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H182" s="51"/>
       <c r="I182" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="132.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A183" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G183" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H183" s="51"/>
       <c r="I183" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="166.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A184" s="14" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G184" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H184" s="51"/>
       <c r="I184" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A185" s="14" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="E185" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="E185" s="7" t="s">
-        <v>750</v>
-      </c>
       <c r="F185" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G185" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H185" s="51"/>
       <c r="I185" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="124.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A186" s="14" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G186" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H186" s="51"/>
       <c r="I186" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A187" s="14" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G187" s="29" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H187" s="51"/>
       <c r="I187" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11711,7 +11711,7 @@
         <v>3</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>4</v>
@@ -11723,7 +11723,7 @@
         <v>624</v>
       </c>
       <c r="I188" s="31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11749,10 +11749,10 @@
         <v>316</v>
       </c>
       <c r="H189" s="45" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I189" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11775,7 +11775,7 @@
       <c r="G190" s="39"/>
       <c r="H190" s="46"/>
       <c r="I190" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11798,7 +11798,7 @@
       <c r="G191" s="39"/>
       <c r="H191" s="46"/>
       <c r="I191" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11821,7 +11821,7 @@
       <c r="G192" s="39"/>
       <c r="H192" s="46"/>
       <c r="I192" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11844,7 +11844,7 @@
       <c r="G193" s="39"/>
       <c r="H193" s="46"/>
       <c r="I193" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11867,7 +11867,7 @@
       <c r="G194" s="39"/>
       <c r="H194" s="46"/>
       <c r="I194" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11890,7 +11890,7 @@
       <c r="G195" s="39"/>
       <c r="H195" s="46"/>
       <c r="I195" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11913,7 +11913,7 @@
       <c r="G196" s="39"/>
       <c r="H196" s="46"/>
       <c r="I196" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11936,7 +11936,7 @@
       <c r="G197" s="39"/>
       <c r="H197" s="46"/>
       <c r="I197" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -11959,7 +11959,7 @@
       <c r="G198" s="39"/>
       <c r="H198" s="46"/>
       <c r="I198" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -11982,7 +11982,7 @@
       <c r="G199" s="39"/>
       <c r="H199" s="46"/>
       <c r="I199" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
@@ -12005,7 +12005,7 @@
       <c r="G200" s="39"/>
       <c r="H200" s="46"/>
       <c r="I200" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="54" x14ac:dyDescent="0.45">
@@ -12030,7 +12030,7 @@
       <c r="G201" s="39"/>
       <c r="H201" s="46"/>
       <c r="I201" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -12055,7 +12055,7 @@
       <c r="G202" s="39"/>
       <c r="H202" s="46"/>
       <c r="I202" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
@@ -12078,7 +12078,7 @@
       <c r="G203" s="39"/>
       <c r="H203" s="46"/>
       <c r="I203" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -12098,12 +12098,12 @@
         <v>606</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G204" s="40"/>
       <c r="H204" s="47"/>
       <c r="I204" s="37" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/敌人数据.xlsx
+++ b/data-source/敌人数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0936DD2-A5BD-43D5-A425-1716F006DBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7899CE5-1285-4559-8779-0FB046075A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5962,10 +5962,19 @@
 可用骷髅、雷电卷轴、火符文、眩晕技能、夜游神镰刀应对；有元素抗性</t>
   </si>
   <si>
+    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，掷斧者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，猎头者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
+【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
+【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
+（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
+（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
+（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
+【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
+  </si>
+  <si>
     <t>【副本介绍】大车炮台一共13个帐篷，其中5个为蓝色名字的中尉，只有打死所有中尉才能开启宝箱；大车炮台目前有普通和英雄两种模式，普通模式下玩家进入大门后，大门不会关闭，此外，玩家可在副本内更换随行的恐狼；然后英雄模式下会关闭大门，若是意外死亡，则副本会刷新，丢失所有物品。英雄模式有一共26种buff和debuff组合，下面会详细列出，且英雄模式会出现4种符文作为陷阱，符文在夜晚很难肉眼发现，建议使用夜视药水；另外，普通模式中概率出现的裸体中尉咸味，在英雄模式中他将身着全套尖刺套装出现，概率掉落金色护卫弗兰贝尔格（火焰大剑），奖励可以回档刷取；另外，英雄模式中，请注意从帐篷中走出的敌人会呼叫附近同伴支援
 【小兵回血机制】受伤后立即回血,单次上限 40,超出部分每 5 秒补一次,总量 200 封顶。举例:掉 35 血 → 立刻回满 35;掉 50 血 → 先回 40,5 秒后再回 10。
 【中尉回血机制】受伤后立即回血,单次上限 100,超出部分每 5 秒补一次,累计 400 封顶。举例:掉 80 血 → 立刻回满 80;掉 150 血 → 先回 100,5 秒后再回 50。
-【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成70点火焰伤害并附加200的持续烧伤；冰冻符文造成30点冰冻伤害并冰冻3秒；恐惧符文踩中会造成少量伤害，并使玩家恐惧5秒；信号符文踩中会造成少量伤害，并额外召唤一名敌人。
+【英雄模式陷阱介绍】符文陷阱有四种：火焰符文造成50点火焰伤害并附加15*10的持续烧伤；冰冻符文造成50点冰冻伤害并冰冻10秒；恐惧符文踩中会造成少量伤害，并使玩家恐惧5秒；信号符文踩中会造成少量伤害，并额外召唤一名敌人。
 【英雄模式buff和debuff介绍】英雄模式的增益和减益组合通常为：玩家增益+玩家减益+敌方强化，在8.5.0的更新中做了一些更改，一些特别困难的组合不会同时出现，例如“生锈护甲”和“沉重打击”，即流亡者护甲降低和敌人伤害增加不会同时出现，这些buff和debuff分别的介绍如下：
 【英雄模式玩家增益】
 1.	良好体魄：玩家最大生命值增加40点
@@ -5975,7 +5984,7 @@
 5.	衰败之触：敌人更容易受到衰败伤害（+50%）
 6.	高效治疗：玩家治疗效果提高50%
 7.	治疗之风：每2秒恢复10生命值
-8.	尖锐尖刺：敌人在攻击你时会受到固定10点伤害
+8.	尖锐尖刺：敌人在攻击你时会受到固定25点伤害
 9.	强力重击：玩家攻击造成额外30点伤害
 【英雄模式玩家减益】
 1.	损坏的药水：无法使用药水（包括投掷药水）
@@ -5996,15 +6005,6 @@
 6.	强悍护甲：敌人护甲提高200
 7.	符文陷阱：地点中的符文数量增加
 8.	超自然反应：敌人有25%的机会躲避攻击</t>
-  </si>
-  <si>
-    <t>【地牢介绍】酷吏地下城一共有三层，第一层的敌人包括痛苦者，掷斧者，女祭司，屠宰者还有酷吏；第二层的敌人包括痛苦者，猎头者，女祭司，惩罚者，残忍酷吏和火焰守卫；第三层敌人主要就是领主卡恩。
-【陷阱类别】一二层陷阱包括：地刺，暗箭，触发空降小怪的暗板，喷火陷阱，毒火陷阱，太阳龙套装和拥有陷阱免疫技能的猫咪可以完全免疫这些陷阱；而第三层的卡恩领主房间的陷阱则无法通过任何方式免疫。
-【最终房间开启机制】第一层只有火盆房，第二层有三种，分别是火盆房间，钥匙房间，和毒火房间；下面是三种房间的介绍：
-（1）火盆房间：6个火盆，按照一定顺序点燃即可打开最终房间，点错则触发空降小怪，第一层来1-2个，第二层来2-3个痛苦者，若每次都点错，则会点击6+5+4+3+2+1一共21次
-（2）钥匙房间：一共有5个铁处女箱子分布在这一层地牢，每个箱子存有一把最终房间的小钥匙，集齐5把即可打开最终房间
-（3）毒火房间：这个房间通往最终房间的道路上设置有伤害超高的毒火陷阱，需要解密即可灭掉所有毒火，你面前有5个拉杆，每个拉杆会改变一处毒火的点燃和熄灭，5个拉杆中只有3个正确的拉杆，拉下这三个拉杆，顺序无关，毒火陷阱即可熄灭
-【炸弹房】一二层会大概率刷新出炸弹房，这些房间内有额外奖励，需要使用三级炸弹炸开，房间内安全没有敌人；这些炸弹房通常设在凹陷进去的光滑墙面，玩家贴上去右下角会显示炸弹图标示意可以进行爆破。</t>
   </si>
 </sst>
 </file>
@@ -8325,7 +8325,7 @@
         <v>694</v>
       </c>
       <c r="H55" s="48" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I55" s="37" t="s">
         <v>833</v>
@@ -11749,7 +11749,7 @@
         <v>316</v>
       </c>
       <c r="H189" s="45" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I189" s="37" t="s">
         <v>833</v>
@@ -11778,7 +11778,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A191" s="11" t="s">
         <v>321</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="27" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A194" s="11" t="s">
         <v>327</v>
       </c>
@@ -11893,7 +11893,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="27" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" ht="50.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A196" s="11" t="s">
         <v>331</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" ht="59.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A197" s="11" t="s">
         <v>333</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="40.5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A199" s="12" t="s">
         <v>337</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="27" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A203" s="12" t="s">
         <v>608</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="70.900000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:9" ht="118.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" s="16" t="s">
         <v>607</v>
       </c>
